--- a/HardwareSemis.xlsx
+++ b/HardwareSemis.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BD0EA4-CFBF-4672-A917-801FFD9720AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DCB3C6-F5A6-4ABD-8808-57242ABBD4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13160" yWindow="4450" windowWidth="21120" windowHeight="11660" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
+    <workbookView xWindow="1360" yWindow="4670" windowWidth="22360" windowHeight="16580" activeTab="1" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
   </bookViews>
   <sheets>
     <sheet name="Semiconductors" sheetId="1" r:id="rId1"/>
-    <sheet name="Quantum" sheetId="5" r:id="rId2"/>
-    <sheet name="Networking" sheetId="3" r:id="rId3"/>
-    <sheet name="Electronics-Computers" sheetId="2" r:id="rId4"/>
-    <sheet name="FX" sheetId="4" r:id="rId5"/>
+    <sheet name="Memory" sheetId="7" r:id="rId2"/>
+    <sheet name="CapEquiment" sheetId="8" r:id="rId3"/>
+    <sheet name="Optical" sheetId="6" r:id="rId4"/>
+    <sheet name="Quantum" sheetId="5" r:id="rId5"/>
+    <sheet name="Networking" sheetId="3" r:id="rId6"/>
+    <sheet name="Electronics-Computers" sheetId="2" r:id="rId7"/>
+    <sheet name="FX" sheetId="4" r:id="rId8"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId6"/>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
     <externalReference r:id="rId9"/>
     <externalReference r:id="rId10"/>
     <externalReference r:id="rId11"/>
@@ -41,6 +41,13 @@
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
     <externalReference r:id="rId26"/>
+    <externalReference r:id="rId27"/>
+    <externalReference r:id="rId28"/>
+    <externalReference r:id="rId29"/>
+    <externalReference r:id="rId30"/>
+    <externalReference r:id="rId31"/>
+    <externalReference r:id="rId32"/>
+    <externalReference r:id="rId33"/>
   </externalReferences>
   <definedNames>
     <definedName name="CNY">FX!$B$4</definedName>
@@ -68,10 +75,38 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={154242C3-2513-48BF-A6D9-D4A0AF6D462E}</author>
+    <author>tc={1D20DD93-FEBE-47F7-BD0B-671BE5F1EC3A}</author>
+  </authors>
+  <commentList>
+    <comment ref="U5" authorId="0" shapeId="0" xr:uid="{154242C3-2513-48BF-A6D9-D4A0AF6D462E}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was 57.10</t>
+      </text>
+    </comment>
+    <comment ref="V5" authorId="1" shapeId="0" xr:uid="{1D20DD93-FEBE-47F7-BD0B-671BE5F1EC3A}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Was  95.65</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="2">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -82,16 +117,170 @@
       </extLst>
     </bk>
   </futureMetadata>
+  <futureMetadata name="XLRICHVALUE" count="15">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="2"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="5"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="14"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="16"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="19"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="26"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="29"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="32"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="35"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="38"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="40"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="43"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="49"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
+  <valueMetadata count="15">
+    <bk>
+      <rc t="2" v="0"/>
+    </bk>
+    <bk>
+      <rc t="2" v="1"/>
+    </bk>
+    <bk>
+      <rc t="2" v="2"/>
+    </bk>
+    <bk>
+      <rc t="2" v="3"/>
+    </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
+    <bk>
+      <rc t="2" v="5"/>
+    </bk>
+    <bk>
+      <rc t="2" v="6"/>
+    </bk>
+    <bk>
+      <rc t="2" v="7"/>
+    </bk>
+    <bk>
+      <rc t="2" v="8"/>
+    </bk>
+    <bk>
+      <rc t="2" v="9"/>
+    </bk>
+    <bk>
+      <rc t="2" v="10"/>
+    </bk>
+    <bk>
+      <rc t="2" v="11"/>
+    </bk>
+    <bk>
+      <rc t="2" v="12"/>
+    </bk>
+    <bk>
+      <rc t="2" v="13"/>
+    </bk>
+    <bk>
+      <rc t="2" v="14"/>
+    </bk>
+  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="363">
   <si>
     <t>Name</t>
   </si>
@@ -99,39 +288,21 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Nvidia</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
     <t>MC</t>
   </si>
   <si>
-    <t>Intel</t>
-  </si>
-  <si>
-    <t>INTC</t>
-  </si>
-  <si>
     <t>AMD</t>
   </si>
   <si>
-    <t>Texas Instruments</t>
-  </si>
-  <si>
     <t>TXN</t>
   </si>
   <si>
     <t>Taiwan Semi</t>
   </si>
   <si>
-    <t>TSM</t>
-  </si>
-  <si>
     <t>Apple</t>
   </si>
   <si>
@@ -165,24 +336,15 @@
     <t>005930 KS</t>
   </si>
   <si>
-    <t>Broadcom</t>
-  </si>
-  <si>
     <t>ASML</t>
   </si>
   <si>
-    <t>AVGO</t>
-  </si>
-  <si>
     <t>CSCO</t>
   </si>
   <si>
     <t>Cisco</t>
   </si>
   <si>
-    <t>Qualcomm</t>
-  </si>
-  <si>
     <t>QCOM</t>
   </si>
   <si>
@@ -192,9 +354,6 @@
     <t>AMAT</t>
   </si>
   <si>
-    <t>Analog Devices</t>
-  </si>
-  <si>
     <t>ADI</t>
   </si>
   <si>
@@ -309,12 +468,6 @@
     <t>NXPI</t>
   </si>
   <si>
-    <t>Juniper</t>
-  </si>
-  <si>
-    <t>JNPR</t>
-  </si>
-  <si>
     <t>1810 HK</t>
   </si>
   <si>
@@ -330,9 +483,6 @@
     <t>MRVL</t>
   </si>
   <si>
-    <t>MediaTek</t>
-  </si>
-  <si>
     <t>2454 TT</t>
   </si>
   <si>
@@ -447,9 +597,6 @@
     <t>Founded</t>
   </si>
   <si>
-    <t>ARM Holdings</t>
-  </si>
-  <si>
     <t>ARM</t>
   </si>
   <si>
@@ -937,6 +1084,291 @@
   </si>
   <si>
     <t>COHR</t>
+  </si>
+  <si>
+    <t>Kioxia</t>
+  </si>
+  <si>
+    <t>285A JP</t>
+  </si>
+  <si>
+    <t>Seagate</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>Palo Alto</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>Sony</t>
+  </si>
+  <si>
+    <t>6758 JP</t>
+  </si>
+  <si>
+    <t>CBRS</t>
+  </si>
+  <si>
+    <t>Zhongji Innolight</t>
+  </si>
+  <si>
+    <t>300308 CH</t>
+  </si>
+  <si>
+    <t>Amphenol</t>
+  </si>
+  <si>
+    <t>APH</t>
+  </si>
+  <si>
+    <t>Murata Manufacturing</t>
+  </si>
+  <si>
+    <t>6981 JP</t>
+  </si>
+  <si>
+    <t>Lumentum</t>
+  </si>
+  <si>
+    <t>LITE</t>
+  </si>
+  <si>
+    <t>Eoptolink</t>
+  </si>
+  <si>
+    <t>300502 CH</t>
+  </si>
+  <si>
+    <t>Credo</t>
+  </si>
+  <si>
+    <t>CRDO</t>
+  </si>
+  <si>
+    <t>Ubiquiti</t>
+  </si>
+  <si>
+    <t>UI</t>
+  </si>
+  <si>
+    <t>Tower Semiconductor</t>
+  </si>
+  <si>
+    <t>TSEM</t>
+  </si>
+  <si>
+    <t>BE Semi</t>
+  </si>
+  <si>
+    <t>BESI</t>
+  </si>
+  <si>
+    <t>763 HK</t>
+  </si>
+  <si>
+    <t>QNT</t>
+  </si>
+  <si>
+    <t>Lattice</t>
+  </si>
+  <si>
+    <t>LSCC</t>
+  </si>
+  <si>
+    <t>Asustek</t>
+  </si>
+  <si>
+    <t>2357 HK</t>
+  </si>
+  <si>
+    <t>Logitech</t>
+  </si>
+  <si>
+    <t>LOGN</t>
+  </si>
+  <si>
+    <t>992 HK</t>
+  </si>
+  <si>
+    <t>Fortinet</t>
+  </si>
+  <si>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>Samsung Electro-Mechanics</t>
+  </si>
+  <si>
+    <t>009150 KS</t>
+  </si>
+  <si>
+    <t>Synaptics</t>
+  </si>
+  <si>
+    <t>SYNA</t>
+  </si>
+  <si>
+    <t>Hamamatsu</t>
+  </si>
+  <si>
+    <t>6965 JP</t>
+  </si>
+  <si>
+    <t>Seiko Epson</t>
+  </si>
+  <si>
+    <t>6724 JP</t>
+  </si>
+  <si>
+    <t>GigaDevice</t>
+  </si>
+  <si>
+    <t>3986 HK</t>
+  </si>
+  <si>
+    <t>United Micro</t>
+  </si>
+  <si>
+    <t>2303 TT</t>
+  </si>
+  <si>
+    <t>Luxshare</t>
+  </si>
+  <si>
+    <t>002475 CH</t>
+  </si>
+  <si>
+    <t>Fujikura</t>
+  </si>
+  <si>
+    <t>5803 JP</t>
+  </si>
+  <si>
+    <t>Suzhou Dongshan Precision Manufacturing</t>
+  </si>
+  <si>
+    <t>002384 CH</t>
+  </si>
+  <si>
+    <t>Yageo Corporation</t>
+  </si>
+  <si>
+    <t>2327 TT</t>
+  </si>
+  <si>
+    <t>Sanmina</t>
+  </si>
+  <si>
+    <t>SANM</t>
+  </si>
+  <si>
+    <t>Teradyne</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>Ciena</t>
+  </si>
+  <si>
+    <t>CIEN</t>
+  </si>
+  <si>
+    <t>Keysight</t>
+  </si>
+  <si>
+    <t>KEYS</t>
+  </si>
+  <si>
+    <t>TE Connectivity</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>Flex</t>
+  </si>
+  <si>
+    <t>FLEX</t>
+  </si>
+  <si>
+    <t>Suzhou TFC Optical Communication</t>
+  </si>
+  <si>
+    <t>300394 CH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yangtze Optical Fibre and Cable </t>
+  </si>
+  <si>
+    <t>6869 HK</t>
+  </si>
+  <si>
+    <t>Fabrinet</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>Victory Giant Technology</t>
+  </si>
+  <si>
+    <t>2476 HK</t>
+  </si>
+  <si>
+    <t>Nanya</t>
+  </si>
+  <si>
+    <t>2408 HK</t>
+  </si>
+  <si>
+    <t>3037 TT</t>
+  </si>
+  <si>
+    <t>Unimicron</t>
+  </si>
+  <si>
+    <t>Shennan Circuit Co</t>
+  </si>
+  <si>
+    <t>002916 CH</t>
+  </si>
+  <si>
+    <t>IBIDEN</t>
+  </si>
+  <si>
+    <t>4062 JP</t>
+  </si>
+  <si>
+    <t>Accton Technology Corp.</t>
+  </si>
+  <si>
+    <t>2345 TT</t>
+  </si>
+  <si>
+    <t>Chaozhou Three-Circle</t>
+  </si>
+  <si>
+    <t>300408 CH</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>nLIGHT</t>
+  </si>
+  <si>
+    <t>LASR</t>
+  </si>
+  <si>
+    <t>Maxlinear</t>
+  </si>
+  <si>
+    <t>MXL</t>
   </si>
 </sst>
 </file>
@@ -949,7 +1381,7 @@
     <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0\x"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -971,19 +1403,25 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="6">
@@ -1054,7 +1492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1081,7 +1519,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1096,6 +1533,9 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1103,6 +1543,20 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1176,18 +1630,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>907.57171200000005</v>
+          <cell r="J3">
+            <v>487.08704</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>9090</v>
+          <cell r="J5">
+            <v>3439.308</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>7937</v>
+          <cell r="J6">
+            <v>8134.6509999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -1244,40 +1698,6 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>148.08975799999999</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>3735</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
           <cell r="J3">
             <v>135.42215899999999</v>
           </cell>
@@ -1299,7 +1719,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink13.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1333,7 +1753,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink14.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1367,7 +1787,143 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink15.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>1145</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>31025</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>5722</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink16.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>148.08975799999999</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>3735</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>393.5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>6021.2000000000007</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>4608.2</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>799</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>13479</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>6553</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1407,7 +1963,41 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="4">
+          <cell r="J4">
+            <v>25931</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="J7">
+            <v>94986</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="J8">
+            <v>2900034</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1449,7 +2039,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1485,7 +2075,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink22.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1537,7 +2127,109 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink23.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>115.959118</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>423.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>796.7</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink24.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>1603</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>335855</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>16560</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink25.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>1044.497032</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>3664</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1571,7 +2263,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1590,158 +2282,22 @@
         </row>
         <row r="5">
           <cell r="K5">
-            <v>112651.8</v>
+            <v>201997.7</v>
           </cell>
         </row>
         <row r="6">
           <cell r="K6">
-            <v>19330.2</v>
+            <v>28138.799999999999</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink21.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="I3">
-            <v>115.959118</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="I5">
-            <v>423.3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="I6">
-            <v>796.7</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="J4">
-            <v>25931</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="J7">
-            <v>94986</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="J8">
-            <v>2900034</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="L3">
-            <v>393.5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="L5">
-            <v>6021.2000000000007</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="L6">
-            <v>4608.2</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="J3">
-            <v>1108.841326</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="J5">
-            <v>9154</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="J6">
-            <v>13258</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1775,41 +2331,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Main"/>
-      <sheetName val="Model"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="3">
-          <cell r="K3">
-            <v>799</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="K5">
-            <v>13479</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="K6">
-            <v>6553</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1826,7 +2348,7 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>4531</v>
+            <v>5026</v>
           </cell>
         </row>
         <row r="5">
@@ -1849,7 +2371,41 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="K3">
+            <v>907.57171200000005</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="K5">
+            <v>9090</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="K6">
+            <v>7937</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
@@ -1881,6 +2437,1739 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="H3">
+            <v>874.8</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="H5">
+            <v>3843.6</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="H6">
+            <v>4961.3</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Martin Shkreli" id="{A1E0C133-7285-4698-B154-62333ECFCACF}" userId="9ffda80931a57275" providerId="Windows Live"/>
+</personList>
+</file>
+
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+  <types>
+    <type name="_imageurl">
+      <keyFlags>
+        <key name="Blip Identifier">
+          <flag name="ShowInCardView" value="0"/>
+        </key>
+      </keyFlags>
+    </type>
+    <type name="_linkedentity">
+      <keyFlags>
+        <key name="%cvi">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+          <flag name="ExcludeFromCalcComparison" value="1"/>
+        </key>
+      </keyFlags>
+    </type>
+    <type name="_linkedentitycore">
+      <keyFlags>
+        <key name="%EntityServiceId">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%EntitySubDomainId">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%EntityCulture">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%EntityId">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%IsRefreshable">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+          <flag name="ExcludeFromCalcComparison" value="1"/>
+        </key>
+        <key name="%ProviderInfo">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%DataProviderExternalLinkLogo">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%DataProviderExternalLink">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+        </key>
+        <key name="%OutdatedReason">
+          <flag name="ShowInCardView" value="0"/>
+          <flag name="ShowInDotNotation" value="0"/>
+          <flag name="ShowInAutoComplete" value="0"/>
+          <flag name="ExcludeFromCalcComparison" value="1"/>
+        </key>
+      </keyFlags>
+    </type>
+  </types>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="50">
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1yv52&amp;q=XNAS%3aNVDA&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1yv52</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>236.54</v>
+    <v>161.61000000000001</v>
+    <v>2.2214</v>
+    <v>8.18</v>
+    <v>-1.8490000000000002E-3</v>
+    <v>4.0339E-2</v>
+    <v>-0.39</v>
+    <v>USD</v>
+    <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
+    <v>42000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
+    <v>211</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999999178122</v>
+    <v>0</v>
+    <v>201.92</v>
+    <v>5105232000000</v>
+    <v>NVIDIA CORPORATION</v>
+    <v>NVIDIA CORPORATION</v>
+    <v>202</v>
+    <v>31.053699999999999</v>
+    <v>202.78</v>
+    <v>210.96</v>
+    <v>210.57</v>
+    <v>24200000000</v>
+    <v>NVDA</v>
+    <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
+    <v>148421001</v>
+    <v>152809403</v>
+    <v>1998</v>
+  </rv>
+  <rv s="2">
+    <v>1</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a24kjc&amp;q=XNYS%3aTSM&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a24kjc</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>479</v>
+    <v>223.7</v>
+    <v>1.3766</v>
+    <v>-2.85</v>
+    <v>3.8929999999999998E-3</v>
+    <v>-6.522E-3</v>
+    <v>1.6898</v>
+    <v>USD</v>
+    <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
+    <v>52045</v>
+    <v>New York Stock Exchange</v>
+    <v>XNYS</v>
+    <v>XNYS</v>
+    <v>No.8, Li-Hsin 6th Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
+    <v>439.65499999999997</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999984895316</v>
+    <v>3</v>
+    <v>428.1</v>
+    <v>2251500228140</v>
+    <v>Taiwan Semiconductor Manufacturing Company Limited</v>
+    <v>Taiwan Semiconductor Manufacturing Company Limited</v>
+    <v>438.66500000000002</v>
+    <v>36.970799999999997</v>
+    <v>436.96</v>
+    <v>434.11</v>
+    <v>435.7998</v>
+    <v>5186474000</v>
+    <v>TSM</v>
+    <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
+    <v>9595123</v>
+    <v>14552561</v>
+    <v>1987</v>
+  </rv>
+  <rv s="2">
+    <v>4</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1nz8m&amp;q=XNAS%3aAVGO&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1nz8m</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>BROADCOM INC. (XNAS:AVGO)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>495</v>
+    <v>269.58</v>
+    <v>1.4661999999999999</v>
+    <v>-1.1399999999999999</v>
+    <v>1.075E-3</v>
+    <v>-2.8419999999999999E-3</v>
+    <v>0.4299</v>
+    <v>USD</v>
+    <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
+    <v>33000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>3421 Hillview Avenue, PALO ALTO, CA, 94304 US</v>
+    <v>402.44</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999910358594</v>
+    <v>6</v>
+    <v>395.7</v>
+    <v>1902889272600</v>
+    <v>BROADCOM INC.</v>
+    <v>BROADCOM INC.</v>
+    <v>398.5</v>
+    <v>66.812899999999999</v>
+    <v>401.11</v>
+    <v>399.97</v>
+    <v>400.3999</v>
+    <v>4757580000</v>
+    <v>AVGO</v>
+    <v>BROADCOM INC. (XNAS:AVGO)</v>
+    <v>14595928</v>
+    <v>34632683</v>
+    <v>2018</v>
+  </rv>
+  <rv s="2">
+    <v>7</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1ndww&amp;q=XNAS%3aAMD&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1ndww</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>584.73</v>
+    <v>141.6</v>
+    <v>2.4632999999999998</v>
+    <v>11.17</v>
+    <v>3.3700000000000002E-3</v>
+    <v>2.0430999999999998E-2</v>
+    <v>1.88</v>
+    <v>USD</v>
+    <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
+    <v>31000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
+    <v>560.25</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999974675782</v>
+    <v>9</v>
+    <v>540.04999999999995</v>
+    <v>909695991890</v>
+    <v>ADVANCED MICRO DEVICES, INC.</v>
+    <v>ADVANCED MICRO DEVICES, INC.</v>
+    <v>544.005</v>
+    <v>182.24610000000001</v>
+    <v>546.72</v>
+    <v>557.89</v>
+    <v>559.77</v>
+    <v>1630601000</v>
+    <v>AMD</v>
+    <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
+    <v>20704530</v>
+    <v>31272350</v>
+    <v>1969</v>
+  </rv>
+  <rv s="2">
+    <v>10</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1vmf2&amp;q=XNAS%3aINTC&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1vmf2</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>INTEL CORPORATION (XNAS:INTC)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>142.35</v>
+    <v>18.965</v>
+    <v>2.1977000000000002</v>
+    <v>-2.7</v>
+    <v>-2.0479999999999999E-3</v>
+    <v>-2.3990999999999998E-2</v>
+    <v>-0.22500000000000001</v>
+    <v>USD</v>
+    <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
+    <v>83200</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
+    <v>110.85</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999984073438</v>
+    <v>12</v>
+    <v>107.45</v>
+    <v>552055840000</v>
+    <v>INTEL CORPORATION</v>
+    <v>INTEL CORPORATION</v>
+    <v>109.575</v>
+    <v>0</v>
+    <v>112.54</v>
+    <v>109.84</v>
+    <v>109.61499999999999</v>
+    <v>5026000000</v>
+    <v>INTC</v>
+    <v>INTEL CORPORATION (XNAS:INTC)</v>
+    <v>70846601</v>
+    <v>127554214</v>
+    <v>1989</v>
+  </rv>
+  <rv s="2">
+    <v>13</v>
+  </rv>
+  <rv s="3">
+    <v>en-US</v>
+    <v>cau7bh</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>5</v>
+    <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
+    <v>6</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>452.7</v>
+    <v>100.02</v>
+    <v>1.2829999999999999</v>
+    <v>-4.4800000000000004</v>
+    <v>3.5620000000000001E-3</v>
+    <v>-1.3664000000000001E-2</v>
+    <v>1.1517999999999999</v>
+    <v>USD</v>
+    <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
+    <v>9584</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>110 Fulbourn Road, CAMBRIDGE, CAMBRIDGESHIRE, CB1 9NJ GB</v>
+    <v>328.28059999999999</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999949501565</v>
+    <v>317.88</v>
+    <v>345406067810</v>
+    <v>ARM HOLDINGS PLC</v>
+    <v>ARM HOLDINGS PLC</v>
+    <v>322.7</v>
+    <v>387.37459999999999</v>
+    <v>327.87</v>
+    <v>323.39</v>
+    <v>324.54180000000002</v>
+    <v>1068079000</v>
+    <v>ARM</v>
+    <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
+    <v>2770934</v>
+    <v>10572514</v>
+    <v>2018</v>
+  </rv>
+  <rv s="2">
+    <v>15</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a24p1h&amp;q=XNAS%3aTXN&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a24p1h</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>TEXAS INSTRUMENTS INCORPORATED (XNAS:TXN)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>334.03</v>
+    <v>152.72999999999999</v>
+    <v>1.3137000000000001</v>
+    <v>2.93</v>
+    <v>1.9589999999999998E-3</v>
+    <v>9.4970000000000002E-3</v>
+    <v>0.61</v>
+    <v>USD</v>
+    <v>Texas Instruments Incorporated is engaged in the design and manufacture of semiconductors. The Company operates through two segments, which include Analog and Embedded Processing. Its Analog segment semiconductors are used to manage power in all electronic equipment by converting, distributing, storing, discharging, isolating, and measuring electrical energy. It consists of two products, which include Power and Signal Chain. The Analog segment includes product lines, such as Power and Signal Chain. Power includes products that help customers manage power in electronic systems. Signal Chain products include amplifiers, data converters, interface products, motor drives, clocks, logic, and sensing products. Its portfolio is designed to manage power requirements across different voltage levels. The Embedded Processing segment products are designed to handle specific tasks and can be optimized for various combinations of performance, power, and cost, depending on the application.</v>
+    <v>33000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>12500 T I Blvd, DALLAS, TX, 75243-0592 US</v>
+    <v>312.92500000000001</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.998741017967</v>
+    <v>17</v>
+    <v>303.39999999999998</v>
+    <v>283457503488</v>
+    <v>TEXAS INSTRUMENTS INCORPORATED</v>
+    <v>TEXAS INSTRUMENTS INCORPORATED</v>
+    <v>304.2</v>
+    <v>56.299900000000001</v>
+    <v>308.52999999999997</v>
+    <v>311.45999999999998</v>
+    <v>312.07</v>
+    <v>910092800</v>
+    <v>TXN</v>
+    <v>TEXAS INSTRUMENTS INCORPORATED (XNAS:TXN)</v>
+    <v>4141905</v>
+    <v>9896056</v>
+    <v>1938</v>
+  </rv>
+  <rv s="2">
+    <v>18</v>
+  </rv>
+  <rv s="0">
+    <v>http://en.wikipedia.org/wiki/Public_domain</v>
+    <v>Public domain</v>
+  </rv>
+  <rv s="0">
+    <v>http://en.wikipedia.org/wiki/Qualcomm</v>
+    <v>Wikipedia</v>
+  </rv>
+  <rv s="4">
+    <v>20</v>
+    <v>21</v>
+  </rv>
+  <rv s="5">
+    <v>11</v>
+    <v>https://www.bing.com/th?id=AMMS_2b1c176dae370ecc0d55a1517537f595&amp;qlt=95</v>
+    <v>22</v>
+    <v>0</v>
+    <v>https://www.bing.com/images/search?form=xlimg&amp;q=qualcomm</v>
+    <v>Image of QUALCOMM INCORPORATED</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a21k2w&amp;q=XNAS%3aQCOM&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="6">
+    <v>en-US</v>
+    <v>a21k2w</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>7</v>
+    <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
+    <v>9</v>
+    <v>10</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>259.92</v>
+    <v>121.99</v>
+    <v>1.6361000000000001</v>
+    <v>-1.95</v>
+    <v>-1.374E-3</v>
+    <v>-1.0204E-2</v>
+    <v>-0.26</v>
+    <v>USD</v>
+    <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
+    <v>52000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
+    <v>190.19</v>
+    <v>23</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999990844532</v>
+    <v>24</v>
+    <v>185.72</v>
+    <v>199374640000</v>
+    <v>QUALCOMM INCORPORATED</v>
+    <v>QUALCOMM INCORPORATED</v>
+    <v>187.50800000000001</v>
+    <v>20.787700000000001</v>
+    <v>191.11</v>
+    <v>189.16</v>
+    <v>188.9</v>
+    <v>1054000000</v>
+    <v>QCOM</v>
+    <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
+    <v>7063957</v>
+    <v>21168579</v>
+    <v>1991</v>
+  </rv>
+  <rv s="2">
+    <v>25</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1xygh&amp;q=XNAS%3aMRVL&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1xygh</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>329.88</v>
+    <v>61.44</v>
+    <v>2.2000999999999999</v>
+    <v>-7.4</v>
+    <v>3.4770000000000001E-3</v>
+    <v>-3.0426000000000002E-2</v>
+    <v>0.82</v>
+    <v>USD</v>
+    <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
+    <v>7480</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>1000 N. West Street, Suite 1200, WILMINGTON, DE, 19801 US</v>
+    <v>240.94</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.999979282031</v>
+    <v>27</v>
+    <v>232.02</v>
+    <v>206514474784</v>
+    <v>MARVELL TECHNOLOGY, INC.</v>
+    <v>MARVELL TECHNOLOGY, INC.</v>
+    <v>237.79</v>
+    <v>83.304500000000004</v>
+    <v>243.21</v>
+    <v>235.81</v>
+    <v>236.63</v>
+    <v>875766400</v>
+    <v>MRVL</v>
+    <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
+    <v>15105972</v>
+    <v>60320638</v>
+    <v>2020</v>
+  </rv>
+  <rv s="2">
+    <v>28</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1mvjc&amp;q=XNAS%3aADI&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1mvjc</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>ANALOG DEVICES, INC. (XNAS:ADI)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>445.91</v>
+    <v>218.37</v>
+    <v>1.194</v>
+    <v>2.0099999999999998</v>
+    <v>1.4149999999999998E-3</v>
+    <v>5.1060000000000003E-3</v>
+    <v>0.56000000000000005</v>
+    <v>USD</v>
+    <v>Analog Devices, Inc. is a global semiconductor company. It combines analog, digital, artificial intelligence (AI), and software technologies into solutions that combat climate change, reliably connect humans and the world, and help drive advancements in automation and robotics, mobility, healthcare, energy and data centers. It designs, manufactures, tests and markets a portfolio of solutions, including integrated circuits (ICs), software and subsystems that leverage high-performance analog, mixed-signal and digital signal processing technologies. Its product portfolio, domain specialization and advanced manufacturing capabilities extend across high-performance precision and high-speed mixed-signal, power management and processing technologies, including data converters, amplifiers, power management, power management, radio frequency ICs, edge processors and other sensors. Its IC product portfolio includes both general-purpose products used by a range of customers and applications.</v>
+    <v>24500</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>One Analog Way, WILMINGTON, MA, 01887 US</v>
+    <v>398.33499999999998</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.997845589845</v>
+    <v>30</v>
+    <v>385.93</v>
+    <v>192715971550</v>
+    <v>ANALOG DEVICES, INC.</v>
+    <v>ANALOG DEVICES, INC.</v>
+    <v>387.5</v>
+    <v>55.972999999999999</v>
+    <v>393.64</v>
+    <v>395.65</v>
+    <v>396.21</v>
+    <v>487087000</v>
+    <v>ADI</v>
+    <v>ANALOG DEVICES, INC. (XNAS:ADI)</v>
+    <v>2325909</v>
+    <v>5475345</v>
+    <v>1965</v>
+  </rv>
+  <rv s="2">
+    <v>31</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=anb9sm&amp;q=XTAI%3a2454&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="7">
+    <v>en-US</v>
+    <v>anb9sm</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>12</v>
+    <v>MediaTek Inc. (XTAI:2454)</v>
+    <v>2</v>
+    <v>13</v>
+    <v>Finance</v>
+    <v>14</v>
+    <v>4970</v>
+    <v>1130</v>
+    <v>2.1217999999999999</v>
+    <v>-70</v>
+    <v>-1.7521999999999999E-2</v>
+    <v>TWD</v>
+    <v>MediaTek Inc is a Taiwan-based company principally engaged in the research, development, manufacture and distribution of multimedia integrated circuit (IC) chipsets. The main products including mobile communication chipsets, tablet computer chips, bluetooth chips, wireless local area network (WLAN) chips, global positioning system (GPS) chips, optical storage chipsets, artificial intelligence Internet of Things device single chips, automotive electronic chipsets and others. The Company is also involved in the provision of related design, testing, maintenance and technological consultancy services. The Company's products are mainly used in mobile phones, digital TVs, personal computer systems, digital home appliances, wearable devices and Internet of Things products. The Company mainly distributes its products in domestic and overseas markets.</v>
+    <v>6999</v>
+    <v>Taiwan Stock Exchange</v>
+    <v>XTAI</v>
+    <v>XTAI</v>
+    <v>No. 1, Dusing 1st Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
+    <v>4050</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46212.402013888888</v>
+    <v>33</v>
+    <v>3925</v>
+    <v>6295287875000</v>
+    <v>MediaTek Inc.</v>
+    <v>MediaTek Inc.</v>
+    <v>3970</v>
+    <v>62.4</v>
+    <v>3995</v>
+    <v>3925</v>
+    <v>1603895000</v>
+    <v>2454</v>
+    <v>MediaTek Inc. (XTAI:2454)</v>
+    <v>7370647</v>
+    <v>11393580</v>
+    <v>1997</v>
+  </rv>
+  <rv s="2">
+    <v>34</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a1y4oc&amp;q=XNAS%3aMU&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a1y4oc</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>1255</v>
+    <v>103.38</v>
+    <v>2.1598000000000002</v>
+    <v>-12.34</v>
+    <v>3.5230000000000001E-3</v>
+    <v>-1.2444E-2</v>
+    <v>3.4500999999999999</v>
+    <v>USD</v>
+    <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
+    <v>53000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
+    <v>998</v>
+    <v>Semiconductors &amp; Semiconductor Equipment</v>
+    <v>Stock</v>
+    <v>46213.9999923375</v>
+    <v>36</v>
+    <v>954.13</v>
+    <v>1106014564900</v>
+    <v>MICRON TECHNOLOGY, INC.</v>
+    <v>MICRON TECHNOLOGY, INC.</v>
+    <v>964.97500000000002</v>
+    <v>22.4495</v>
+    <v>991.64</v>
+    <v>979.3</v>
+    <v>982.75009999999997</v>
+    <v>1129393000</v>
+    <v>MU</v>
+    <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
+    <v>31768093</v>
+    <v>55952383</v>
+    <v>1984</v>
+  </rv>
+  <rv s="2">
+    <v>37</v>
+  </rv>
+  <rv s="3">
+    <v>en-US</v>
+    <v>cfwqww</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>5</v>
+    <v>SANDISK CORPORATION (XNAS:SNDK)</v>
+    <v>6</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>2354.3899000000001</v>
+    <v>40.1</v>
+    <v>2.706</v>
+    <v>57.65</v>
+    <v>9.9590000000000008E-3</v>
+    <v>3.1023000000000002E-2</v>
+    <v>19.079999999999998</v>
+    <v>USD</v>
+    <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
+    <v>11000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>951 Sandisk Drive, MILPITAS, CA, 95035 US</v>
+    <v>1946.835</v>
+    <v>Computers, Phones &amp; Household Electronics</v>
+    <v>Stock</v>
+    <v>46213.999983726564</v>
+    <v>1773</v>
+    <v>283728209616</v>
+    <v>SANDISK CORPORATION</v>
+    <v>SANDISK CORPORATION</v>
+    <v>1778.9839999999999</v>
+    <v>67.734800000000007</v>
+    <v>1858.27</v>
+    <v>1915.92</v>
+    <v>1935</v>
+    <v>148089800</v>
+    <v>SNDK</v>
+    <v>SANDISK CORPORATION (XNAS:SNDK)</v>
+    <v>11022652</v>
+    <v>12066811</v>
+    <v>2024</v>
+  </rv>
+  <rv s="2">
+    <v>39</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a23rjc&amp;q=XNAS%3aSTX&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="1">
+    <v>en-US</v>
+    <v>a23rjc</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>0</v>
+    <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
+    <v>2</v>
+    <v>3</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>1145</v>
+    <v>138.30000000000001</v>
+    <v>2.0746000000000002</v>
+    <v>20.25</v>
+    <v>4.4709999999999997E-4</v>
+    <v>2.2751E-2</v>
+    <v>0.40699999999999997</v>
+    <v>USD</v>
+    <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
+    <v>30000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>121 Woodlands Avenue 5, 739009 SG</v>
+    <v>927.2799</v>
+    <v>Computers, Phones &amp; Household Electronics</v>
+    <v>Stock</v>
+    <v>46213.999899767972</v>
+    <v>41</v>
+    <v>861.63</v>
+    <v>205966336714</v>
+    <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
+    <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
+    <v>861.63</v>
+    <v>84.516499999999994</v>
+    <v>890.09</v>
+    <v>910.34</v>
+    <v>910.74699999999996</v>
+    <v>226252100</v>
+    <v>STX</v>
+    <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
+    <v>4051284</v>
+    <v>4658461</v>
+    <v>2017</v>
+  </rv>
+  <rv s="2">
+    <v>42</v>
+  </rv>
+  <rv s="0">
+    <v>http://en.wikipedia.org/wiki/Western_Digital</v>
+    <v>Wikipedia</v>
+  </rv>
+  <rv s="4">
+    <v>20</v>
+    <v>44</v>
+  </rv>
+  <rv s="5">
+    <v>11</v>
+    <v>https://www.bing.com/th?id=AMMS_b9efb984265253a027f300c3dcbbcbc0&amp;qlt=95</v>
+    <v>45</v>
+    <v>0</v>
+    <v>https://www.bing.com/images/search?form=xlimg&amp;q=western+digital</v>
+    <v>Image of WESTERN DIGITAL CORPORATION</v>
+  </rv>
+  <rv s="0">
+    <v>https://www.bing.com/financeapi/forcetrigger?t=a25rnm&amp;q=XNAS%3aWDC&amp;form=skydnc</v>
+    <v>Learn more on Bing</v>
+  </rv>
+  <rv s="6">
+    <v>en-US</v>
+    <v>a25rnm</v>
+    <v>268435456</v>
+    <v>1</v>
+    <v>Powered by Refinitiv</v>
+    <v>7</v>
+    <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
+    <v>9</v>
+    <v>10</v>
+    <v>Finance</v>
+    <v>4</v>
+    <v>799.87</v>
+    <v>64.23</v>
+    <v>2.1341999999999999</v>
+    <v>4.5350000000000001</v>
+    <v>-1.116E-4</v>
+    <v>7.8449999999999995E-3</v>
+    <v>-6.5000000000000002E-2</v>
+    <v>USD</v>
+    <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
+    <v>40000</v>
+    <v>Nasdaq Stock Market</v>
+    <v>XNAS</v>
+    <v>XNAS</v>
+    <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
+    <v>585.20000000000005</v>
+    <v>46</v>
+    <v>Computers, Phones &amp; Household Electronics</v>
+    <v>Stock</v>
+    <v>46213.999795358592</v>
+    <v>47</v>
+    <v>562.76</v>
+    <v>200806621228</v>
+    <v>WESTERN DIGITAL CORPORATION</v>
+    <v>WESTERN DIGITAL CORPORATION</v>
+    <v>563.995</v>
+    <v>37.670299999999997</v>
+    <v>578.04999999999995</v>
+    <v>582.58500000000004</v>
+    <v>582.52</v>
+    <v>344682100</v>
+    <v>WDC</v>
+    <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
+    <v>4814144</v>
+    <v>10042796</v>
+    <v>2000</v>
+  </rv>
+  <rv s="2">
+    <v>48</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+  <s t="_hyperlink">
+    <k n="Address" t="s"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_linkedentity">
+    <k n="%cvi" t="r"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_sourceattribution">
+    <k n="License" t="r"/>
+    <k n="Source" t="r"/>
+  </s>
+  <s t="_imageurl">
+    <k n="_Provider" t="spb"/>
+    <k n="Address" t="s"/>
+    <k n="Attribution" t="r"/>
+    <k n="ComputedImage" t="b"/>
+    <k n="More Images Address" t="s"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change % (Extended hours)"/>
+    <k n="Change (%)"/>
+    <k n="Change (Extended hours)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Image" t="r"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Price (Extended hours)"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
+<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
+  <spbArrays count="4">
+    <a count="45">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="44">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="46">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Price (Extended hours)</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (Extended hours)</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Change % (Extended hours)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">Image</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="42">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+  </spbArrays>
+  <spbData count="15">
+    <spb s="0">
+      <v>0</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="1">
+      <v>0</v>
+      <v>0</v>
+      <v>0</v>
+    </spb>
+    <spb s="2">
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+    </spb>
+    <spb s="3">
+      <v>1</v>
+      <v>2</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+    </spb>
+    <spb s="4">
+      <v>at close</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: Nasdaq</v>
+      <v>GMT</v>
+      <v>Delayed 15 minutes</v>
+      <v>from close</v>
+      <v>from close</v>
+    </spb>
+    <spb s="5">
+      <v>1</v>
+      <v>Name</v>
+    </spb>
+    <spb s="6">
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+    </spb>
+    <spb s="0">
+      <v>2</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="7">
+      <v>0</v>
+      <v>0</v>
+    </spb>
+    <spb s="8">
+      <v>8</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+    </spb>
+    <spb s="9">
+      <v>1</v>
+      <v>2</v>
+      <v>2</v>
+      <v>1</v>
+      <v>3</v>
+      <v>1</v>
+      <v>10</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>6</v>
+      <v>1</v>
+      <v>1</v>
+      <v>1</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+      <v>1</v>
+      <v>1</v>
+      <v>5</v>
+    </spb>
+    <spb s="10">
+      <v>Powered by Refinitiv</v>
+    </spb>
+    <spb s="0">
+      <v>3</v>
+      <v>Name</v>
+      <v>LearnMoreOnLink</v>
+    </spb>
+    <spb s="11">
+      <v>11</v>
+      <v>2</v>
+      <v>2</v>
+      <v>11</v>
+      <v>3</v>
+      <v>11</v>
+      <v>11</v>
+      <v>11</v>
+      <v>4</v>
+      <v>4</v>
+      <v>5</v>
+      <v>12</v>
+      <v>11</v>
+      <v>11</v>
+      <v>11</v>
+      <v>4</v>
+      <v>7</v>
+      <v>8</v>
+      <v>9</v>
+      <v>4</v>
+    </spb>
+    <spb s="12">
+      <v>Delayed 20 minutes</v>
+      <v>from previous close</v>
+      <v>from previous close</v>
+      <v>Source: TWSE</v>
+      <v>GMT</v>
+    </spb>
+  </spbData>
+</supportingPropertyBags>
+</file>
+
+<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="13">
+  <s>
+    <k n="^Order" t="spba"/>
+    <k n="TitleProperty" t="s"/>
+    <k n="SubTitleProperty" t="s"/>
+  </s>
+  <s>
+    <k n="ShowInCardView" t="b"/>
+    <k n="ShowInDotNotation" t="b"/>
+    <k n="ShowInAutoComplete" t="b"/>
+  </s>
+  <s>
+    <k n="ExchangeID" t="spb"/>
+    <k n="UniqueName" t="spb"/>
+    <k n="`%ProviderInfo" t="spb"/>
+    <k n="LearnMoreOnLink" t="spb"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="P/E" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="Price" t="s"/>
+    <k n="Change" t="s"/>
+    <k n="Change (%)" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Last trade time" t="s"/>
+    <k n="Price (Extended hours)" t="s"/>
+    <k n="Change (Extended hours)" t="s"/>
+    <k n="Change % (Extended hours)" t="s"/>
+  </s>
+  <s>
+    <k n="^Order" t="spba"/>
+    <k n="TitleProperty" t="s"/>
+  </s>
+  <s>
+    <k n="ExchangeID" t="spb"/>
+    <k n="UniqueName" t="spb"/>
+    <k n="`%ProviderInfo" t="spb"/>
+  </s>
+  <s>
+    <k n="ShowInDotNotation" t="b"/>
+    <k n="ShowInAutoComplete" t="b"/>
+  </s>
+  <s>
+    <k n="Image" t="spb"/>
+    <k n="ExchangeID" t="spb"/>
+    <k n="UniqueName" t="spb"/>
+    <k n="`%ProviderInfo" t="spb"/>
+    <k n="LearnMoreOnLink" t="spb"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="P/E" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Image" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+    <k n="Price (Extended hours)" t="i"/>
+    <k n="Change (Extended hours)" t="i"/>
+    <k n="Change % (Extended hours)" t="i"/>
+  </s>
+  <s>
+    <k n="name" t="s"/>
+  </s>
+  <s>
+    <k n="Low" t="i"/>
+    <k n="P/E" t="i"/>
+    <k n="Beta" t="i"/>
+    <k n="High" t="i"/>
+    <k n="Name" t="i"/>
+    <k n="Open" t="i"/>
+    <k n="Price" t="i"/>
+    <k n="Change" t="i"/>
+    <k n="Volume" t="i"/>
+    <k n="Employees" t="i"/>
+    <k n="Change (%)" t="i"/>
+    <k n="Market cap" t="i"/>
+    <k n="52 week low" t="i"/>
+    <k n="52 week high" t="i"/>
+    <k n="Previous close" t="i"/>
+    <k n="Volume average" t="i"/>
+    <k n="Last trade time" t="i"/>
+    <k n="Year incorporated" t="i"/>
+    <k n="`%EntityServiceId" t="i"/>
+    <k n="Shares outstanding" t="i"/>
+  </s>
+  <s>
+    <k n="Price" t="s"/>
+    <k n="Change" t="s"/>
+    <k n="Change (%)" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Last trade time" t="s"/>
+  </s>
+</spbStructures>
+</file>
+
+<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
+<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <dxfs count="7">
+    <x:dxf>
+      <x:numFmt numFmtId="0" formatCode="General"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="3" formatCode="#,##0"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="14" formatCode="0.00%"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="27" formatCode="m/d/yyyy\ h:mm"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="1" formatCode="0"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="2" formatCode="0.00"/>
+    </x:dxf>
+  </dxfs>
+  <richProperties>
+    <rPr n="NumberFormat" t="s"/>
+    <rPr n="IsTitleField" t="b"/>
+    <rPr n="IsHeroField" t="b"/>
+  </richProperties>
+  <richStyles>
+    <rSty dxfid="0">
+      <rpv i="0">_([$$-en-US]* #,##0.00_);_([$$-en-US]* (#,##0.00);_([$$-en-US]* "-"??_);_(@_)</rpv>
+    </rSty>
+    <rSty dxfid="1">
+      <rpv i="0">#,##0.00</rpv>
+    </rSty>
+    <rSty>
+      <rpv i="1">1</rpv>
+    </rSty>
+    <rSty dxfid="2">
+      <rpv i="0">#,##0</rpv>
+    </rSty>
+    <rSty dxfid="3"/>
+    <rSty dxfid="0">
+      <rpv i="0">_([$$-en-US]* #,##0_);_([$$-en-US]* (#,##0);_([$$-en-US]* "-"_);_(@_)</rpv>
+    </rSty>
+    <rSty dxfid="4"/>
+    <rSty dxfid="5">
+      <rpv i="0">0</rpv>
+    </rSty>
+    <rSty dxfid="6">
+      <rpv i="0">0.00</rpv>
+    </rSty>
+    <rSty>
+      <rpv i="2">1</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">_-[$NT$-zh-TW]* #,##0.00_-;-[$NT$-zh-TW]* #,##0.00_-;_-[$NT$-zh-TW]* "-"??_-;_-@_-</rpv>
+    </rSty>
+    <rSty dxfid="0">
+      <rpv i="0">_-[$NT$-zh-TW]* #,##0_-;-[$NT$-zh-TW]* #,##0_-;_-[$NT$-zh-TW]* "-"_-;_-@_-</rpv>
+    </rSty>
+  </richStyles>
+</richStyleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2178,9 +4467,20 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="U5" dT="2026-07-11T14:13:23.22" personId="{A1E0C133-7285-4698-B154-62333ECFCACF}" id="{154242C3-2513-48BF-A6D9-D4A0AF6D462E}">
+    <text>Was 57.10</text>
+  </threadedComment>
+  <threadedComment ref="V5" dT="2026-07-11T14:13:33.10" personId="{A1E0C133-7285-4698-B154-62333ECFCACF}" id="{1D20DD93-FEBE-47F7-BD0B-671BE5F1EC3A}">
+    <text>Was  95.65</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B77F9E42-3F4A-4F5B-8F7C-4C05A85AC67E}">
-  <dimension ref="A2:AA58"/>
+  <dimension ref="A2:AA66"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.453125" customWidth="1"/>
@@ -2190,50 +4490,50 @@
     <col min="5" max="7" width="9.54296875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="9.1796875" style="3"/>
     <col min="10" max="10" width="11.81640625" style="3" customWidth="1"/>
-    <col min="12" max="12" width="7.453125" style="18" customWidth="1"/>
+    <col min="12" max="12" width="7.453125" style="17" customWidth="1"/>
     <col min="13" max="15" width="7.453125" customWidth="1"/>
-    <col min="16" max="16" width="7.453125" style="19" customWidth="1"/>
-    <col min="17" max="17" width="7.90625" style="18" customWidth="1"/>
+    <col min="16" max="16" width="7.453125" style="18" customWidth="1"/>
+    <col min="17" max="17" width="7.90625" style="17" customWidth="1"/>
     <col min="18" max="21" width="7.90625" customWidth="1"/>
-    <col min="22" max="22" width="7.90625" style="19" customWidth="1"/>
+    <col min="22" max="22" width="7.90625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>272</v>
-      </c>
-      <c r="M2" s="21">
-        <f>AVERAGE(M5:M19)</f>
-        <v>31.284158119831861</v>
-      </c>
-      <c r="N2" s="21">
-        <f>AVERAGE(N5:N19)</f>
-        <v>21.202967297362857</v>
+        <v>258</v>
+      </c>
+      <c r="M2" s="20">
+        <f ca="1">AVERAGE(M5:M17)</f>
+        <v>59.164673809953719</v>
+      </c>
+      <c r="N2" s="20">
+        <f ca="1">AVERAGE(N5:N17)</f>
+        <v>39.254719714013234</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L3" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="M3" s="24"/>
-      <c r="N3" s="24"/>
-      <c r="O3" s="24"/>
-      <c r="P3" s="25"/>
-      <c r="Q3" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="R3" s="24"/>
-      <c r="S3" s="24"/>
-      <c r="T3" s="24"/>
-      <c r="U3" s="24"/>
-      <c r="V3" s="25"/>
+      <c r="L3" s="25" t="s">
+        <v>257</v>
+      </c>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+      <c r="T3" s="26"/>
+      <c r="U3" s="26"/>
+      <c r="V3" s="27"/>
       <c r="Z3" s="13">
-        <f>AVERAGE(Z5:Z35)</f>
-        <v>1108057.2676866585</v>
+        <f>AVERAGE(Z5:Z33)</f>
+        <v>1052549.8109809407</v>
       </c>
       <c r="AA3" s="13">
-        <f>AVERAGE(AA5:AA35)</f>
-        <v>772594.93333333335</v>
+        <f>AVERAGE(AA5:AA33)</f>
+        <v>792600.5</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -2244,30 +4544,30 @@
         <v>1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L4" s="18">
+        <v>104</v>
+      </c>
+      <c r="L4" s="17">
         <v>2025</v>
       </c>
       <c r="M4">
@@ -2281,11 +4581,11 @@
         <f>+N4+1</f>
         <v>2028</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="18">
         <f>+O4+1</f>
         <v>2029</v>
       </c>
-      <c r="Q4" s="17">
+      <c r="Q4" s="16">
         <v>2024</v>
       </c>
       <c r="R4">
@@ -2302,57 +4602,59 @@
         <f>+T4+1</f>
         <v>2028</v>
       </c>
-      <c r="V4" s="19">
+      <c r="V4" s="18">
         <f>+U4+1</f>
         <v>2029</v>
       </c>
       <c r="W4" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="X4" t="s">
-        <v>277</v>
+        <v>263</v>
       </c>
       <c r="Y4" t="s">
-        <v>276</v>
+        <v>262</v>
       </c>
       <c r="Z4" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="AA4" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4">
-        <v>199.6</v>
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" t="str" cm="1">
+        <f t="array" aca="1" ref="C5" ca="1">_FV(B5,"Ticker symbol",TRUE)</f>
+        <v>NVDA</v>
+      </c>
+      <c r="D5" s="4" cm="1">
+        <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Price")</f>
+        <v>210.96</v>
       </c>
       <c r="E5" s="6">
-        <f>+D5*H5</f>
-        <v>4850280</v>
+        <f ca="1">+D5*H5</f>
+        <v>5126328</v>
       </c>
       <c r="F5" s="6">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
         <v>48325</v>
       </c>
       <c r="G5" s="6">
-        <f>+E5-F5</f>
-        <v>4801955</v>
+        <f t="shared" ref="G5:G16" ca="1" si="0">+E5-F5</f>
+        <v>5078003</v>
       </c>
       <c r="H5" s="6">
         <f>+[1]Main!$K$3</f>
         <v>24300</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>268</v>
+        <v>254</v>
       </c>
       <c r="J5" s="10">
         <v>46101</v>
@@ -2360,24 +4662,24 @@
       <c r="K5">
         <v>1993</v>
       </c>
-      <c r="L5" s="20">
-        <f>($G5/$H5)/R5</f>
-        <v>67.214733630077546</v>
-      </c>
-      <c r="M5" s="21">
-        <f>($G$5/$H$5)/S5</f>
-        <v>40.328840178046526</v>
-      </c>
-      <c r="N5" s="21">
-        <f>($G$5/$H$5)/T5</f>
-        <v>23.866101071549274</v>
-      </c>
-      <c r="O5" s="21">
-        <f>($G$5/$H$5)/U5</f>
-        <v>17.754835298511047</v>
-      </c>
-      <c r="P5" s="21"/>
-      <c r="Q5" s="22">
+      <c r="L5" s="19">
+        <f ca="1">($G5/$H5)/R5</f>
+        <v>71.078679208308841</v>
+      </c>
+      <c r="M5" s="20">
+        <f ca="1">($G$5/$H$5)/S5</f>
+        <v>42.647207524985298</v>
+      </c>
+      <c r="N5" s="20">
+        <f ca="1">($G$5/$H$5)/T5</f>
+        <v>25.238081747877779</v>
+      </c>
+      <c r="O5" s="20">
+        <f ca="1">($G$5/$H$5)/U5</f>
+        <v>18.775500168232522</v>
+      </c>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="21">
         <v>1.19</v>
       </c>
       <c r="R5" s="2">
@@ -2400,53 +4702,55 @@
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4">
-        <v>440.61</v>
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C6" t="str" cm="1">
+        <f t="array" aca="1" ref="C6" ca="1">_FV(B6,"Ticker symbol",TRUE)</f>
+        <v>TSM</v>
+      </c>
+      <c r="D6" s="4" cm="1">
+        <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Price")</f>
+        <v>434.11</v>
       </c>
       <c r="E6" s="6">
-        <f>+D6*H6/5</f>
-        <v>2285091.5819999999</v>
+        <f ca="1">+D6*H6/5</f>
+        <v>2251381.2820000001</v>
       </c>
       <c r="F6" s="6">
-        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
+        <f>([2]Main!$J$7-[2]Main!$J$8)/FX!C5</f>
         <v>-87685.151609878085</v>
       </c>
       <c r="G6" s="6">
-        <f>+E6-F6</f>
-        <v>2372776.733609878</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2339066.4336098782</v>
       </c>
       <c r="H6" s="6">
-        <f>+[3]Main!$J$4</f>
+        <f>+[2]Main!$J$4</f>
         <v>25931</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J6" s="10">
         <v>45652</v>
       </c>
-      <c r="L6" s="20">
-        <f>($G6/$H6)/R6*5</f>
-        <v>43.040206847695082</v>
-      </c>
-      <c r="M6" s="21">
-        <f>($G6/$H6)/S6*5</f>
-        <v>29.290486478296977</v>
-      </c>
-      <c r="N6" s="21">
-        <f>($G6/$H6)/T6*5</f>
-        <v>23.378507858507859</v>
-      </c>
-      <c r="Q6" s="18">
+      <c r="L6" s="19">
+        <f ca="1">($G6/$H6)/R6*5</f>
+        <v>42.428729895672504</v>
+      </c>
+      <c r="M6" s="20">
+        <f ca="1">($G6/$H6)/S6*5</f>
+        <v>28.874353315684942</v>
+      </c>
+      <c r="N6" s="20">
+        <f ca="1">($G6/$H6)/T6*5</f>
+        <v>23.04636682631573</v>
+      </c>
+      <c r="Q6" s="17">
         <v>7.04</v>
       </c>
       <c r="R6">
@@ -2465,14 +4769,14 @@
       <c r="AA6" s="13"/>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>46</v>
+      <c r="A7" t="s">
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>16</v>
       </c>
       <c r="D7" s="4">
         <v>2375</v>
@@ -2482,15 +4786,15 @@
         <v>1884520.3488372094</v>
       </c>
       <c r="F7" s="6">
-        <f>([3]Main!$J$7-[3]Main!$J$8)/FX!C5</f>
+        <f>([2]Main!$J$7-[2]Main!$J$8)/FX!C5</f>
         <v>-87685.151609878085</v>
       </c>
       <c r="G7" s="6">
-        <f>+E7-F7</f>
+        <f t="shared" si="0"/>
         <v>1972205.5004470875</v>
       </c>
       <c r="H7" s="6">
-        <f>+[3]Main!$J$4</f>
+        <f>+[2]Main!$J$4</f>
         <v>25931</v>
       </c>
       <c r="I7" s="3" t="str">
@@ -2508,54 +4812,56 @@
       <c r="AA7" s="13"/>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4">
-        <v>394.27</v>
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="e" vm="3">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" t="str" cm="1">
+        <f t="array" aca="1" ref="C8" ca="1">_FV(B8,"Ticker symbol",TRUE)</f>
+        <v>AVGO</v>
+      </c>
+      <c r="D8" s="4" cm="1">
+        <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Price")</f>
+        <v>399.97</v>
       </c>
       <c r="E8" s="6">
-        <f>+D8*H8</f>
-        <v>1927191.76</v>
+        <f ca="1">+D8*H8</f>
+        <v>1955053.36</v>
       </c>
       <c r="F8" s="6">
-        <f>+[2]Main!$J$5-[2]Main!$J$6</f>
+        <f>+[3]Main!$J$5-[3]Main!$J$6</f>
         <v>-51883</v>
       </c>
       <c r="G8" s="6">
-        <f>+E8-F8</f>
-        <v>1979074.76</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>2006936.36</v>
       </c>
       <c r="H8" s="6">
-        <f>+[2]Main!$J$3</f>
+        <f>+[3]Main!$J$3</f>
         <v>4888</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="J8" s="10">
         <v>45722</v>
       </c>
-      <c r="L8" s="20">
-        <f>($G8/$H8)/R8</f>
-        <v>84.881417547615868</v>
-      </c>
-      <c r="M8" s="21">
-        <f>($G8/$H8)/S8</f>
-        <v>35.767169761672051</v>
-      </c>
-      <c r="N8" s="21">
-        <f>($G8/$H8)/T8</f>
-        <v>22.506079027355625</v>
-      </c>
-      <c r="O8" s="21"/>
-      <c r="Q8" s="18">
+      <c r="L8" s="19">
+        <f t="shared" ref="L8:N10" ca="1" si="1">($G8/$H8)/R8</f>
+        <v>86.076386101075002</v>
+      </c>
+      <c r="M8" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>36.270703330576652</v>
+      </c>
+      <c r="N8" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>22.822921717739174</v>
+      </c>
+      <c r="O8" s="20"/>
+      <c r="Q8" s="17">
         <v>1.23</v>
       </c>
       <c r="R8">
@@ -2575,1133 +4881,1113 @@
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" t="s">
-        <v>14</v>
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D9" s="6">
-        <v>199400</v>
+        <v>277500</v>
       </c>
       <c r="E9" s="6">
-        <f>1270340000/KRW</f>
-        <v>875040.46840020665</v>
+        <f>+D9*H9/KRW</f>
+        <v>1291958.0450318581</v>
+      </c>
+      <c r="F9" s="6">
+        <f>+([4]Main!$K$5-[4]Main!$K$6)/KRW*1000</f>
+        <v>119758.15395212676</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="0"/>
+        <v>1172199.8910797313</v>
+      </c>
+      <c r="H9" s="6">
+        <f>+[4]Main!$K$3</f>
+        <v>6758.9192499999999</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J9" s="10">
+        <v>46211</v>
       </c>
       <c r="Z9" s="13"/>
       <c r="AA9" s="13"/>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="e" vm="4">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" cm="1">
+        <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Price")</f>
+        <v>557.89</v>
+      </c>
+      <c r="E10" s="6">
+        <f t="shared" ref="E10:E16" ca="1" si="2">+D10*H10</f>
+        <v>915497.49</v>
+      </c>
+      <c r="F10" s="6">
+        <f>+[5]Main!$M$5-[5]Main!$M$6</f>
+        <v>4023</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>911474.49</v>
+      </c>
+      <c r="H10" s="6">
+        <f>+[5]Main!$M$3</f>
+        <v>1641</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="J10" s="10">
+        <v>45939</v>
+      </c>
+      <c r="K10">
+        <v>1969</v>
+      </c>
+      <c r="L10" s="19">
+        <f t="shared" ca="1" si="1"/>
+        <v>209.5994136111207</v>
+      </c>
+      <c r="M10" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>81.085904535689025</v>
+      </c>
+      <c r="N10" s="20">
+        <f t="shared" ca="1" si="1"/>
+        <v>49.504317831503549</v>
+      </c>
+      <c r="O10" s="20"/>
+      <c r="Q10" s="21">
+        <v>1</v>
+      </c>
+      <c r="R10" s="2">
+        <v>2.65</v>
+      </c>
+      <c r="S10" s="2">
+        <v>6.85</v>
+      </c>
+      <c r="T10" s="2">
+        <v>11.22</v>
+      </c>
+      <c r="Z10" s="13">
+        <v>1291258</v>
+      </c>
+      <c r="AA10" s="13">
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="1" t="e" vm="5">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C11" t="str" cm="1">
+        <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Ticker symbol",TRUE)</f>
+        <v>INTC</v>
+      </c>
+      <c r="D11" s="4" cm="1">
+        <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Price")</f>
+        <v>109.84</v>
+      </c>
+      <c r="E11" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>552055.84</v>
+      </c>
+      <c r="F11" s="6">
+        <f>+[6]Main!$L$5-[6]Main!$L$6</f>
+        <v>-6951</v>
+      </c>
+      <c r="G11" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>559006.84</v>
+      </c>
+      <c r="H11" s="6">
+        <f>+[6]Main!$L$3</f>
+        <v>5026</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J11" s="10">
+        <v>46198</v>
+      </c>
+      <c r="L11" s="19">
+        <f t="shared" ref="L11:N11" ca="1" si="3">($G11/$H11)/R11</f>
+        <v>-1853.7168059424328</v>
+      </c>
+      <c r="M11" s="20">
+        <f t="shared" ca="1" si="3"/>
+        <v>106.94520034283265</v>
+      </c>
+      <c r="N11" s="20">
+        <f t="shared" ca="1" si="3"/>
+        <v>75.661910446629904</v>
+      </c>
+      <c r="Q11" s="17">
+        <v>-4.38</v>
+      </c>
+      <c r="R11">
+        <v>-0.06</v>
+      </c>
+      <c r="S11">
+        <v>1.04</v>
+      </c>
+      <c r="T11">
+        <v>1.47</v>
+      </c>
+      <c r="Z11" s="13">
+        <v>1000000</v>
+      </c>
+      <c r="AA11" s="13">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="1" t="e" vm="6">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="4" cm="1">
+        <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Price")</f>
+        <v>323.39</v>
+      </c>
+      <c r="E12" s="6">
+        <f ca="1">+D12*H12</f>
+        <v>337779.89517847996</v>
+      </c>
+      <c r="F12" s="6">
+        <f>+[25]Main!$L$5-[25]Main!$L$6</f>
+        <v>3664</v>
+      </c>
+      <c r="G12" s="6">
+        <f ca="1">+E12-F12</f>
+        <v>334115.89517847996</v>
+      </c>
+      <c r="H12" s="6">
+        <f>+[25]Main!$L$3</f>
+        <v>1044.497032</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA12" s="13">
+        <v>1350000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="1" t="e" vm="7">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" cm="1">
+        <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Price")</f>
+        <v>311.45999999999998</v>
+      </c>
+      <c r="E13" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>282672.28541951999</v>
+      </c>
+      <c r="F13" s="6">
+        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
+        <v>1153</v>
+      </c>
+      <c r="G13" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>281519.28541951999</v>
+      </c>
+      <c r="H13" s="6">
+        <f>+[7]Main!$K$3</f>
+        <v>907.57171200000005</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J13" s="10">
+        <v>44946</v>
+      </c>
+      <c r="AA13" s="13">
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="e" vm="8">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="4" cm="1">
+        <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Price")</f>
+        <v>189.16</v>
+      </c>
+      <c r="E14" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>210724.24</v>
+      </c>
+      <c r="F14" s="6">
+        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
+        <v>-1522</v>
+      </c>
+      <c r="G14" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>212246.24</v>
+      </c>
+      <c r="H14" s="6">
+        <f>+[8]Main!$L$3</f>
+        <v>1114</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J14" s="10">
+        <v>45581</v>
+      </c>
+      <c r="Z14" s="13">
+        <v>1350000</v>
+      </c>
+      <c r="AA14" s="13">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="1" t="e" vm="9">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="4" cm="1">
+        <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Price")</f>
+        <v>235.81</v>
+      </c>
+      <c r="E15" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>206286.58799999999</v>
+      </c>
+      <c r="F15" s="6">
+        <f>+[9]Main!$H$5-[9]Main!$H$6</f>
+        <v>-1117.7000000000003</v>
+      </c>
+      <c r="G15" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>207404.288</v>
+      </c>
+      <c r="H15" s="6">
+        <f>[9]Main!$H$3</f>
+        <v>874.8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J15" s="10">
+        <v>46203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="4" cm="1">
+        <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Price")</f>
+        <v>395.65</v>
+      </c>
+      <c r="E16" s="6">
+        <f t="shared" ca="1" si="2"/>
+        <v>192715.98737599998</v>
+      </c>
+      <c r="F16" s="6">
+        <f>+[10]Main!$J$5-[10]Main!$J$6</f>
+        <v>-4695.3429999999998</v>
+      </c>
+      <c r="G16" s="6">
+        <f t="shared" ca="1" si="0"/>
+        <v>197411.33037599997</v>
+      </c>
+      <c r="H16" s="6">
+        <f>+[10]Main!$J$3</f>
+        <v>487.08704</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J16" s="10">
+        <v>46211</v>
+      </c>
+      <c r="AA16" s="13">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" s="1" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="4" cm="1">
+        <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Price")</f>
+        <v>3925</v>
+      </c>
+      <c r="E17" s="6">
+        <f ca="1">+D17*H17/FX!C5</f>
+        <v>196679.43107221008</v>
+      </c>
+      <c r="F17" s="6">
+        <f>([24]Main!$K$5-[24]Main!$K$6)/FX!C5</f>
+        <v>9981.0878399499852</v>
+      </c>
+      <c r="G17" s="6">
+        <f ca="1">+E17-F17</f>
+        <v>186698.34323226009</v>
+      </c>
+      <c r="H17" s="6">
+        <f>+[24]Main!$K$3</f>
+        <v>1603</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J17" s="10">
+        <v>46213</v>
+      </c>
+      <c r="K17">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="4">
-        <v>1348</v>
-      </c>
-      <c r="E10" s="6">
-        <f>+D10*H10</f>
-        <v>530438</v>
-      </c>
-      <c r="F10" s="6">
-        <f>+[4]Main!$L$5-[4]Main!$L$6</f>
-        <v>1413.0000000000009</v>
-      </c>
-      <c r="G10" s="6">
-        <f>+E10-F10</f>
-        <v>529025</v>
-      </c>
-      <c r="H10" s="6">
-        <f>+[4]Main!$L$3</f>
-        <v>393.5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J10" s="10">
-        <v>45581</v>
-      </c>
-      <c r="Z10" s="13"/>
-      <c r="AA10" s="13">
-        <v>784000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1007000</v>
-      </c>
-      <c r="E11" s="6">
-        <f>649720/KRW*1000</f>
-        <v>447542.62097468576</v>
-      </c>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="4">
-        <v>587</v>
-      </c>
-      <c r="E12" s="6">
-        <f>+D12*H12</f>
-        <v>650889.85836199997</v>
-      </c>
-      <c r="F12" s="6">
-        <f>+[5]Main!$J$5-[5]Main!$J$6</f>
-        <v>-4104</v>
-      </c>
-      <c r="G12" s="6">
-        <f>+E12-F12</f>
-        <v>654993.85836199997</v>
-      </c>
-      <c r="H12" s="6">
-        <f>+[5]Main!$J$3</f>
-        <v>1108.841326</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J12" s="10">
-        <v>45554</v>
-      </c>
-      <c r="L12" s="20">
-        <f t="shared" ref="L12:N14" si="0">($G12/$H12)/R12</f>
-        <v>77.826239888750877</v>
-      </c>
-      <c r="M12" s="21">
-        <f t="shared" si="0"/>
-        <v>10.345029085037114</v>
-      </c>
-      <c r="N12" s="21">
-        <f t="shared" si="0"/>
-        <v>6.1756524909108119</v>
-      </c>
-      <c r="Q12" s="22">
-        <v>0.7</v>
-      </c>
-      <c r="R12" s="2">
-        <v>7.59</v>
-      </c>
-      <c r="S12" s="2">
-        <v>57.1</v>
-      </c>
-      <c r="T12" s="2">
-        <v>95.65</v>
-      </c>
-      <c r="Z12" s="13">
-        <v>1446185</v>
-      </c>
-      <c r="AA12" s="13">
-        <v>749323</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4">
-        <v>200</v>
-      </c>
-      <c r="E13" s="6">
-        <f>+D13*H13</f>
-        <v>328200</v>
-      </c>
-      <c r="F13" s="6">
-        <f>+[6]Main!$M$5-[6]Main!$M$6</f>
-        <v>4023</v>
-      </c>
-      <c r="G13" s="6">
-        <f>+E13-F13</f>
-        <v>324177</v>
-      </c>
-      <c r="H13" s="6">
-        <f>+[6]Main!$M$3</f>
-        <v>1641</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="J13" s="10">
-        <v>45939</v>
-      </c>
-      <c r="K13">
-        <v>1969</v>
-      </c>
-      <c r="L13" s="20">
-        <f t="shared" si="0"/>
-        <v>74.546583422441444</v>
-      </c>
-      <c r="M13" s="21">
-        <f t="shared" si="0"/>
-        <v>28.839189207221875</v>
-      </c>
-      <c r="N13" s="21">
-        <f t="shared" si="0"/>
-        <v>17.606813375175562</v>
-      </c>
-      <c r="O13" s="21"/>
-      <c r="Q13" s="22">
-        <v>1</v>
-      </c>
-      <c r="R13" s="2">
-        <v>2.65</v>
-      </c>
-      <c r="S13" s="2">
-        <v>6.85</v>
-      </c>
-      <c r="T13" s="2">
-        <v>11.22</v>
-      </c>
-      <c r="Z13" s="13">
-        <v>1291258</v>
-      </c>
-      <c r="AA13" s="13">
-        <v>820000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="4">
-        <v>360</v>
-      </c>
-      <c r="E14" s="6">
-        <v>267520</v>
-      </c>
-      <c r="F14" s="6">
-        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
-        <v>6926</v>
-      </c>
-      <c r="G14" s="6">
-        <f>+E14-F14</f>
-        <v>260594</v>
-      </c>
-      <c r="H14" s="6">
-        <f>+[7]Main!$K$3</f>
-        <v>799</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="L14" s="20">
-        <f t="shared" si="0"/>
-        <v>37.661684495920134</v>
-      </c>
-      <c r="M14" s="21">
-        <f t="shared" si="0"/>
-        <v>29.462528250647548</v>
-      </c>
-      <c r="N14" s="21">
-        <f t="shared" si="0"/>
-        <v>23.082108119934066</v>
-      </c>
-      <c r="Q14" s="18">
-        <v>8.61</v>
-      </c>
-      <c r="R14">
-        <v>8.66</v>
-      </c>
-      <c r="S14">
-        <v>11.07</v>
-      </c>
-      <c r="T14">
-        <v>14.13</v>
-      </c>
-      <c r="Z14" s="13">
-        <v>1030000</v>
-      </c>
-      <c r="AA14" s="13">
-        <v>665000</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" s="4">
-        <v>226</v>
-      </c>
-      <c r="E15" s="6">
-        <v>260830</v>
-      </c>
-      <c r="G15" s="6">
-        <f>E15-F15</f>
-        <v>260830</v>
-      </c>
-      <c r="J15" s="10">
-        <v>46089</v>
-      </c>
-      <c r="K15">
-        <v>1980</v>
-      </c>
-      <c r="W15" t="s">
-        <v>263</v>
-      </c>
-      <c r="X15" t="s">
-        <v>264</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z15" s="13">
-        <v>1236539</v>
-      </c>
-      <c r="AA15" s="13">
-        <v>714596</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="4">
-        <v>45.22</v>
-      </c>
-      <c r="E16" s="6">
-        <f>+D16*H16</f>
-        <v>204891.82</v>
-      </c>
-      <c r="F16" s="6">
-        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
-        <v>-6951</v>
-      </c>
-      <c r="G16" s="6">
-        <f>+E16-F16</f>
-        <v>211842.82</v>
-      </c>
-      <c r="H16" s="6">
-        <f>+[8]Main!$L$3</f>
-        <v>4531</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J16" s="10">
-        <v>45507</v>
-      </c>
-      <c r="L16" s="20">
-        <f>($G16/$H16)/R16</f>
-        <v>-779.2349738836167</v>
-      </c>
-      <c r="M16" s="21">
-        <f>($G16/$H16)/S16</f>
-        <v>44.95586387790096</v>
-      </c>
-      <c r="N16" s="21">
-        <f>($G16/$H16)/T16</f>
-        <v>31.805509138106803</v>
-      </c>
-      <c r="Q16" s="18">
-        <v>-4.38</v>
-      </c>
-      <c r="R16">
-        <v>-0.06</v>
-      </c>
-      <c r="S16">
-        <v>1.04</v>
-      </c>
-      <c r="T16">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" s="13">
-        <v>1000000</v>
-      </c>
-      <c r="AA16" s="13">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="4">
-        <v>132</v>
-      </c>
-      <c r="E17" s="6">
-        <f>+D17*H17</f>
-        <v>147048</v>
-      </c>
-      <c r="F17" s="6">
-        <f>+[9]Main!$L$5-[9]Main!$L$6</f>
-        <v>-1522</v>
-      </c>
-      <c r="G17" s="6">
-        <f>+E17-F17</f>
-        <v>148570</v>
-      </c>
-      <c r="H17" s="6">
-        <f>+[9]Main!$L$3</f>
-        <v>1114</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J17" s="10">
-        <v>45581</v>
-      </c>
-      <c r="Z17" s="13">
-        <v>1350000</v>
-      </c>
-      <c r="AA17" s="13">
-        <v>800000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1462</v>
+      <c r="D18" s="6">
+        <v>41720</v>
       </c>
       <c r="E18" s="6">
-        <v>182590</v>
-      </c>
-      <c r="AA18" s="13">
-        <v>750000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D19" s="4">
-        <v>310</v>
-      </c>
-      <c r="E19" s="6">
-        <v>160070</v>
-      </c>
-      <c r="AA19" s="13">
-        <v>700000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
-        <v>10</v>
-      </c>
-      <c r="D20" s="4">
-        <v>190</v>
-      </c>
-      <c r="E20" s="6">
-        <f>+D20*H20</f>
-        <v>172438.62528000001</v>
-      </c>
-      <c r="F20" s="6">
-        <f>+[10]Main!$K$5-[10]Main!$K$6</f>
-        <v>1153</v>
-      </c>
-      <c r="G20" s="6">
-        <f>+E20-F20</f>
-        <v>171285.62528000001</v>
-      </c>
-      <c r="H20" s="6">
-        <f>+[10]Main!$K$3</f>
-        <v>907.57171200000005</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J20" s="10">
-        <v>44946</v>
-      </c>
-      <c r="AA20" s="13">
-        <v>830000</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
-      <c r="C21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D21" s="4">
-        <v>133</v>
-      </c>
-      <c r="E21" s="6">
-        <v>126470</v>
-      </c>
-      <c r="AA21" s="13">
-        <v>1350000</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D22" s="6">
-        <v>41720</v>
-      </c>
-      <c r="E22" s="6">
         <f>124700</f>
         <v>124700</v>
       </c>
     </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19" s="6">
+        <v>25535</v>
+      </c>
+      <c r="E19" s="6">
+        <v>119990</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>51</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="6">
+        <v>6226</v>
+      </c>
+      <c r="E20" s="6">
+        <v>73070</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="4">
+        <v>209.6</v>
+      </c>
+      <c r="E21" s="6">
+        <v>52970</v>
+      </c>
+      <c r="AA21">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" s="3">
+        <v>67.91</v>
+      </c>
+      <c r="E22" s="6">
+        <v>36740</v>
+      </c>
+      <c r="AA22">
+        <v>280918</v>
+      </c>
+    </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>46</v>
-      </c>
       <c r="B23" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>200</v>
-      </c>
-      <c r="D23" s="6">
-        <v>25535</v>
+        <v>38</v>
+      </c>
+      <c r="D23" s="3">
+        <v>17.760000000000002</v>
       </c>
       <c r="E23" s="6">
-        <v>119990</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24" s="4">
-        <v>1775</v>
-      </c>
-      <c r="E24" s="6">
-        <f>2830000/FX!$C$2</f>
-        <v>86597.307221542229</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
-        <v>61</v>
-      </c>
-      <c r="C25" t="s">
-        <v>62</v>
-      </c>
-      <c r="D25" s="6">
-        <v>6226</v>
-      </c>
-      <c r="E25" s="6">
-        <v>73070</v>
-      </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="4">
-        <v>209.6</v>
-      </c>
-      <c r="E26" s="6">
-        <v>52970</v>
-      </c>
-      <c r="AA26">
-        <v>580000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" t="s">
-        <v>82</v>
-      </c>
-      <c r="D27" s="3">
-        <v>67.91</v>
-      </c>
-      <c r="E27" s="6">
-        <v>36740</v>
-      </c>
-      <c r="AA27">
-        <v>280918</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" t="s">
-        <v>48</v>
-      </c>
-      <c r="D28" s="3">
-        <v>17.760000000000002</v>
-      </c>
-      <c r="E28" s="6">
         <f>134230/CNY</f>
         <v>19175.714285714286</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C29" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" s="4">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" s="4">
         <v>20.65</v>
       </c>
-      <c r="E29" s="6">
-        <f>+D29*H29</f>
+      <c r="E24" s="6">
+        <f>+D24*H24</f>
         <v>13216</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F24" s="6">
         <f>+[11]Main!$M$5-[11]Main!$M$6</f>
         <v>-504</v>
       </c>
-      <c r="G29" s="6">
-        <f>+E29-F29</f>
+      <c r="G24" s="6">
+        <f>+E24-F24</f>
         <v>13720</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H24" s="6">
         <f>+[11]Main!$M$3</f>
         <v>640</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J29" s="10">
+      <c r="I24" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J24" s="10">
         <v>45560</v>
       </c>
     </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>187</v>
+      </c>
+      <c r="C25" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>193</v>
+      </c>
+      <c r="C26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>306</v>
+      </c>
+      <c r="C29" t="s">
+        <v>307</v>
+      </c>
+    </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>46</v>
+      <c r="A30" t="s">
+        <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>201</v>
+        <v>76</v>
       </c>
       <c r="C30" t="s">
-        <v>202</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>46</v>
-      </c>
       <c r="B31" t="s">
+        <v>95</v>
+      </c>
+      <c r="C31" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>195</v>
+      </c>
+      <c r="C32" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="3">
+        <v>32.51</v>
+      </c>
+      <c r="E33" s="6">
+        <v>28890</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" t="s">
+        <v>197</v>
+      </c>
+      <c r="C34" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>205</v>
+      </c>
+      <c r="C35" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>316</v>
+      </c>
+      <c r="C36" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>234</v>
+      </c>
+      <c r="C37" t="s">
+        <v>235</v>
+      </c>
+      <c r="D37" s="3">
+        <v>118.63</v>
+      </c>
+      <c r="AA37">
+        <v>615000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
         <v>207</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C38" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B33" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" t="s">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
         <v>209</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C39" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="3">
-        <v>32.51</v>
-      </c>
-      <c r="E35" s="6">
-        <v>28890</v>
-      </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B36" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B37" t="s">
-        <v>219</v>
-      </c>
-      <c r="C37" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A38" s="14"/>
-      <c r="B38" t="s">
-        <v>280</v>
-      </c>
-      <c r="C38" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" t="s">
-        <v>221</v>
-      </c>
-      <c r="C39" t="s">
-        <v>222</v>
+      <c r="D39" s="4">
+        <v>717</v>
+      </c>
+      <c r="E39" s="6">
+        <v>41130</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>46</v>
+      <c r="A40" t="s">
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>223</v>
+        <v>314</v>
       </c>
       <c r="C40" t="s">
-        <v>224</v>
-      </c>
-      <c r="D40" s="4">
-        <v>717</v>
-      </c>
-      <c r="E40" s="6">
-        <v>41130</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6"/>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>46</v>
+      <c r="A41" t="s">
+        <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>239</v>
+        <v>225</v>
       </c>
       <c r="C41" t="s">
-        <v>240</v>
+        <v>226</v>
       </c>
       <c r="D41" s="4">
         <v>353.5</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A42" s="14"/>
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
-      </c>
-      <c r="D42" s="4">
+        <v>292</v>
+      </c>
+      <c r="D42" s="4"/>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>297</v>
+      </c>
+      <c r="C43" t="s">
+        <v>298</v>
+      </c>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" t="s">
+        <v>293</v>
+      </c>
+      <c r="C44" t="s">
+        <v>294</v>
+      </c>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" t="s">
+        <v>308</v>
+      </c>
+      <c r="C45" t="s">
+        <v>309</v>
+      </c>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>332</v>
+      </c>
+      <c r="C46" t="s">
+        <v>333</v>
+      </c>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>328</v>
+      </c>
+      <c r="C47" t="s">
+        <v>329</v>
+      </c>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s">
+        <v>310</v>
+      </c>
+      <c r="C48" t="s">
+        <v>311</v>
+      </c>
+      <c r="D48" s="4"/>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>242</v>
+      </c>
+      <c r="C49" t="s">
+        <v>241</v>
+      </c>
+      <c r="D49" s="4">
         <v>3270</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E49" s="6">
         <f>264920/FX!$C$5</f>
         <v>8281.337918099407</v>
       </c>
     </row>
-    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B43" t="s">
-        <v>241</v>
-      </c>
-      <c r="C43" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="14"/>
-      <c r="B44" t="s">
-        <v>257</v>
-      </c>
-      <c r="C44" t="s">
-        <v>258</v>
-      </c>
-      <c r="D44" s="4">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>227</v>
+      </c>
+      <c r="C50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>243</v>
+      </c>
+      <c r="C51" t="s">
+        <v>244</v>
+      </c>
+      <c r="D51" s="4">
         <v>2355</v>
       </c>
-      <c r="E44" s="6">
+      <c r="E51" s="6">
         <f>315600/FX!$C$5</f>
         <v>9865.5829946858394</v>
       </c>
     </row>
-    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A45" s="14"/>
-      <c r="B45" t="s">
-        <v>259</v>
-      </c>
-      <c r="C45" t="s">
-        <v>260</v>
-      </c>
-      <c r="D45" s="4">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="s">
+        <v>346</v>
+      </c>
+      <c r="C52" t="s">
+        <v>347</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6"/>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>359</v>
+      </c>
+      <c r="C53" t="s">
+        <v>360</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6"/>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>361</v>
+      </c>
+      <c r="C54" t="s">
+        <v>362</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6"/>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" t="s">
+        <v>246</v>
+      </c>
+      <c r="D55" s="4">
         <v>159</v>
       </c>
-      <c r="E45" s="6">
+      <c r="E55" s="6">
         <f>41430/FX!$C$5</f>
         <v>1295.0922163175994</v>
       </c>
     </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>46</v>
-      </c>
-      <c r="B46" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" t="s">
-        <v>100</v>
-      </c>
-      <c r="D46" s="4">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="3">
-        <v>47.15</v>
-      </c>
-      <c r="E47" s="6">
-        <v>26330</v>
-      </c>
-    </row>
-    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" t="s">
-        <v>109</v>
-      </c>
-      <c r="C48" t="s">
-        <v>110</v>
-      </c>
-      <c r="D48" s="3">
-        <v>60.46</v>
-      </c>
-      <c r="E48" s="6">
-        <v>23800</v>
-      </c>
-      <c r="AA48">
-        <v>600000</v>
-      </c>
-    </row>
-    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B49" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C49" t="s">
-        <v>270</v>
-      </c>
-      <c r="D49" s="4">
-        <v>1222</v>
-      </c>
-      <c r="E49" s="6">
-        <f>+D49*H49</f>
-        <v>180965.68427599999</v>
-      </c>
-      <c r="F49" s="6">
-        <f>+[12]Main!$L$5-[12]Main!$L$6</f>
-        <v>3735</v>
-      </c>
-      <c r="G49" s="6">
-        <f>+E49-F49</f>
-        <v>177230.68427599999</v>
-      </c>
-      <c r="H49" s="6">
-        <f>+[12]Main!$L$3</f>
-        <v>148.08975799999999</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="J49" s="10">
-        <v>46146</v>
-      </c>
-      <c r="AA49">
-        <v>625000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>46</v>
-      </c>
-      <c r="B50" t="s">
-        <v>248</v>
-      </c>
-      <c r="C50" t="s">
-        <v>249</v>
-      </c>
-      <c r="D50" s="3">
-        <v>118.63</v>
-      </c>
-      <c r="AA50">
-        <v>615000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" t="s">
-        <v>111</v>
-      </c>
-      <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" s="4">
-        <v>61.5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="C52" t="s">
-        <v>135</v>
-      </c>
-      <c r="D52" s="4">
-        <v>112</v>
-      </c>
-      <c r="E52" s="6">
-        <f>+D52*H52</f>
-        <v>15167.281808</v>
-      </c>
-      <c r="F52" s="6">
-        <f>+[13]Main!$J$5-[13]Main!$J$6</f>
-        <v>446.97199999999998</v>
-      </c>
-      <c r="G52" s="6">
-        <f>+E52-F52</f>
-        <v>14720.309808</v>
-      </c>
-      <c r="H52" s="6">
-        <f>+[13]Main!$J$3</f>
-        <v>135.42215899999999</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J52" s="10">
-        <v>45561</v>
-      </c>
-    </row>
-    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B53" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="C53" t="s">
-        <v>137</v>
-      </c>
-      <c r="D53" s="4">
-        <v>13</v>
-      </c>
-      <c r="E53" s="6">
-        <f>+D53*H53</f>
-        <v>10543.625651</v>
-      </c>
-      <c r="F53" s="6">
-        <f>+[14]Main!$K$5-[14]Main!$K$6</f>
-        <v>1203</v>
-      </c>
-      <c r="G53" s="6">
-        <f>+E53-F53</f>
-        <v>9340.6256510000003</v>
-      </c>
-      <c r="H53" s="6">
-        <f>+[14]Main!$K$3</f>
-        <v>811.04812700000002</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J53" s="10">
-        <v>45561</v>
-      </c>
-      <c r="AA53">
-        <v>752335</v>
-      </c>
-    </row>
-    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B54" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C54" t="s">
-        <v>244</v>
-      </c>
-      <c r="D54" s="4">
-        <v>23.19</v>
-      </c>
-      <c r="E54" s="6">
-        <f>+D54*H54</f>
-        <v>1481.01784776</v>
-      </c>
-      <c r="F54" s="6">
-        <f>+[15]Main!$J$5-[15]Main!$J$6</f>
-        <v>295.214</v>
-      </c>
-      <c r="G54" s="6">
-        <f>+E54-F54</f>
-        <v>1185.8038477600001</v>
-      </c>
-      <c r="H54" s="6">
-        <f>+[15]Main!$J$3</f>
-        <v>63.864503999999997</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J54" s="10">
-        <v>45796</v>
-      </c>
-    </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>63</v>
+        <v>86</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
+      </c>
+      <c r="D56" s="4">
+        <v>9.8000000000000007</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>36</v>
+      </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>92</v>
+      </c>
+      <c r="C57" t="s">
+        <v>93</v>
+      </c>
+      <c r="D57" s="3">
+        <v>47.15</v>
+      </c>
+      <c r="E57" s="6">
+        <v>26330</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>36</v>
+      </c>
       <c r="B58" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="C58" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="3">
+        <v>60.46</v>
+      </c>
+      <c r="E58" s="6">
+        <v>23800</v>
+      </c>
+      <c r="AA58">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>36</v>
+      </c>
+      <c r="B59" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" t="s">
+        <v>99</v>
+      </c>
+      <c r="D59" s="4">
+        <v>61.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" t="s">
+        <v>121</v>
+      </c>
+      <c r="D60" s="4">
+        <v>112</v>
+      </c>
+      <c r="E60" s="6">
+        <f>+D60*H60</f>
+        <v>15167.281808</v>
+      </c>
+      <c r="F60" s="6">
+        <f>+[12]Main!$J$5-[12]Main!$J$6</f>
+        <v>446.97199999999998</v>
+      </c>
+      <c r="G60" s="6">
+        <f>+E60-F60</f>
+        <v>14720.309808</v>
+      </c>
+      <c r="H60" s="6">
+        <f>+[12]Main!$J$3</f>
+        <v>135.42215899999999</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J60" s="10">
+        <v>45561</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" t="s">
+        <v>123</v>
+      </c>
+      <c r="D61" s="4">
+        <v>13</v>
+      </c>
+      <c r="E61" s="6">
+        <f>+D61*H61</f>
+        <v>10543.625651</v>
+      </c>
+      <c r="F61" s="6">
+        <f>+[13]Main!$K$5-[13]Main!$K$6</f>
+        <v>1203</v>
+      </c>
+      <c r="G61" s="6">
+        <f>+E61-F61</f>
+        <v>9340.6256510000003</v>
+      </c>
+      <c r="H61" s="6">
+        <f>+[13]Main!$K$3</f>
+        <v>811.04812700000002</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J61" s="10">
+        <v>45561</v>
+      </c>
+      <c r="AA61">
+        <v>752335</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B62" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="C62" t="s">
+        <v>230</v>
+      </c>
+      <c r="D62" s="4">
+        <v>42.96</v>
+      </c>
+      <c r="E62" s="6">
+        <f>+D62*H62</f>
+        <v>2743.6190918399998</v>
+      </c>
+      <c r="F62" s="6">
+        <f>+[14]Main!$J$5-[14]Main!$J$6</f>
+        <v>295.214</v>
+      </c>
+      <c r="G62" s="6">
+        <f>+E62-F62</f>
+        <v>2448.4050918399998</v>
+      </c>
+      <c r="H62" s="6">
+        <f>+[14]Main!$J$3</f>
+        <v>63.864503999999997</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J62" s="10">
+        <v>45796</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B64" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B65" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>36</v>
+      </c>
+      <c r="B66" t="s">
+        <v>95</v>
+      </c>
+      <c r="C66" t="s">
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -3710,29 +5996,780 @@
     <mergeCell ref="Q3:V3"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1" xr:uid="{82B60337-F6F7-4A89-BE21-94E4E4FAE923}"/>
-    <hyperlink ref="B20" r:id="rId2" xr:uid="{89BFBE39-15FE-4D88-BD35-419556A195F8}"/>
-    <hyperlink ref="B16" r:id="rId3" xr:uid="{ACBF0F19-D83E-41D4-B3AD-01439A0CCE2D}"/>
-    <hyperlink ref="B13" r:id="rId4" xr:uid="{0B4AADBB-7802-4155-9477-7B8867856D77}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{D5C26AF1-ADC4-4E03-9D8B-12F3C24C324B}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{DD4F0CC9-D485-4053-9B41-DE6F39511946}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{05815C98-BE17-4CF3-942D-C5BFAB80DA80}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{37FE970B-81E9-4AF7-98E1-474982CC16D7}"/>
-    <hyperlink ref="B29" r:id="rId9" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
-    <hyperlink ref="B52" r:id="rId10" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
-    <hyperlink ref="B53" r:id="rId11" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
-    <hyperlink ref="B17" r:id="rId12" xr:uid="{E7CBB7C3-B2DF-42D5-A84A-8A1B7E26DDB6}"/>
-    <hyperlink ref="B10" r:id="rId13" xr:uid="{3EEE25FB-8581-4AA9-ADEF-37DC0B2F3F4D}"/>
-    <hyperlink ref="B54" r:id="rId14" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
-    <hyperlink ref="B15" r:id="rId15" xr:uid="{0E1B41B2-39E3-482E-80B4-4D069EE9643C}"/>
-    <hyperlink ref="B14" r:id="rId16" xr:uid="{5BA02E53-CE6F-4CB1-A08A-138D1B40007E}"/>
-    <hyperlink ref="B49" r:id="rId17" xr:uid="{336EFAF6-6C79-4F1F-A0B5-C64D94F56B90}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{DD4F0CC9-D485-4053-9B41-DE6F39511946}"/>
+    <hyperlink ref="B24" r:id="rId2" xr:uid="{CF0C3BE9-553F-4E6A-8F72-3B6D86F868FC}"/>
+    <hyperlink ref="B60" r:id="rId3" xr:uid="{35D78F35-BD1B-401F-9830-193EF147D21A}"/>
+    <hyperlink ref="B61" r:id="rId4" xr:uid="{8FC74BE2-2095-4EFE-8F49-C1E00A6EF2C6}"/>
+    <hyperlink ref="B62" r:id="rId5" xr:uid="{3A48277A-E40F-4BB9-B4C3-9290548C0B09}"/>
+    <hyperlink ref="B15" r:id="rId6" display="MRVL.xlsx" xr:uid="{1346A1F9-3F01-40BA-A797-A622F2C17A6A}"/>
+    <hyperlink ref="B13" r:id="rId7" display="TXN.xlsx" xr:uid="{10F4C2CB-9810-4405-A79E-26F565F087F6}"/>
+    <hyperlink ref="B14" r:id="rId8" display="QCOM.xlsx" xr:uid="{DBD42285-D260-40E8-9D57-8F45E1D61BC2}"/>
+    <hyperlink ref="B11" r:id="rId9" display="INTC.xlsx" xr:uid="{EA99702A-557B-4C65-A8FA-275B178299EA}"/>
+    <hyperlink ref="B8" r:id="rId10" display="AVGO.xlsx" xr:uid="{92BA26BA-5ED7-4BD4-9536-704B3CD0F70A}"/>
+    <hyperlink ref="B10" r:id="rId11" display="AMD.xlsx" xr:uid="{EC67840E-18D2-4F0F-A5A8-854E99F5F539}"/>
+    <hyperlink ref="B6" r:id="rId12" display="TSM.xlsx" xr:uid="{66699C44-5CD6-4D6C-A702-88C22BFBCBDD}"/>
+    <hyperlink ref="B5" r:id="rId13" display="NVDA.xlsx" xr:uid="{41959447-08BC-4124-91C7-5621BE11E295}"/>
+    <hyperlink ref="B9" r:id="rId14" xr:uid="{2B90458D-E570-4287-BE8C-6AA1527B1BCB}"/>
+    <hyperlink ref="B12" r:id="rId15" display="ARM.xlsx" xr:uid="{EDFF8EAA-F0C0-4AD9-A9CE-06C5F0CECDD4}"/>
+    <hyperlink ref="B16" r:id="rId16" display="ADI.xlsx" xr:uid="{E9120624-73BC-4C1B-A57B-3C4288B30E7A}"/>
+    <hyperlink ref="B17" r:id="rId17" display="2454 TT MediaTek.xlsx" xr:uid="{0CFD06DE-D7B0-479F-91F4-5C68224B7360}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2C85977-16E5-412D-BE16-996917CEEE32}">
+  <dimension ref="A1:AC10"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="0.1796875" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.81640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="8.7265625" style="3"/>
+    <col min="8" max="8" width="9.54296875" style="3" customWidth="1"/>
+    <col min="9" max="10" width="8.7265625" style="3"/>
+    <col min="11" max="11" width="9.36328125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="8.7265625" style="17"/>
+    <col min="18" max="18" width="8.7265625" style="18"/>
+    <col min="24" max="24" width="8.7265625" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" ht="13" x14ac:dyDescent="0.3">
+      <c r="M2" s="33" t="s">
+        <v>257</v>
+      </c>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="35"/>
+    </row>
+    <row r="3" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="17">
+        <v>2025</v>
+      </c>
+      <c r="N3">
+        <v>2026</v>
+      </c>
+      <c r="O3">
+        <f>+N3+1</f>
+        <v>2027</v>
+      </c>
+      <c r="P3">
+        <f>+O3+1</f>
+        <v>2028</v>
+      </c>
+      <c r="Q3">
+        <f>+P3+1</f>
+        <v>2029</v>
+      </c>
+      <c r="R3" s="18">
+        <v>2030</v>
+      </c>
+      <c r="S3">
+        <v>2025</v>
+      </c>
+      <c r="T3">
+        <v>2026</v>
+      </c>
+      <c r="U3">
+        <v>2027</v>
+      </c>
+      <c r="V3">
+        <f>+U3+1</f>
+        <v>2028</v>
+      </c>
+      <c r="W3">
+        <f>+V3+1</f>
+        <v>2029</v>
+      </c>
+      <c r="X3" s="18">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="6">
+        <v>285000</v>
+      </c>
+      <c r="F4" s="6">
+        <f>+E4*I4/KRW</f>
+        <v>1326875.8300327191</v>
+      </c>
+      <c r="G4" s="6">
+        <f>([4]Main!$K$5-[4]Main!$K$6)/KRW*1000</f>
+        <v>119758.15395212676</v>
+      </c>
+      <c r="H4" s="6">
+        <f>+F4-G4</f>
+        <v>1207117.6760805922</v>
+      </c>
+      <c r="I4" s="6">
+        <f>+[4]Main!$K$3</f>
+        <v>6758.9192499999999</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="K4" s="10">
+        <v>46207</v>
+      </c>
+      <c r="N4" s="29"/>
+      <c r="O4" s="29"/>
+      <c r="P4" s="29"/>
+      <c r="Q4" s="29"/>
+      <c r="S4" s="29"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="4">
+        <v>980</v>
+      </c>
+      <c r="F5" s="6">
+        <f>+E5*I5</f>
+        <v>1122100</v>
+      </c>
+      <c r="G5" s="6">
+        <f>+[15]Main!$J$5-[15]Main!$J$6</f>
+        <v>25303</v>
+      </c>
+      <c r="H5" s="6">
+        <f>+F5-G5</f>
+        <v>1096797</v>
+      </c>
+      <c r="I5" s="6">
+        <f>+[15]Main!$J$3</f>
+        <v>1145</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K5" s="10">
+        <v>46207</v>
+      </c>
+      <c r="L5">
+        <v>1978</v>
+      </c>
+      <c r="M5" s="19">
+        <f>($H5/$I5)/S5</f>
+        <v>1368.4304429195261</v>
+      </c>
+      <c r="N5" s="31">
+        <f>($H5/$I5)/T5</f>
+        <v>126.20570619811174</v>
+      </c>
+      <c r="O5" s="31">
+        <f>($H5/$I5)/U5</f>
+        <v>13.096818567728576</v>
+      </c>
+      <c r="P5" s="31">
+        <f>($H5/$I5)/V5</f>
+        <v>6.2784381598195464</v>
+      </c>
+      <c r="Q5" s="31">
+        <f>($H5/$I5)/W5</f>
+        <v>10.775042857634061</v>
+      </c>
+      <c r="R5" s="32">
+        <f>($H5/$I5)/X5</f>
+        <v>15.314169624998691</v>
+      </c>
+      <c r="S5" s="30">
+        <v>0.7</v>
+      </c>
+      <c r="T5" s="2">
+        <v>7.59</v>
+      </c>
+      <c r="U5" s="2">
+        <v>73.14</v>
+      </c>
+      <c r="V5" s="2">
+        <v>152.57</v>
+      </c>
+      <c r="W5" s="28">
+        <v>88.9</v>
+      </c>
+      <c r="X5" s="18">
+        <v>62.55</v>
+      </c>
+      <c r="AB5" s="13">
+        <v>1446185</v>
+      </c>
+      <c r="AC5" s="13">
+        <v>749323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="C6" t="s">
+        <v>268</v>
+      </c>
+      <c r="D6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="Q6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="AB6" s="13"/>
+      <c r="AC6" s="13"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E7" s="6">
+        <v>1007000</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="Q7" s="29"/>
+      <c r="S7" s="29"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="1" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D8" t="s">
+        <v>256</v>
+      </c>
+      <c r="E8" s="4" cm="1">
+        <f t="array" aca="1" ref="E8" ca="1">_FV(B8,"Price")</f>
+        <v>1915.92</v>
+      </c>
+      <c r="F8" s="6">
+        <f ca="1">+E8*I8</f>
+        <v>283728.12914735998</v>
+      </c>
+      <c r="G8" s="6">
+        <f>+[16]Main!$L$5-[16]Main!$L$6</f>
+        <v>3735</v>
+      </c>
+      <c r="H8" s="6">
+        <f ca="1">+F8-G8</f>
+        <v>279993.12914735998</v>
+      </c>
+      <c r="I8" s="6">
+        <f>+[16]Main!$L$3</f>
+        <v>148.08975799999999</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K8" s="10">
+        <v>46146</v>
+      </c>
+      <c r="Q8" s="29"/>
+      <c r="S8" s="29"/>
+      <c r="AC8">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" s="1" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="D9" t="s">
+        <v>271</v>
+      </c>
+      <c r="E9" s="4" cm="1">
+        <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
+        <v>910.34</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="Q9" s="29"/>
+      <c r="S9" s="29"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="e" vm="15">
+        <v>#VALUE!</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E10" s="4" cm="1">
+        <f t="array" aca="1" ref="E10" ca="1">_FV(B10,"Price")</f>
+        <v>582.58500000000004</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="Q10" s="29"/>
+      <c r="S10" s="29"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="M2:R2"/>
+    <mergeCell ref="S2:X2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" display="MU.xlsx" xr:uid="{C50FA289-6EE1-4DAA-B344-2AFF21D7BBD1}"/>
+    <hyperlink ref="B7" r:id="rId2" display="NVDA.xlsx" xr:uid="{BB28EC67-A86C-4D67-BB7A-EC0D785C32BB}"/>
+    <hyperlink ref="B6" r:id="rId3" display="NVDA.xlsx" xr:uid="{F58E2C92-B174-41FA-9008-D56DC0490143}"/>
+    <hyperlink ref="B8" r:id="rId4" display="NVDA.xlsx" xr:uid="{189BA126-A6AA-4682-BBEF-32377A1B9453}"/>
+    <hyperlink ref="B9" r:id="rId5" display="NVDA.xlsx" xr:uid="{57AC8EC0-51DD-418F-B632-90A83298F5CA}"/>
+    <hyperlink ref="B10" r:id="rId6" display="NVDA.xlsx" xr:uid="{08079C4F-8AB3-4A9B-9015-3E26D655952F}"/>
+    <hyperlink ref="B4" r:id="rId7" xr:uid="{B27CF321-7BF4-4270-AEE8-B748F0C4C26B}"/>
+    <hyperlink ref="C4" r:id="rId8" xr:uid="{1029B44D-CEA0-4D67-8448-8B6C9BD51C81}"/>
+    <hyperlink ref="C7" r:id="rId9" xr:uid="{CFBBFB6B-8B2B-4FFB-8BF8-C48FB7738363}"/>
+    <hyperlink ref="C5" r:id="rId10" xr:uid="{7B5B4C89-03CC-4E5D-A0CC-890BDE26B1A6}"/>
+    <hyperlink ref="C8" r:id="rId11" xr:uid="{C3511D7D-1F0E-40D4-818C-166E2D5CD881}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId12"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08789E08-EB45-4F3D-9705-50DBCEAD455F}">
+  <dimension ref="B2:AA6"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.6328125" customWidth="1"/>
+    <col min="2" max="2" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.90625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1348</v>
+      </c>
+      <c r="E3" s="6">
+        <f>+D3*H3</f>
+        <v>530438</v>
+      </c>
+      <c r="F3" s="6">
+        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
+        <v>1413.0000000000009</v>
+      </c>
+      <c r="G3" s="6">
+        <f>+E3-F3</f>
+        <v>529025</v>
+      </c>
+      <c r="H3" s="6">
+        <f>+[17]Main!$L$3</f>
+        <v>393.5</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J3" s="10">
+        <v>45581</v>
+      </c>
+      <c r="L3" s="17"/>
+      <c r="P3" s="18"/>
+      <c r="Q3" s="17"/>
+      <c r="V3" s="18"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13">
+        <v>784000</v>
+      </c>
+    </row>
+    <row r="4" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="4">
+        <v>360</v>
+      </c>
+      <c r="E4" s="6">
+        <v>267520</v>
+      </c>
+      <c r="F4" s="6">
+        <f>+[18]Main!$K$5-[18]Main!$K$6</f>
+        <v>6926</v>
+      </c>
+      <c r="G4" s="6">
+        <f>+E4-F4</f>
+        <v>260594</v>
+      </c>
+      <c r="H4" s="6">
+        <f>+[18]Main!$K$3</f>
+        <v>799</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J4" s="3"/>
+      <c r="L4" s="19">
+        <f>($G4/$H4)/R4</f>
+        <v>37.661684495920134</v>
+      </c>
+      <c r="M4" s="20">
+        <f>($G4/$H4)/S4</f>
+        <v>29.462528250647548</v>
+      </c>
+      <c r="N4" s="20">
+        <f>($G4/$H4)/T4</f>
+        <v>23.082108119934066</v>
+      </c>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="17">
+        <v>8.61</v>
+      </c>
+      <c r="R4">
+        <v>8.66</v>
+      </c>
+      <c r="S4">
+        <v>11.07</v>
+      </c>
+      <c r="T4">
+        <v>14.13</v>
+      </c>
+      <c r="V4" s="18"/>
+      <c r="Z4" s="13">
+        <v>1030000</v>
+      </c>
+      <c r="AA4" s="13">
+        <v>665000</v>
+      </c>
+    </row>
+    <row r="5" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D5" s="4">
+        <v>226</v>
+      </c>
+      <c r="E5" s="6">
+        <v>260830</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="6">
+        <f>E5-F5</f>
+        <v>260830</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="10">
+        <v>46089</v>
+      </c>
+      <c r="K5">
+        <v>1980</v>
+      </c>
+      <c r="L5" s="17"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="17"/>
+      <c r="V5" s="18"/>
+      <c r="W5" t="s">
+        <v>249</v>
+      </c>
+      <c r="X5" t="s">
+        <v>250</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>251</v>
+      </c>
+      <c r="Z5" s="13">
+        <v>1236539</v>
+      </c>
+      <c r="AA5" s="13">
+        <v>714596</v>
+      </c>
+    </row>
+    <row r="6" spans="2:27" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1462</v>
+      </c>
+      <c r="E6" s="6">
+        <v>182590</v>
+      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="L6" s="17"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="17"/>
+      <c r="V6" s="18"/>
+      <c r="AA6" s="13">
+        <v>750000</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B3" r:id="rId1" xr:uid="{3EEE25FB-8581-4AA9-ADEF-37DC0B2F3F4D}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{0E1B41B2-39E3-482E-80B4-4D069EE9643C}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{5BA02E53-CE6F-4CB1-A08A-138D1B40007E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF4C6BF-D4BF-4479-9128-495AD030DB4E}">
+  <dimension ref="A4:V9"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.90625" customWidth="1"/>
+    <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>267</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="L4" s="17"/>
+      <c r="P4" s="18"/>
+      <c r="Q4" s="17"/>
+      <c r="V4" s="18"/>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C5" t="s">
+        <v>284</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="L5" s="17"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="17"/>
+      <c r="V5" s="18"/>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="L6" s="17"/>
+      <c r="P6" s="18"/>
+      <c r="Q6" s="17"/>
+      <c r="V6" s="18"/>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" s="22" t="s">
+        <v>340</v>
+      </c>
+      <c r="C8" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7969B36B-DEE6-4982-80A3-7EB4D6794539}">
   <dimension ref="A1:K63"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -3743,7 +6780,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -3754,36 +6791,36 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="6">
@@ -3798,10 +6835,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="6">
@@ -3816,10 +6853,10 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="D5" s="2">
         <v>48</v>
@@ -3829,7 +6866,7 @@
         <v>17711.180015999998</v>
       </c>
       <c r="F5" s="13">
-        <f>+[16]Main!$J$5-[16]Main!$J$6</f>
+        <f>+[19]Main!$J$5-[19]Main!$J$6</f>
         <v>3336.799</v>
       </c>
       <c r="G5" s="13">
@@ -3837,11 +6874,11 @@
         <v>14374.381015999999</v>
       </c>
       <c r="H5" s="13">
-        <f>+[16]Main!$J$3</f>
+        <f>+[19]Main!$J$3</f>
         <v>368.98291699999999</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J5" s="5">
         <v>45664</v>
@@ -3849,10 +6886,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D6">
         <v>14.95</v>
@@ -3862,7 +6899,7 @@
         <v>4239.0257214499998</v>
       </c>
       <c r="F6" s="13">
-        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
+        <f>+[20]Main!$L$5-[20]Main!$L$6</f>
         <v>217</v>
       </c>
       <c r="G6" s="13">
@@ -3870,11 +6907,11 @@
         <v>4022.0257214499998</v>
       </c>
       <c r="H6" s="13">
-        <f>+[17]Main!$L$3</f>
+        <f>+[20]Main!$L$3</f>
         <v>283.54687100000001</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J6" s="5">
         <v>45664</v>
@@ -3882,10 +6919,10 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C7" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D7" s="2">
         <v>7.15</v>
@@ -3896,10 +6933,10 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D8" s="2">
         <v>15.75</v>
@@ -3909,7 +6946,7 @@
         <v>5460.8176507499993</v>
       </c>
       <c r="F8" s="13">
-        <f>+[18]Main!$L$5-[18]Main!$L$6</f>
+        <f>+[21]Main!$L$5-[21]Main!$L$6</f>
         <v>804.03300000000002</v>
       </c>
       <c r="G8" s="13">
@@ -3917,11 +6954,11 @@
         <v>4656.7846507499989</v>
       </c>
       <c r="H8" s="13">
-        <f>+[18]Main!$L$3</f>
+        <f>+[21]Main!$L$3</f>
         <v>346.71858099999997</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="J8" s="5">
         <v>45663</v>
@@ -3929,10 +6966,10 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C9" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D9" s="2">
         <v>3.03</v>
@@ -3940,10 +6977,10 @@
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>267</v>
+        <v>253</v>
       </c>
       <c r="C10" t="s">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="D10" s="2">
         <v>8.93</v>
@@ -3951,255 +6988,255 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="C35" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B38" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B39" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
     </row>
     <row r="57" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
     </row>
     <row r="58" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
     </row>
     <row r="59" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
     </row>
     <row r="63" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -4213,12 +7250,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17F6CD82-B069-4824-8BA4-1B2E25134518}">
-  <dimension ref="A2:K10"/>
+  <dimension ref="A2:K15"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08984375" customWidth="1"/>
     <col min="4" max="5" width="9.1796875" style="11"/>
   </cols>
   <sheetData>
@@ -4230,39 +7268,39 @@
         <v>1</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="I2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J2" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K2" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>46</v>
+      <c r="A3" t="s">
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="D3" s="11">
         <v>48.51</v>
@@ -4272,80 +7310,135 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>46</v>
+      <c r="A4" t="s">
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>46</v>
+      <c r="A5" t="s">
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>272</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
+      <c r="A8" t="s">
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>46</v>
+      <c r="A9" t="s">
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>46</v>
+      <c r="A10" t="s">
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="C10" t="s">
-        <v>232</v>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>304</v>
+      </c>
+      <c r="C13" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" t="s">
+        <v>330</v>
+      </c>
+      <c r="C14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="C15" t="s">
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -4356,9 +7449,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11ECA54-B59D-4EDC-8BE7-0C63EA165B15}">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P62"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.1796875" customWidth="1"/>
@@ -4375,7 +7468,7 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -4386,54 +7479,54 @@
         <v>1</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>46</v>
+      <c r="A3" t="s">
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D3" s="4">
         <v>205.51</v>
@@ -4443,7 +7536,7 @@
         <v>3071963.48</v>
       </c>
       <c r="F3" s="6">
-        <f>+[19]Main!$O$5-[19]Main!$O$6</f>
+        <f>+[22]Main!$O$5-[22]Main!$O$6</f>
         <v>31288</v>
       </c>
       <c r="G3" s="6">
@@ -4451,17 +7544,17 @@
         <v>3040675.48</v>
       </c>
       <c r="H3" s="6">
-        <f>+[19]Main!$O$3</f>
+        <f>+[22]Main!$O$3</f>
         <v>14948</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J3" s="5">
         <v>45750</v>
       </c>
       <c r="K3" s="2">
-        <f>[19]Model!$CE$39</f>
+        <f>[22]Model!$CE$39</f>
         <v>0.46906012207980208</v>
       </c>
       <c r="L3" s="7">
@@ -4469,11 +7562,11 @@
         <v>-0.99771758005897615</v>
       </c>
       <c r="M3" s="8">
-        <f>+[19]Model!$CE$36</f>
+        <f>+[22]Model!$CE$36</f>
         <v>4.1953407917453944E-2</v>
       </c>
       <c r="N3" s="8">
-        <f>+[19]Model!$CE$37</f>
+        <f>+[22]Model!$CE$37</f>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="O3" s="8">
@@ -4484,16 +7577,16 @@
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>46</v>
+      <c r="A4" t="s">
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="15">
+        <v>17</v>
+      </c>
+      <c r="D4" s="14">
         <v>57600</v>
       </c>
       <c r="E4" s="6" cm="1">
@@ -4501,35 +7594,32 @@
         <v>268168.58880661271</v>
       </c>
       <c r="F4" s="6">
-        <f>([20]Main!$K$5-[20]Main!$K$6)/KRW</f>
-        <v>64.28214224212158</v>
+        <f>([4]Main!$K$5-[4]Main!$K$6)/KRW</f>
+        <v>119.75815395212676</v>
       </c>
       <c r="G4" s="6">
         <f>+E4-F4</f>
-        <v>268104.30666437058</v>
+        <v>268048.83065266057</v>
       </c>
       <c r="H4" s="6">
-        <f>+[20]Main!$K$3</f>
+        <f>+[4]Main!$K$3</f>
         <v>6758.9192499999999</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="J4" s="5">
         <v>45750</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>46</v>
-      </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="16">
+        <v>42</v>
+      </c>
+      <c r="D5" s="15">
         <v>73.36</v>
       </c>
       <c r="E5" s="6">
@@ -4545,421 +7635,670 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>46</v>
+      <c r="A6" t="s">
+        <v>36</v>
       </c>
       <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
         <v>59</v>
       </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>46</v>
+      <c r="A9" t="s">
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>46</v>
+      <c r="A10" t="s">
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>46</v>
+      <c r="A11" t="s">
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>46</v>
+      <c r="A12" t="s">
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>46</v>
+      <c r="A13" t="s">
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>198</v>
+        <v>279</v>
       </c>
       <c r="C13" t="s">
-        <v>76</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>91</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>46</v>
+      <c r="A15" t="s">
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="C15" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>46</v>
+      <c r="A16" t="s">
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>203</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>46</v>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>205</v>
+        <v>189</v>
       </c>
       <c r="C18" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>46</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
       </c>
       <c r="B19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B21" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>36</v>
+      </c>
+      <c r="B22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C22" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" t="s">
+        <v>274</v>
+      </c>
+      <c r="C23" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C24" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>36</v>
+      </c>
+      <c r="B25" t="s">
         <v>215</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C25" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" t="s">
-        <v>225</v>
-      </c>
-      <c r="C20" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" t="s">
-        <v>229</v>
-      </c>
-      <c r="C21" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="C26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="C27" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>36</v>
+      </c>
+      <c r="B31" t="s">
+        <v>320</v>
+      </c>
+      <c r="C31" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C32" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>334</v>
+      </c>
+      <c r="C33" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B35" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>36</v>
+      </c>
+      <c r="B36" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="C37" s="22" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>232</v>
+      </c>
+      <c r="C38" t="s">
         <v>233</v>
       </c>
-      <c r="C22" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" t="s">
-        <v>97</v>
-      </c>
-      <c r="C23" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" t="s">
-        <v>235</v>
-      </c>
-      <c r="C24" t="s">
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" t="s">
+        <v>318</v>
+      </c>
+      <c r="C39" s="22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B40" t="s">
+        <v>118</v>
+      </c>
+      <c r="C40" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>36</v>
+      </c>
+      <c r="B41" t="s">
+        <v>312</v>
+      </c>
+      <c r="C41" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>36</v>
+      </c>
+      <c r="B42" t="s">
+        <v>326</v>
+      </c>
+      <c r="C42" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" t="s">
+        <v>299</v>
+      </c>
+      <c r="C43" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="C44" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="C45" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>36</v>
+      </c>
+      <c r="B47" t="s">
+        <v>301</v>
+      </c>
+      <c r="C47" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s">
+        <v>124</v>
+      </c>
+      <c r="C48" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="4">
+        <v>39</v>
+      </c>
+      <c r="E50" s="6">
+        <f>+D50*H50</f>
+        <v>14390.333762999999</v>
+      </c>
+      <c r="F50" s="6">
+        <f>+[19]Main!$J$5-[19]Main!$J$6</f>
+        <v>3336.799</v>
+      </c>
+      <c r="G50" s="6">
+        <f>+E50-F50</f>
+        <v>11053.534763</v>
+      </c>
+      <c r="H50" s="6">
+        <f>+[19]Main!$J$3</f>
+        <v>368.98291699999999</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J50" s="5">
+        <v>45534</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D51" s="3">
+        <v>8.51</v>
+      </c>
+      <c r="E51" s="6">
+        <f>+D51*H51</f>
+        <v>2412.9838722099998</v>
+      </c>
+      <c r="F51" s="6">
+        <f>+[20]Main!$L$5-[20]Main!$L$6</f>
+        <v>217</v>
+      </c>
+      <c r="G51" s="6">
+        <f>+E51-F51</f>
+        <v>2195.9838722099998</v>
+      </c>
+      <c r="H51" s="6">
+        <f>+[20]Main!$L$3</f>
+        <v>283.54687100000001</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J51" s="5">
+        <v>45534</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C52" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C53" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" t="s">
+        <v>117</v>
+      </c>
+      <c r="D54" s="3">
+        <v>101.64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>236</v>
       </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="C55" t="s">
         <v>237</v>
       </c>
-      <c r="C25" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D55" s="4">
         <v>247</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B28" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B29" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" t="s">
-        <v>123</v>
-      </c>
-      <c r="D29" s="4">
-        <v>39</v>
-      </c>
-      <c r="E29" s="6">
-        <f>+D29*H29</f>
-        <v>14390.333762999999</v>
-      </c>
-      <c r="F29" s="6">
-        <f>+[16]Main!$J$5-[16]Main!$J$6</f>
-        <v>3336.799</v>
-      </c>
-      <c r="G29" s="6">
-        <f>+E29-F29</f>
-        <v>11053.534763</v>
-      </c>
-      <c r="H29" s="6">
-        <f>+[16]Main!$J$3</f>
-        <v>368.98291699999999</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="J29" s="5">
-        <v>45534</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B30" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>126</v>
-      </c>
-      <c r="D30" s="3">
-        <v>8.51</v>
-      </c>
-      <c r="E30" s="6">
-        <f>+D30*H30</f>
-        <v>2412.9838722099998</v>
-      </c>
-      <c r="F30" s="6">
-        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
-        <v>217</v>
-      </c>
-      <c r="G30" s="6">
-        <f>+E30-F30</f>
-        <v>2195.9838722099998</v>
-      </c>
-      <c r="H30" s="6">
-        <f>+[17]Main!$L$3</f>
-        <v>283.54687100000001</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J30" s="5">
-        <v>45534</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B31" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B32" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="C32" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B33" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="C33" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="3">
-        <v>101.64</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B34" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C34" t="s">
-        <v>251</v>
-      </c>
-      <c r="D34" s="4">
-        <v>247</v>
-      </c>
-      <c r="E34" s="6">
-        <f>+D34*H34</f>
+      <c r="E55" s="6">
+        <f>+D55*H55</f>
         <v>28641.902146</v>
       </c>
-      <c r="F34" s="6">
-        <f>+[21]Main!$I$5-[21]Main!$I$6</f>
+      <c r="F55" s="6">
+        <f>+[23]Main!$I$5-[23]Main!$I$6</f>
         <v>-373.40000000000003</v>
       </c>
-      <c r="G34" s="6">
-        <f>+E34-F34</f>
+      <c r="G55" s="6">
+        <f>+E55-F55</f>
         <v>29015.302146000002</v>
       </c>
-      <c r="H34" s="6">
-        <f>+[21]Main!$I$3</f>
+      <c r="H55" s="6">
+        <f>+[23]Main!$I$3</f>
         <v>115.959118</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="J34" s="5">
+      <c r="I55" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J55" s="5">
         <v>45915</v>
       </c>
     </row>
-    <row r="38" spans="2:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="B38" s="9" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>65</v>
-      </c>
-      <c r="E39" s="3">
+    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="B59" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>55</v>
+      </c>
+      <c r="E60" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B40" t="s">
-        <v>64</v>
-      </c>
-      <c r="E40" s="3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B61" t="s">
+        <v>54</v>
+      </c>
+      <c r="E61" s="3">
         <v>150</v>
       </c>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B41" t="s">
-        <v>35</v>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B62" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{CD056E5E-713C-45E7-82FC-EFD06739D880}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{E138C484-1EF3-497D-8DD8-4398C67AAB14}"/>
-    <hyperlink ref="B33" r:id="rId3" xr:uid="{17EE0F28-0CA3-4454-8659-59421816F562}"/>
+    <hyperlink ref="B50" r:id="rId2" xr:uid="{E138C484-1EF3-497D-8DD8-4398C67AAB14}"/>
+    <hyperlink ref="B54" r:id="rId3" xr:uid="{17EE0F28-0CA3-4454-8659-59421816F562}"/>
     <hyperlink ref="A1" location="Semiconductors!A1" display="Semis" xr:uid="{3EBFEA52-93DD-4F50-8A15-3931D4DD8A3B}"/>
-    <hyperlink ref="B30" r:id="rId4" xr:uid="{B849A3EA-637F-401B-9004-B19AC4384C38}"/>
-    <hyperlink ref="B31" r:id="rId5" xr:uid="{B3FD8109-CF06-4F67-80CA-74CB8FA3899F}"/>
-    <hyperlink ref="B32" r:id="rId6" xr:uid="{41CB0E3A-9A33-4B05-90FA-F5D94D41DCCA}"/>
+    <hyperlink ref="B51" r:id="rId4" xr:uid="{B849A3EA-637F-401B-9004-B19AC4384C38}"/>
+    <hyperlink ref="B52" r:id="rId5" xr:uid="{B3FD8109-CF06-4F67-80CA-74CB8FA3899F}"/>
+    <hyperlink ref="B53" r:id="rId6" xr:uid="{41CB0E3A-9A33-4B05-90FA-F5D94D41DCCA}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{080EF83F-F30F-4A70-B656-61CF4AB15DF7}"/>
-    <hyperlink ref="B34" r:id="rId8" xr:uid="{0A91E701-42A1-47EB-A9B9-A7A56A386588}"/>
+    <hyperlink ref="B55" r:id="rId8" xr:uid="{0A91E701-42A1-47EB-A9B9-A7A56A386588}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC72FDEE-60E0-4B9B-AACF-AB184FD947A1}">
   <dimension ref="B2:C7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
@@ -4969,7 +8308,7 @@
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="C2">
         <v>32.68</v>
@@ -4977,7 +8316,7 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="C3" s="2">
         <v>1451.75</v>
@@ -4988,12 +8327,12 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>261</v>
+        <v>247</v>
       </c>
       <c r="C5">
         <v>31.99</v>
@@ -5001,7 +8340,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>262</v>
+        <v>248</v>
       </c>
       <c r="C6">
         <v>157.66</v>
@@ -5009,7 +8348,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>279</v>
+        <v>265</v>
       </c>
     </row>
   </sheetData>

--- a/HardwareSemis.xlsx
+++ b/HardwareSemis.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DCB3C6-F5A6-4ABD-8808-57242ABBD4C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F89572-0BA2-4DAD-80EE-AC1F5956AE99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1360" yWindow="4670" windowWidth="22360" windowHeight="16580" activeTab="1" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
+    <workbookView xWindow="500" yWindow="1650" windowWidth="20990" windowHeight="18600" firstSheet="2" activeTab="7" xr2:uid="{98D8347A-DFA4-427C-8784-96E5573B433C}"/>
   </bookViews>
   <sheets>
     <sheet name="Semiconductors" sheetId="1" r:id="rId1"/>
@@ -48,6 +48,10 @@
     <externalReference r:id="rId31"/>
     <externalReference r:id="rId32"/>
     <externalReference r:id="rId33"/>
+    <externalReference r:id="rId34"/>
+    <externalReference r:id="rId35"/>
+    <externalReference r:id="rId36"/>
+    <externalReference r:id="rId37"/>
   </externalReferences>
   <definedNames>
     <definedName name="CNY">FX!$B$4</definedName>
@@ -280,7 +284,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="367">
   <si>
     <t>Name</t>
   </si>
@@ -1369,19 +1373,32 @@
   </si>
   <si>
     <t>MXL</t>
+  </si>
+  <si>
+    <t>Bloom Energy</t>
+  </si>
+  <si>
+    <t>BE</t>
+  </si>
+  <si>
+    <t>Applied Optoelectronics</t>
+  </si>
+  <si>
+    <t>AAOI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="[$₩-412]#,##0"/>
     <numFmt numFmtId="166" formatCode="[$¥-804]#,##0.00"/>
     <numFmt numFmtId="167" formatCode="0\x"/>
+    <numFmt numFmtId="168" formatCode="[$¥-411]#,##0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -1407,12 +1424,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -1492,7 +1503,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1536,6 +1547,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1545,11 +1566,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1609,9 +1625,9 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1630,18 +1646,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="J3">
-            <v>487.08704</v>
+          <cell r="H3">
+            <v>874.8</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>3439.308</v>
+          <cell r="H5">
+            <v>3843.6</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>8134.6509999999998</v>
+          <cell r="H6">
+            <v>4961.3</v>
           </cell>
         </row>
       </sheetData>
@@ -1664,18 +1680,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="M3">
-            <v>640</v>
+          <cell r="J3">
+            <v>487.08704</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="M5">
-            <v>1670</v>
+          <cell r="J5">
+            <v>3439.308</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="M6">
-            <v>2174</v>
+          <cell r="J6">
+            <v>8134.6509999999998</v>
           </cell>
         </row>
       </sheetData>
@@ -1698,18 +1714,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="J3">
-            <v>135.42215899999999</v>
+          <cell r="K3">
+            <v>1603</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>1646.404</v>
+          <cell r="K5">
+            <v>335855</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>1199.432</v>
+          <cell r="K6">
+            <v>16560</v>
           </cell>
         </row>
       </sheetData>
@@ -1732,18 +1748,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>811.04812700000002</v>
+          <cell r="M3">
+            <v>640</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>1203</v>
+          <cell r="M5">
+            <v>1670</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>0</v>
+          <cell r="M6">
+            <v>2174</v>
           </cell>
         </row>
       </sheetData>
@@ -1767,17 +1783,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>63.864503999999997</v>
+            <v>135.42215899999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>522.64</v>
+            <v>1646.404</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>227.42599999999999</v>
+            <v>1199.432</v>
           </cell>
         </row>
       </sheetData>
@@ -1800,22 +1816,22 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="J3">
-            <v>1145</v>
+          <cell r="K3">
+            <v>811.04812700000002</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="J5">
-            <v>31025</v>
+          <cell r="K5">
+            <v>1203</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="J6">
-            <v>5722</v>
+          <cell r="K6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1834,18 +1850,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>148.08975799999999</v>
+          <cell r="J3">
+            <v>63.864503999999997</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>3735</v>
+          <cell r="J5">
+            <v>522.64</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>0</v>
+          <cell r="J6">
+            <v>227.42599999999999</v>
           </cell>
         </row>
       </sheetData>
@@ -1868,18 +1884,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>393.5</v>
+          <cell r="J3">
+            <v>1145</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>6021.2000000000007</v>
+          <cell r="J5">
+            <v>31025</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>4608.2</v>
+          <cell r="J6">
+            <v>5722</v>
           </cell>
         </row>
       </sheetData>
@@ -1902,18 +1918,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>799</v>
+          <cell r="L3">
+            <v>712</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>13479</v>
+          <cell r="L5">
+            <v>87960000</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>6553</v>
+          <cell r="L6">
+            <v>18590000</v>
           </cell>
         </row>
       </sheetData>
@@ -1932,32 +1948,26 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Presentation"/>
-      <sheetName val="Papers"/>
-      <sheetName val="Glossary"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="J3">
-            <v>368.98291699999999</v>
+            <v>541.45541700000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="J5">
-            <v>3336.799</v>
+            <v>705225</v>
           </cell>
         </row>
         <row r="6">
           <cell r="J6">
-            <v>0</v>
+            <v>1047568</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2006,21 +2016,17 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="Gates"/>
-      <sheetName val="Bubbles"/>
-      <sheetName val="TOPS"/>
-      <sheetName val="DNA"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>283.54687100000001</v>
+            <v>148.08975799999999</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>217</v>
+            <v>3735</v>
           </cell>
         </row>
         <row r="6">
@@ -2030,10 +2036,6 @@
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2048,28 +2050,26 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="QUBO"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>346.71858099999997</v>
+            <v>393.5</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>836.23099999999999</v>
+            <v>6021.2000000000007</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>32.198</v>
+            <v>4608.2</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2084,44 +2084,26 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
-      <sheetName val="iPhone"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="O3">
-            <v>14948</v>
+          <cell r="K3">
+            <v>799</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="O5">
-            <v>132986</v>
+          <cell r="K5">
+            <v>13479</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="O6">
-            <v>101698</v>
+          <cell r="K6">
+            <v>6553</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1">
-        <row r="36">
-          <cell r="CE36">
-            <v>4.1953407917453944E-2</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="CE37">
-            <v>3.632000000000013E-2</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="CE39">
-            <v>0.46906012207980208</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2141,17 +2123,17 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="I3">
-            <v>115.959118</v>
+            <v>96.2</v>
           </cell>
         </row>
         <row r="5">
           <cell r="I5">
-            <v>423.3</v>
+            <v>3172.3</v>
           </cell>
         </row>
         <row r="6">
           <cell r="I6">
-            <v>796.7</v>
+            <v>3281.7999999999997</v>
           </cell>
         </row>
       </sheetData>
@@ -2174,22 +2156,22 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>1603</v>
+          <cell r="J3">
+            <v>84.569237000000001</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>335855</v>
+          <cell r="J5">
+            <v>499.73700000000002</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>16560</v>
+          <cell r="J6">
+            <v>57.258000000000003</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2204,17 +2186,61 @@
     <sheetNames>
       <sheetName val="Main"/>
       <sheetName val="Model"/>
+      <sheetName val="Presentation"/>
+      <sheetName val="Papers"/>
+      <sheetName val="Glossary"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="J3">
+            <v>371</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="J5">
+            <v>3091.8959999999997</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="J6">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink26.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="Gates"/>
+      <sheetName val="Bubbles"/>
+      <sheetName val="TOPS"/>
+      <sheetName val="DNA"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>1044.497032</v>
+            <v>283.54687100000001</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>3664</v>
+            <v>217</v>
           </cell>
         </row>
         <row r="6">
@@ -2223,7 +2249,133 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink27.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="QUBO"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="L3">
+            <v>346.71858099999997</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="L5">
+            <v>836.23099999999999</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="L6">
+            <v>32.198</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink28.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+      <sheetName val="iPhone"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="O3">
+            <v>14948</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="O5">
+            <v>132986</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="O6">
+            <v>101698</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1">
+        <row r="36">
+          <cell r="CE36">
+            <v>4.1953407917453944E-2</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="CE37">
+            <v>3.632000000000013E-2</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="CE39">
+            <v>0.46906012207980208</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink29.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Main"/>
+      <sheetName val="Model"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="I3">
+            <v>115.959118</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="I5">
+            <v>423.3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="I6">
+            <v>796.7</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2257,7 +2409,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2291,7 +2443,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2325,7 +2477,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2348,24 +2500,24 @@
       <sheetData sheetId="0">
         <row r="3">
           <cell r="L3">
-            <v>5026</v>
+            <v>5104</v>
           </cell>
         </row>
         <row r="5">
           <cell r="L5">
-            <v>39602</v>
+            <v>38137</v>
           </cell>
         </row>
         <row r="6">
           <cell r="L6">
-            <v>46553</v>
+            <v>50537</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -2384,18 +2536,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="K3">
-            <v>907.57171200000005</v>
+          <cell r="L3">
+            <v>1044.497032</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="K5">
-            <v>9090</v>
+          <cell r="L5">
+            <v>3664</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="K6">
-            <v>7937</v>
+          <cell r="L6">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -2418,18 +2570,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="L3">
-            <v>1114</v>
+          <cell r="K3">
+            <v>907.57171200000005</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="L5">
-            <v>13032</v>
+          <cell r="K5">
+            <v>9090</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="L6">
-            <v>14554</v>
+          <cell r="K6">
+            <v>7937</v>
           </cell>
         </row>
       </sheetData>
@@ -2452,18 +2604,18 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
-          <cell r="H3">
-            <v>874.8</v>
+          <cell r="L3">
+            <v>1114</v>
           </cell>
         </row>
         <row r="5">
-          <cell r="H5">
-            <v>3843.6</v>
+          <cell r="L5">
+            <v>13032</v>
           </cell>
         </row>
         <row r="6">
-          <cell r="H6">
-            <v>4961.3</v>
+          <cell r="L6">
+            <v>14554</v>
           </cell>
         </row>
       </sheetData>
@@ -2608,12 +2760,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>236.54</v>
-    <v>161.61000000000001</v>
-    <v>2.2214</v>
-    <v>8.18</v>
-    <v>-1.8490000000000002E-3</v>
-    <v>4.0339E-2</v>
-    <v>-0.39</v>
+    <v>164.07</v>
+    <v>2.2162999999999999</v>
+    <v>-0.14000000000000001</v>
+    <v>-6.2140000000000003E-4</v>
     <v>USD</v>
     <v>NVIDIA Corporation is an artificial intelligence (AI) infrastructure company. The Company is engaged in accelerated computing to help solve the challenging computational problems. Its segments include Compute &amp; Networking and Graphics. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and AI solutions and software, and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment includes GeForce GPUs for gaming and personal computers (PCs), and Quadro/NVIDIA RTX GPUs for enterprise workstation graphics. Its technology stack includes the foundational NVIDIA CUDA development platform that runs on all NVIDIA GPUs, as well as hundreds of domain-specific software libraries, frameworks, algorithms, software development kits (SDKs), and application programming interfaces (APIs). Its platforms address four markets, which include Data Center, Gaming, Professional Visualization, and Automotive.</v>
     <v>42000</v>
@@ -2621,25 +2771,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2788 San Tomas Expressway, SANTA CLARA, CA, 95051 US</v>
-    <v>211</v>
+    <v>227.49</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999999178122</v>
+    <v>46248.999991816403</v>
     <v>0</v>
-    <v>201.92</v>
-    <v>5105232000000</v>
+    <v>224.5</v>
+    <v>5448872000000</v>
     <v>NVIDIA CORPORATION</v>
     <v>NVIDIA CORPORATION</v>
-    <v>202</v>
-    <v>31.053699999999999</v>
-    <v>202.78</v>
-    <v>210.96</v>
-    <v>210.57</v>
+    <v>226.76499999999999</v>
+    <v>34.481000000000002</v>
+    <v>225.3</v>
+    <v>225.16</v>
     <v>24200000000</v>
     <v>NVDA</v>
     <v>NVIDIA CORPORATION (XNAS:NVDA)</v>
-    <v>148421001</v>
-    <v>152809403</v>
+    <v>1067548</v>
+    <v>124706636</v>
     <v>1998</v>
   </rv>
   <rv s="2">
@@ -2663,11 +2812,9 @@
     <v>4</v>
     <v>479</v>
     <v>223.7</v>
-    <v>1.3766</v>
-    <v>-2.85</v>
-    <v>3.8929999999999998E-3</v>
-    <v>-6.522E-3</v>
-    <v>1.6898</v>
+    <v>1.3936999999999999</v>
+    <v>-4.1399999999999997</v>
+    <v>-9.6170000000000005E-3</v>
     <v>USD</v>
     <v>Taiwan Semiconductor Manufacturing Co Ltd is a Taiwan-based integrated circuit foundry service provider. The Company is primarily engaged in integrated circuit manufacturing services. It offers advanced process technologies, specialised process solutions, advanced photomask and silicon stacking, and packaging-related technologies, while supporting a comprehensive design ecosystem. The Company's products serve diverse electronic sectors including artificial intelligence, high-performance computing, wired and wireless communications, automotive and industrial equipment, personal computing, information applications, consumer electronics, smart internet of things, and wearable devices.</v>
     <v>52045</v>
@@ -2675,25 +2822,24 @@
     <v>XNYS</v>
     <v>XNYS</v>
     <v>No.8, Li-Hsin 6th Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
-    <v>439.65499999999997</v>
+    <v>429.26990000000001</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999984895316</v>
+    <v>46248.999969455472</v>
     <v>3</v>
-    <v>428.1</v>
-    <v>2251500228140</v>
+    <v>424.1</v>
+    <v>2211253189900</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited</v>
-    <v>438.66500000000002</v>
-    <v>36.970799999999997</v>
-    <v>436.96</v>
-    <v>434.11</v>
-    <v>435.7998</v>
+    <v>429.2</v>
+    <v>31.009899999999998</v>
+    <v>430.49</v>
+    <v>426.35</v>
     <v>5186474000</v>
     <v>TSM</v>
     <v>Taiwan Semiconductor Manufacturing Company Limited (XNYS:TSM)</v>
-    <v>9595123</v>
-    <v>14552561</v>
+    <v>104829</v>
+    <v>13980925</v>
     <v>1987</v>
   </rv>
   <rv s="2">
@@ -2716,12 +2862,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>495</v>
-    <v>269.58</v>
-    <v>1.4661999999999999</v>
-    <v>-1.1399999999999999</v>
-    <v>1.075E-3</v>
-    <v>-2.8419999999999999E-3</v>
-    <v>0.4299</v>
+    <v>281.87</v>
+    <v>1.4547000000000001</v>
+    <v>-24.83</v>
+    <v>-5.9428000000000002E-2</v>
     <v>USD</v>
     <v>Broadcom Inc. is a global technology firm that designs, develops, and supplies a range of semiconductors, enterprise software and security solutions. The Company operates through two segments: semiconductor solutions and infrastructure software. Its semiconductor solutions segment includes all of its product lines and intellectual property (IP) licensing. It provides a variety of radio frequency semiconductor devices, wireless connectivity solutions, custom touch controllers, and inductive charging solutions for mobile applications. Its infrastructure software segment includes its private and hybrid cloud, application development and delivery, software-defined edge, application networking and security, mainframe, distributed and cybersecurity solutions, and its FC SAN business. It provides a portfolio of software solutions that enable customers to plan, develop, automate, manage and secure applications across mainframe, distributed, mobile and cloud platforms.</v>
     <v>33000</v>
@@ -2729,25 +2873,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>3421 Hillview Avenue, PALO ALTO, CA, 94304 US</v>
-    <v>402.44</v>
+    <v>412.5</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999910358594</v>
+    <v>46248.999961191403</v>
     <v>6</v>
-    <v>395.7</v>
-    <v>1902889272600</v>
+    <v>388.5</v>
+    <v>1869681364200</v>
     <v>BROADCOM INC.</v>
     <v>BROADCOM INC.</v>
-    <v>398.5</v>
-    <v>66.812899999999999</v>
-    <v>401.11</v>
-    <v>399.97</v>
-    <v>400.3999</v>
+    <v>411.96</v>
+    <v>65.460400000000007</v>
+    <v>417.82</v>
+    <v>392.99</v>
     <v>4757580000</v>
     <v>AVGO</v>
     <v>BROADCOM INC. (XNAS:AVGO)</v>
-    <v>14595928</v>
-    <v>34632683</v>
+    <v>282329</v>
+    <v>18062656</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -2770,12 +2913,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>584.73</v>
-    <v>141.6</v>
-    <v>2.4632999999999998</v>
-    <v>11.17</v>
-    <v>3.3700000000000002E-3</v>
-    <v>2.0430999999999998E-2</v>
-    <v>1.88</v>
+    <v>149.22</v>
+    <v>2.4801000000000002</v>
+    <v>31.38</v>
+    <v>6.4967999999999998E-2</v>
     <v>USD</v>
     <v>Advanced Micro Devices, Inc. is a global semiconductor company. The Company is focused on high-performance computing and artificial intelligence (AI). Its segments include Data Center, Client and Gaming, and Embedded. Data Center segment includes AI accelerators, microprocessors (CPUs) for servers, graphics processing units (GPUs), accelerated processing units (APUs), data processing units (DPUs), Field Programmable Gate Arrays (FPGAs), and Adaptive system-on-Chip (SoC) products for data centers. Client and Gaming segment includes CPUs, APUs, chipsets for desktops and notebooks, discrete GPUs, and semi-custom SoC products and development services. Embedded segment includes embedded CPUs, APUs, FPGAs, system on modules (SOMs), and Adaptive SoC products. It markets and sells its products under the AMD trademark. Its products include AMD EPYC, AMD Ryzen, AMD Ryzen PRO, Virtex UltraScale+, among others.</v>
     <v>31000</v>
@@ -2783,25 +2924,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2485 Augustine Drive, SANTA CLARA, CA, 95054 US</v>
-    <v>560.25</v>
+    <v>514.66999999999996</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999974675782</v>
+    <v>46248.999995057813</v>
     <v>9</v>
-    <v>540.04999999999995</v>
-    <v>909695991890</v>
+    <v>483.2</v>
+    <v>839728815250</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
     <v>ADVANCED MICRO DEVICES, INC.</v>
-    <v>544.005</v>
-    <v>182.24610000000001</v>
-    <v>546.72</v>
-    <v>557.89</v>
-    <v>559.77</v>
-    <v>1630601000</v>
+    <v>487.6</v>
+    <v>131.28489999999999</v>
+    <v>483.01</v>
+    <v>514.39</v>
+    <v>1632475000</v>
     <v>AMD</v>
     <v>ADVANCED MICRO DEVICES, INC. (XNAS:AMD)</v>
-    <v>20704530</v>
-    <v>31272350</v>
+    <v>317829</v>
+    <v>27855532</v>
     <v>1969</v>
   </rv>
   <rv s="2">
@@ -2824,38 +2964,35 @@
     <v>Finance</v>
     <v>4</v>
     <v>142.35</v>
-    <v>18.965</v>
-    <v>2.1977000000000002</v>
-    <v>-2.7</v>
-    <v>-2.0479999999999999E-3</v>
-    <v>-2.3990999999999998E-2</v>
-    <v>-0.22500000000000001</v>
+    <v>22.774999999999999</v>
+    <v>2.2505999999999999</v>
+    <v>-2.06</v>
+    <v>-1.9702000000000001E-2</v>
     <v>USD</v>
     <v>Intel Corporation is a global designer and manufacturer of semiconductor products. The Company's segments include Intel Products, Intel Foundry, and All Other. Its Intel Products comprise Client Computing Group (CCG) and Data Center and AI (DCAI). CCG delivers platforms and processors that power PCs and edge devices, enabling enhanced performance, connectivity and user experience for consumer and commercial markets with capabilities that also support retail, industrial robotics and AI ecosystems at the edge. DCAI delivers workload-optimized solutions based upon its x86 architecture for data centers, including CPUs, AI accelerators, NICs, IPUs and custom ASICs, enabling performance and scalability for cloud, enterprise, telecommunication and HPC environments. The Intel Foundry segment comprises technology development, manufacturing and foundry services, developing new semiconductor process technologies and advanced packaging technologies. All Other segments include Mobileye and Other.</v>
-    <v>83200</v>
+    <v>82300</v>
     <v>Nasdaq Stock Market</v>
     <v>XNAS</v>
     <v>XNAS</v>
     <v>2200 Mission College Blvd, Rnb-4-151, SANTA CLARA, CA, 95054 US</v>
-    <v>110.85</v>
+    <v>106.87</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999984073438</v>
+    <v>46248.999990392971</v>
     <v>12</v>
-    <v>107.45</v>
-    <v>552055840000</v>
+    <v>102.05</v>
+    <v>541719572500</v>
     <v>INTEL CORPORATION</v>
     <v>INTEL CORPORATION</v>
-    <v>109.575</v>
+    <v>104.48</v>
     <v>0</v>
-    <v>112.54</v>
-    <v>109.84</v>
-    <v>109.61499999999999</v>
-    <v>5026000000</v>
+    <v>104.56</v>
+    <v>102.5</v>
+    <v>5285069000</v>
     <v>INTC</v>
     <v>INTEL CORPORATION (XNAS:INTC)</v>
-    <v>70846601</v>
-    <v>127554214</v>
+    <v>1805557</v>
+    <v>116349255</v>
     <v>1989</v>
   </rv>
   <rv s="2">
@@ -2875,11 +3012,9 @@
     <v>4</v>
     <v>452.7</v>
     <v>100.02</v>
-    <v>1.2829999999999999</v>
-    <v>-4.4800000000000004</v>
-    <v>3.5620000000000001E-3</v>
-    <v>-1.3664000000000001E-2</v>
-    <v>1.1517999999999999</v>
+    <v>1.2010000000000001</v>
+    <v>0.79</v>
+    <v>2.8349999999999998E-3</v>
     <v>USD</v>
     <v>Arm Holdings plc is a United Kingdom-based company. The Company is engaged in the design of central processing units (CPUs) and compute platforms for semiconductor chips. It develops and licenses CPU products and related technology. Its cloud and data center solutions include Arm AGI CPU and Arm Neoverse Compute Subsystems. The Arm Agentic Generalized Infrastructure (AGI) CPU is a production-ready system on a chip (SoC) for artificial intelligence (AI) data centers, delivering compute at scale. The Arm Neoverse Compute Subsystems (CSS) are pre-validated, performance-optimized compute platforms designed to accelerate infrastructure silicon development. The Company's primary markets include smartphone applications, processors and other chips used in mobile phones, consumer electronics, networking equipment, cloud and data center servers, automotive applications, Internet of Things (loT) and other embedded computing devices.</v>
     <v>9584</v>
@@ -2887,24 +3022,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>110 Fulbourn Road, CAMBRIDGE, CAMBRIDGESHIRE, CB1 9NJ GB</v>
-    <v>328.28059999999999</v>
+    <v>281.66989999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999949501565</v>
-    <v>317.88</v>
-    <v>345406067810</v>
+    <v>46248.999313182816</v>
+    <v>274.45499999999998</v>
+    <v>298441920000</v>
     <v>ARM HOLDINGS PLC</v>
     <v>ARM HOLDINGS PLC</v>
-    <v>322.7</v>
-    <v>387.37459999999999</v>
-    <v>327.87</v>
-    <v>323.39</v>
-    <v>324.54180000000002</v>
-    <v>1068079000</v>
+    <v>278.23</v>
+    <v>330.1551</v>
+    <v>278.64999999999998</v>
+    <v>279.44</v>
+    <v>1068000000</v>
     <v>ARM</v>
     <v>ARM HOLDINGS PLC (XNAS:ARM)</v>
-    <v>2770934</v>
-    <v>10572514</v>
+    <v>63691</v>
+    <v>5734365</v>
     <v>2018</v>
   </rv>
   <rv s="2">
@@ -2928,11 +3062,9 @@
     <v>4</v>
     <v>334.03</v>
     <v>152.72999999999999</v>
-    <v>1.3137000000000001</v>
-    <v>2.93</v>
-    <v>1.9589999999999998E-3</v>
-    <v>9.4970000000000002E-3</v>
-    <v>0.61</v>
+    <v>1.3169999999999999</v>
+    <v>6.15</v>
+    <v>2.2492000000000002E-2</v>
     <v>USD</v>
     <v>Texas Instruments Incorporated is engaged in the design and manufacture of semiconductors. The Company operates through two segments, which include Analog and Embedded Processing. Its Analog segment semiconductors are used to manage power in all electronic equipment by converting, distributing, storing, discharging, isolating, and measuring electrical energy. It consists of two products, which include Power and Signal Chain. The Analog segment includes product lines, such as Power and Signal Chain. Power includes products that help customers manage power in electronic systems. Signal Chain products include amplifiers, data converters, interface products, motor drives, clocks, logic, and sensing products. Its portfolio is designed to manage power requirements across different voltage levels. The Embedded Processing segment products are designed to handle specific tasks and can be optimized for various combinations of performance, power, and cost, depending on the application.</v>
     <v>33000</v>
@@ -2940,25 +3072,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>12500 T I Blvd, DALLAS, TX, 75243-0592 US</v>
-    <v>312.92500000000001</v>
+    <v>280.27499999999998</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.998741017967</v>
+    <v>46248.996138448434</v>
     <v>17</v>
-    <v>303.39999999999998</v>
-    <v>283457503488</v>
+    <v>272.51</v>
+    <v>255325791966</v>
     <v>TEXAS INSTRUMENTS INCORPORATED</v>
     <v>TEXAS INSTRUMENTS INCORPORATED</v>
-    <v>304.2</v>
-    <v>56.299900000000001</v>
-    <v>308.52999999999997</v>
-    <v>311.45999999999998</v>
-    <v>312.07</v>
-    <v>910092800</v>
+    <v>273.62</v>
+    <v>42.523800000000001</v>
+    <v>273.43</v>
+    <v>279.58</v>
+    <v>913247700</v>
     <v>TXN</v>
     <v>TEXAS INSTRUMENTS INCORPORATED (XNAS:TXN)</v>
-    <v>4141905</v>
-    <v>9896056</v>
+    <v>19954</v>
+    <v>7530819</v>
     <v>1938</v>
   </rv>
   <rv s="2">
@@ -3002,11 +3133,9 @@
     <v>4</v>
     <v>259.92</v>
     <v>121.99</v>
-    <v>1.6361000000000001</v>
-    <v>-1.95</v>
-    <v>-1.374E-3</v>
-    <v>-1.0204E-2</v>
-    <v>-0.26</v>
+    <v>1.6787000000000001</v>
+    <v>1</v>
+    <v>6.0680000000000005E-3</v>
     <v>USD</v>
     <v>Qualcomm Incorporated is engaged in the development and commercialization of foundational technologies for the wireless industry, including third generation (3G), fourth generation (4G) and fifth generation (5G) wireless connectivity, and high-performance and low-power computing, including on-device artificial intelligence. Its segments include Qualcomm CDMA Technologies (QCT), Qualcomm Technology Licensing (QTL) and Qualcomm Strategic Initiatives. QCT develops and supplies integrated circuits and system software based on 3G/4G/5G and other technologies, including radio frequency front-end, digital cockpit and advanced driver assistance and automated driving, Internet of things including consumer electronic devices, industrial devices and edge networking products. QTL grants licenses or otherwise provides rights to use portions of its intellectual property portfolio that includes certain patent rights essential to and/or useful in the manufacture and sale of certain wireless products.</v>
     <v>52000</v>
@@ -3014,26 +3143,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5775 Morehouse Drive, SAN DIEGO, CA, 92121 US</v>
-    <v>190.19</v>
+    <v>166.965</v>
     <v>23</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999990844532</v>
+    <v>46248.999833332811</v>
     <v>24</v>
-    <v>185.72</v>
-    <v>199374640000</v>
+    <v>163.18</v>
+    <v>174079500000</v>
     <v>QUALCOMM INCORPORATED</v>
     <v>QUALCOMM INCORPORATED</v>
-    <v>187.50800000000001</v>
-    <v>20.787700000000001</v>
-    <v>191.11</v>
-    <v>189.16</v>
-    <v>188.9</v>
-    <v>1054000000</v>
+    <v>165.63</v>
+    <v>19.187799999999999</v>
+    <v>164.79</v>
+    <v>165.79</v>
+    <v>1050000000</v>
     <v>QCOM</v>
     <v>QUALCOMM INCORPORATED (XNAS:QCOM)</v>
-    <v>7063957</v>
-    <v>21168579</v>
+    <v>77209</v>
+    <v>12005333</v>
     <v>1991</v>
   </rv>
   <rv s="2">
@@ -3057,11 +3185,9 @@
     <v>4</v>
     <v>329.88</v>
     <v>61.44</v>
-    <v>2.2000999999999999</v>
-    <v>-7.4</v>
-    <v>3.4770000000000001E-3</v>
-    <v>-3.0426000000000002E-2</v>
-    <v>0.82</v>
+    <v>2.2650999999999999</v>
+    <v>-0.16</v>
+    <v>-7.2009999999999999E-4</v>
     <v>USD</v>
     <v>Marvell Technology, Inc. together with its consolidated subsidiaries, is a supplier of data infrastructure semiconductor solutions, spanning the data center core to network edge. It is engaged in the design, development and sale of integrated circuits. Its product offerings include custom application-specific integrated circuits (ASICs), interconnects, ethernet solutions, fiber channel adapters, processors and storage controllers. In addition, it is also developing Ultra Accelerator LinkTM (UALinkTM) switches and ethernet for scale-up networking (ESUN) switches for the emerging scale-out artificial intelligence market. Its solutions integrate multiple analogs, mixed-signal and digital intellectual property components incorporating hardware, firmware and software technologies and its system knowledge to provide its customers with integrated solutions for their end products. It designs and manufactures photonic integrated circuits for ultra-high-bandwidth and low-power applications.</v>
     <v>7480</v>
@@ -3069,25 +3195,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>1000 N. West Street, Suite 1200, WILMINGTON, DE, 19801 US</v>
-    <v>240.94</v>
+    <v>223.5179</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.999979282031</v>
+    <v>46248.999992534373</v>
     <v>27</v>
-    <v>232.02</v>
-    <v>206514474784</v>
+    <v>217.1</v>
+    <v>194437656128</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
     <v>MARVELL TECHNOLOGY, INC.</v>
-    <v>237.79</v>
-    <v>83.304500000000004</v>
-    <v>243.21</v>
-    <v>235.81</v>
-    <v>236.63</v>
+    <v>221.39500000000001</v>
+    <v>76.046499999999995</v>
+    <v>222.18</v>
+    <v>222.02</v>
     <v>875766400</v>
     <v>MRVL</v>
     <v>MARVELL TECHNOLOGY, INC. (XNAS:MRVL)</v>
-    <v>15105972</v>
-    <v>60320638</v>
+    <v>434213</v>
+    <v>23016247</v>
     <v>2020</v>
   </rv>
   <rv s="2">
@@ -3110,12 +3235,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>445.91</v>
-    <v>218.37</v>
-    <v>1.194</v>
-    <v>2.0099999999999998</v>
-    <v>1.4149999999999998E-3</v>
-    <v>5.1060000000000003E-3</v>
-    <v>0.56000000000000005</v>
+    <v>223.47</v>
+    <v>1.2131000000000001</v>
+    <v>8.2200000000000006</v>
+    <v>2.1564999999999997E-2</v>
     <v>USD</v>
     <v>Analog Devices, Inc. is a global semiconductor company. It combines analog, digital, artificial intelligence (AI), and software technologies into solutions that combat climate change, reliably connect humans and the world, and help drive advancements in automation and robotics, mobility, healthcare, energy and data centers. It designs, manufactures, tests and markets a portfolio of solutions, including integrated circuits (ICs), software and subsystems that leverage high-performance analog, mixed-signal and digital signal processing technologies. Its product portfolio, domain specialization and advanced manufacturing capabilities extend across high-performance precision and high-speed mixed-signal, power management and processing technologies, including data converters, amplifiers, power management, power management, radio frequency ICs, edge processors and other sensors. Its IC product portfolio includes both general-purpose products used by a range of customers and applications.</v>
     <v>24500</v>
@@ -3123,25 +3246,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>One Analog Way, WILMINGTON, MA, 01887 US</v>
-    <v>398.33499999999998</v>
+    <v>389.45</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.997845589845</v>
+    <v>46248.999139803127</v>
     <v>30</v>
-    <v>385.93</v>
-    <v>192715971550</v>
+    <v>380.12</v>
+    <v>189666806930</v>
     <v>ANALOG DEVICES, INC.</v>
     <v>ANALOG DEVICES, INC.</v>
-    <v>387.5</v>
-    <v>55.972999999999999</v>
-    <v>393.64</v>
-    <v>395.65</v>
-    <v>396.21</v>
+    <v>381.98</v>
+    <v>55.368699999999997</v>
+    <v>381.17</v>
+    <v>389.39</v>
     <v>487087000</v>
     <v>ADI</v>
     <v>ANALOG DEVICES, INC. (XNAS:ADI)</v>
-    <v>2325909</v>
-    <v>5475345</v>
+    <v>12239</v>
+    <v>3705752</v>
     <v>1965</v>
   </rv>
   <rv s="2">
@@ -3151,23 +3273,23 @@
     <v>https://www.bing.com/financeapi/forcetrigger?t=anb9sm&amp;q=XTAI%3a2454&amp;form=skydnc</v>
     <v>Learn more on Bing</v>
   </rv>
-  <rv s="7">
+  <rv s="1">
     <v>en-US</v>
     <v>anb9sm</v>
     <v>268435456</v>
     <v>1</v>
     <v>Powered by Refinitiv</v>
-    <v>12</v>
+    <v>0</v>
     <v>MediaTek Inc. (XTAI:2454)</v>
     <v>2</v>
+    <v>12</v>
+    <v>Finance</v>
     <v>13</v>
-    <v>Finance</v>
-    <v>14</v>
     <v>4970</v>
     <v>1130</v>
-    <v>2.1217999999999999</v>
-    <v>-70</v>
-    <v>-1.7521999999999999E-2</v>
+    <v>2.1334</v>
+    <v>-160</v>
+    <v>-3.8004999999999997E-2</v>
     <v>TWD</v>
     <v>MediaTek Inc is a Taiwan-based company principally engaged in the research, development, manufacture and distribution of multimedia integrated circuit (IC) chipsets. The main products including mobile communication chipsets, tablet computer chips, bluetooth chips, wireless local area network (WLAN) chips, global positioning system (GPS) chips, optical storage chipsets, artificial intelligence Internet of Things device single chips, automotive electronic chipsets and others. The Company is also involved in the provision of related design, testing, maintenance and technological consultancy services. The Company's products are mainly used in mobile phones, digital TVs, personal computer systems, digital home appliances, wearable devices and Internet of Things products. The Company mainly distributes its products in domestic and overseas markets.</v>
     <v>6999</v>
@@ -3175,24 +3297,24 @@
     <v>XTAI</v>
     <v>XTAI</v>
     <v>No. 1, Dusing 1st Road, Hsinchu Science Park, HSINCHU, HSINCHU, 300 TW</v>
-    <v>4050</v>
+    <v>4225</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46212.402013888888</v>
+    <v>46251.395613425928</v>
     <v>33</v>
-    <v>3925</v>
-    <v>6295287875000</v>
+    <v>4025</v>
+    <v>6495774750000</v>
     <v>MediaTek Inc.</v>
     <v>MediaTek Inc.</v>
-    <v>3970</v>
-    <v>62.4</v>
-    <v>3995</v>
-    <v>3925</v>
+    <v>4205</v>
+    <v>66.743600000000001</v>
+    <v>4210</v>
+    <v>4050</v>
     <v>1603895000</v>
     <v>2454</v>
     <v>MediaTek Inc. (XTAI:2454)</v>
-    <v>7370647</v>
-    <v>11393580</v>
+    <v>10559715</v>
+    <v>9415060</v>
     <v>1997</v>
   </rv>
   <rv s="2">
@@ -3215,12 +3337,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>1255</v>
-    <v>103.38</v>
-    <v>2.1598000000000002</v>
-    <v>-12.34</v>
-    <v>3.5230000000000001E-3</v>
-    <v>-1.2444E-2</v>
-    <v>3.4500999999999999</v>
+    <v>113.46</v>
+    <v>2.2261000000000002</v>
+    <v>21.83</v>
+    <v>2.2982999999999996E-2</v>
     <v>USD</v>
     <v>Micron Technology, Inc. provides memory and storage solutions. The Company delivers a portfolio of high-performance dynamic random-access memory (DRAM), NAND, and NOR memory and storage products through its Micron and Crucial brands. The Company's products enable advancing in artificial intelligence (AI) and compute-intensive applications. Its segments include Cloud Memory Business Unit (CMBU), Core Data Center Business Unit (CDBU), Mobile and Client Business Unit (MCBU) and Automotive and Embedded Business Unit (AEBU). CMBU is focused on memory solutions for large hyperscale cloud customers, and high bandwidth memory (HBM) for all data center customers. CDBU is focused on memory solutions for mid-tier cloud, enterprise, and OEM data center customers and storage solutions for all data center customers. MCBU is focused on memory and storage solutions for mobile and client segments. AEBU is focused on memory and storage solutions for the automotive, industrial, and consumer segments.</v>
     <v>53000</v>
@@ -3228,25 +3348,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>8000 S Federal Way, Po Box 6, BOISE, ID, 83716-9632 US</v>
-    <v>998</v>
+    <v>984</v>
     <v>Semiconductors &amp; Semiconductor Equipment</v>
     <v>Stock</v>
-    <v>46213.9999923375</v>
+    <v>46248.999982233596</v>
     <v>36</v>
-    <v>954.13</v>
-    <v>1106014564900</v>
+    <v>956.2</v>
+    <v>1097386002380</v>
     <v>MICRON TECHNOLOGY, INC.</v>
     <v>MICRON TECHNOLOGY, INC.</v>
-    <v>964.97500000000002</v>
-    <v>22.4495</v>
-    <v>991.64</v>
-    <v>979.3</v>
-    <v>982.75009999999997</v>
+    <v>979.32</v>
+    <v>21.9971</v>
+    <v>949.83</v>
+    <v>971.66</v>
     <v>1129393000</v>
     <v>MU</v>
     <v>MICRON TECHNOLOGY, INC. (XNAS:MU)</v>
-    <v>31768093</v>
-    <v>55952383</v>
+    <v>1141250</v>
+    <v>42986433</v>
     <v>1984</v>
   </rv>
   <rv s="2">
@@ -3265,12 +3384,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>2354.3899000000001</v>
-    <v>40.1</v>
-    <v>2.706</v>
-    <v>57.65</v>
-    <v>9.9590000000000008E-3</v>
-    <v>3.1023000000000002E-2</v>
-    <v>19.079999999999998</v>
+    <v>43.201599999999999</v>
+    <v>2.59</v>
+    <v>113</v>
+    <v>7.3948E-2</v>
     <v>USD</v>
     <v>SanDisk Corporation is a developer, manufacturer and provider of data storage devices and solutions based on NAND flash technology and has consumer brands and franchises globally. The Company's solutions include a range of solid state drives (SSDs) embedded products, removable cards, universal serial bus (USB) drives, and wafers and components. Its broad portfolio of technology and products addresses multiple end markets of Datacenter, Edge and Consumer. Its Datacenter end market is composed primarily of products for public or private cloud environments and enterprise customers. The Company, through the Edge end market, provides original equipment manufacturer and channel customers a broad array of high-performance flash solutions across personal computer, mobile, gaming, automotive, virtual reality headsets, at-home entertainment, and industrial spaces. The Company serves the Consumer end market with a broad range of retail and other end-user products.</v>
     <v>11000</v>
@@ -3278,24 +3395,23 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>951 Sandisk Drive, MILPITAS, CA, 95035 US</v>
-    <v>1946.835</v>
+    <v>1667.19</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46213.999983726564</v>
-    <v>1773</v>
-    <v>283728209616</v>
+    <v>46248.999993043748</v>
+    <v>1565</v>
+    <v>239602060000</v>
     <v>SANDISK CORPORATION</v>
     <v>SANDISK CORPORATION</v>
-    <v>1778.9839999999999</v>
-    <v>67.734800000000007</v>
-    <v>1858.27</v>
-    <v>1915.92</v>
-    <v>1935</v>
-    <v>148089800</v>
+    <v>1646.93</v>
+    <v>22.248899999999999</v>
+    <v>1528.11</v>
+    <v>1641.11</v>
+    <v>146000000</v>
     <v>SNDK</v>
     <v>SANDISK CORPORATION (XNAS:SNDK)</v>
-    <v>11022652</v>
-    <v>12066811</v>
+    <v>726071</v>
+    <v>16258976</v>
     <v>2024</v>
   </rv>
   <rv s="2">
@@ -3318,12 +3434,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>1145</v>
-    <v>138.30000000000001</v>
-    <v>2.0746000000000002</v>
-    <v>20.25</v>
-    <v>4.4709999999999997E-4</v>
-    <v>2.2751E-2</v>
-    <v>0.40699999999999997</v>
+    <v>152.5</v>
+    <v>2.1078000000000001</v>
+    <v>52.07</v>
+    <v>5.6513999999999995E-2</v>
     <v>USD</v>
     <v>Seagate Technology Holdings plc provides mass-data storage infrastructure solution. The Company’s principal products are hard disk drives, commonly referred to as disk drives, hard drives (HDDs). In addition to HDDs, the Company produces a range of data storage products, including solid state drives (SSDs), solid state hybrid drives, storage subsystems, as well as a scalable edge-to-cloud mass data platform. Its HDD products are designed for mass capacity storage and legacy markets. Mass capacity storage involves use cases, such as hyperscale data centers and public clouds, as well as emerging use cases. The Company’s HDD and SSD product portfolio includes Serial Advanced Technology Attachment, Serial Attached SCSI and Non-Volatile Memory Express based designs to support a variety of mass capacity and legacy applications. Its systems portfolio includes storage subsystems for enterprises, cloud service providers, scale-out storage servers and original equipment manufacturers.</v>
     <v>30000</v>
@@ -3331,25 +3445,24 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>121 Woodlands Avenue 5, 739009 SG</v>
-    <v>927.2799</v>
+    <v>990.61</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46213.999899767972</v>
+    <v>46248.999947071097</v>
     <v>41</v>
-    <v>861.63</v>
-    <v>205966336714</v>
+    <v>920</v>
+    <v>220624822080</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY</v>
-    <v>861.63</v>
-    <v>84.516499999999994</v>
-    <v>890.09</v>
-    <v>910.34</v>
-    <v>910.74699999999996</v>
-    <v>226252100</v>
+    <v>941.26</v>
+    <v>70.011899999999997</v>
+    <v>921.37</v>
+    <v>973.44</v>
+    <v>226644500</v>
     <v>STX</v>
     <v>SEAGATE TECHNOLOGY HOLDINGS PUBLIC LIMITED COMPANY (XNAS:STX)</v>
-    <v>4051284</v>
-    <v>4658461</v>
+    <v>45190</v>
+    <v>5399379</v>
     <v>2017</v>
   </rv>
   <rv s="2">
@@ -3388,12 +3501,10 @@
     <v>Finance</v>
     <v>4</v>
     <v>799.87</v>
-    <v>64.23</v>
-    <v>2.1341999999999999</v>
-    <v>4.5350000000000001</v>
-    <v>-1.116E-4</v>
-    <v>7.8449999999999995E-3</v>
-    <v>-6.5000000000000002E-2</v>
+    <v>73.14</v>
+    <v>2.1255000000000002</v>
+    <v>21.51</v>
+    <v>4.4142000000000001E-2</v>
     <v>USD</v>
     <v>Western Digital Corporation is a developer, manufacturer and provider of data storage devices and solutions on hard disk drives (HDD) technologies. The Company manufactures, markets, and sells data storage devices and solutions through its sales personnel, dealers, distributors, retailers, and subsidiaries. Its portfolio of technology and products addresses end markets: Cloud, Client, and Consumer. Cloud is comprised primarily of products for public or private cloud environments and enterprise customers. Through the Client end market, the Company provides its original equipment manufacturer (OEM) and channel customers with a broad array of high-performance HDD solutions across desktops and notebooks. The Consumer end market offers a range of retail and other end-user products. Its product portfolio includes Internal HDD, Data Center Drives, Data Center Platforms, External Drives, Portable Drives, network-attached storage (NAS) for Home and Office, and Accessories.</v>
     <v>40000</v>
@@ -3401,26 +3512,25 @@
     <v>XNAS</v>
     <v>XNAS</v>
     <v>5601 Great Oaks Parkway, SAN JOSE, CA, 95119 US</v>
-    <v>585.20000000000005</v>
+    <v>516.35</v>
     <v>46</v>
     <v>Computers, Phones &amp; Household Electronics</v>
     <v>Stock</v>
-    <v>46213.999795358592</v>
+    <v>46248.999964988281</v>
     <v>47</v>
-    <v>562.76</v>
-    <v>200806621228</v>
+    <v>487.1</v>
+    <v>175374252480</v>
     <v>WESTERN DIGITAL CORPORATION</v>
     <v>WESTERN DIGITAL CORPORATION</v>
-    <v>563.995</v>
-    <v>37.670299999999997</v>
-    <v>578.04999999999995</v>
-    <v>582.58500000000004</v>
-    <v>582.52</v>
+    <v>503.5</v>
+    <v>20.955500000000001</v>
+    <v>487.29</v>
+    <v>508.8</v>
     <v>344682100</v>
     <v>WDC</v>
     <v>WESTERN DIGITAL CORPORATION (XNAS:WDC)</v>
-    <v>4814144</v>
-    <v>10042796</v>
+    <v>145110</v>
+    <v>7971077</v>
     <v>2000</v>
   </rv>
   <rv s="2">
@@ -3430,166 +3540,10 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="7">
   <s t="_hyperlink">
     <k n="Address" t="s"/>
     <k n="Text" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_linkedentity">
-    <k n="%cvi" t="r"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
-  </s>
-  <s t="_sourceattribution">
-    <k n="License" t="r"/>
-    <k n="Source" t="r"/>
-  </s>
-  <s t="_imageurl">
-    <k n="_Provider" t="spb"/>
-    <k n="Address" t="s"/>
-    <k n="Attribution" t="r"/>
-    <k n="ComputedImage" t="b"/>
-    <k n="More Images Address" t="s"/>
-    <k n="Text" t="s"/>
-  </s>
-  <s t="_linkedentitycore">
-    <k n="%EntityCulture" t="s"/>
-    <k n="%EntityId" t="s"/>
-    <k n="%EntityServiceId"/>
-    <k n="%IsRefreshable" t="b"/>
-    <k n="%ProviderInfo" t="s"/>
-    <k n="_Display" t="spb"/>
-    <k n="_DisplayString" t="s"/>
-    <k n="_Flags" t="spb"/>
-    <k n="_Format" t="spb"/>
-    <k n="_Icon" t="s"/>
-    <k n="_SubLabel" t="spb"/>
-    <k n="52 week high"/>
-    <k n="52 week low"/>
-    <k n="Beta"/>
-    <k n="Change"/>
-    <k n="Change % (Extended hours)"/>
-    <k n="Change (%)"/>
-    <k n="Change (Extended hours)"/>
-    <k n="Currency" t="s"/>
-    <k n="Description" t="s"/>
-    <k n="Employees"/>
-    <k n="Exchange" t="s"/>
-    <k n="Exchange abbreviation" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Headquarters" t="s"/>
-    <k n="High"/>
-    <k n="Image" t="r"/>
-    <k n="Industry" t="s"/>
-    <k n="Instrument type" t="s"/>
-    <k n="Last trade time"/>
-    <k n="LearnMoreOnLink" t="r"/>
-    <k n="Low"/>
-    <k n="Market cap"/>
-    <k n="Name" t="s"/>
-    <k n="Official name" t="s"/>
-    <k n="Open"/>
-    <k n="P/E"/>
-    <k n="Previous close"/>
-    <k n="Price"/>
-    <k n="Price (Extended hours)"/>
-    <k n="Shares outstanding"/>
-    <k n="Ticker symbol" t="s"/>
-    <k n="UniqueName" t="s"/>
-    <k n="Volume"/>
-    <k n="Volume average"/>
-    <k n="Year incorporated"/>
   </s>
   <s t="_linkedentitycore">
     <k n="%EntityCulture" t="s"/>
@@ -3635,153 +3589,115 @@
     <k n="Volume average"/>
     <k n="Year incorporated"/>
   </s>
+  <s t="_linkedentity">
+    <k n="%cvi" t="r"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
+  <s t="_sourceattribution">
+    <k n="License" t="r"/>
+    <k n="Source" t="r"/>
+  </s>
+  <s t="_imageurl">
+    <k n="_Provider" t="spb"/>
+    <k n="Address" t="s"/>
+    <k n="Attribution" t="r"/>
+    <k n="ComputedImage" t="b"/>
+    <k n="More Images Address" t="s"/>
+    <k n="Text" t="s"/>
+  </s>
+  <s t="_linkedentitycore">
+    <k n="%EntityCulture" t="s"/>
+    <k n="%EntityId" t="s"/>
+    <k n="%EntityServiceId"/>
+    <k n="%IsRefreshable" t="b"/>
+    <k n="%ProviderInfo" t="s"/>
+    <k n="_Display" t="spb"/>
+    <k n="_DisplayString" t="s"/>
+    <k n="_Flags" t="spb"/>
+    <k n="_Format" t="spb"/>
+    <k n="_Icon" t="s"/>
+    <k n="_SubLabel" t="spb"/>
+    <k n="52 week high"/>
+    <k n="52 week low"/>
+    <k n="Beta"/>
+    <k n="Change"/>
+    <k n="Change (%)"/>
+    <k n="Currency" t="s"/>
+    <k n="Description" t="s"/>
+    <k n="Employees"/>
+    <k n="Exchange" t="s"/>
+    <k n="Exchange abbreviation" t="s"/>
+    <k n="ExchangeID" t="s"/>
+    <k n="Headquarters" t="s"/>
+    <k n="High"/>
+    <k n="Image" t="r"/>
+    <k n="Industry" t="s"/>
+    <k n="Instrument type" t="s"/>
+    <k n="Last trade time"/>
+    <k n="LearnMoreOnLink" t="r"/>
+    <k n="Low"/>
+    <k n="Market cap"/>
+    <k n="Name" t="s"/>
+    <k n="Official name" t="s"/>
+    <k n="Open"/>
+    <k n="P/E"/>
+    <k n="Previous close"/>
+    <k n="Price"/>
+    <k n="Shares outstanding"/>
+    <k n="Ticker symbol" t="s"/>
+    <k n="UniqueName" t="s"/>
+    <k n="Volume"/>
+    <k n="Volume average"/>
+    <k n="Year incorporated"/>
+  </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbArrays count="4">
-    <a count="45">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="44">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
-    <a count="46">
-      <v t="s">%EntityServiceId</v>
-      <v t="s">_Format</v>
-      <v t="s">%IsRefreshable</v>
-      <v t="s">%EntityCulture</v>
-      <v t="s">%EntityId</v>
-      <v t="s">_Icon</v>
-      <v t="s">_Display</v>
-      <v t="s">Name</v>
-      <v t="s">_SubLabel</v>
-      <v t="s">Price</v>
-      <v t="s">Price (Extended hours)</v>
-      <v t="s">Exchange</v>
-      <v t="s">Official name</v>
-      <v t="s">Last trade time</v>
-      <v t="s">Ticker symbol</v>
-      <v t="s">Exchange abbreviation</v>
-      <v t="s">Change</v>
-      <v t="s">Change (Extended hours)</v>
-      <v t="s">Change (%)</v>
-      <v t="s">Change % (Extended hours)</v>
-      <v t="s">Currency</v>
-      <v t="s">Previous close</v>
-      <v t="s">Open</v>
-      <v t="s">High</v>
-      <v t="s">Low</v>
-      <v t="s">52 week high</v>
-      <v t="s">52 week low</v>
-      <v t="s">Volume</v>
-      <v t="s">Volume average</v>
-      <v t="s">Market cap</v>
-      <v t="s">Beta</v>
-      <v t="s">P/E</v>
-      <v t="s">Shares outstanding</v>
-      <v t="s">Description</v>
-      <v t="s">Employees</v>
-      <v t="s">Headquarters</v>
-      <v t="s">Industry</v>
-      <v t="s">Instrument type</v>
-      <v t="s">Year incorporated</v>
-      <v t="s">_Flags</v>
-      <v t="s">UniqueName</v>
-      <v t="s">_DisplayString</v>
-      <v t="s">LearnMoreOnLink</v>
-      <v t="s">Image</v>
-      <v t="s">ExchangeID</v>
-      <v t="s">%ProviderInfo</v>
-    </a>
+  <spbArrays count="3">
     <a count="42">
       <v t="s">%EntityServiceId</v>
       <v t="s">_Format</v>
@@ -3826,8 +3742,96 @@
       <v t="s">ExchangeID</v>
       <v t="s">%ProviderInfo</v>
     </a>
+    <a count="41">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
+    <a count="43">
+      <v t="s">%EntityServiceId</v>
+      <v t="s">_Format</v>
+      <v t="s">%IsRefreshable</v>
+      <v t="s">%EntityCulture</v>
+      <v t="s">%EntityId</v>
+      <v t="s">_Icon</v>
+      <v t="s">_Display</v>
+      <v t="s">Name</v>
+      <v t="s">_SubLabel</v>
+      <v t="s">Price</v>
+      <v t="s">Exchange</v>
+      <v t="s">Official name</v>
+      <v t="s">Last trade time</v>
+      <v t="s">Ticker symbol</v>
+      <v t="s">Exchange abbreviation</v>
+      <v t="s">Change</v>
+      <v t="s">Change (%)</v>
+      <v t="s">Currency</v>
+      <v t="s">Previous close</v>
+      <v t="s">Open</v>
+      <v t="s">High</v>
+      <v t="s">Low</v>
+      <v t="s">52 week high</v>
+      <v t="s">52 week low</v>
+      <v t="s">Volume</v>
+      <v t="s">Volume average</v>
+      <v t="s">Market cap</v>
+      <v t="s">Beta</v>
+      <v t="s">P/E</v>
+      <v t="s">Shares outstanding</v>
+      <v t="s">Description</v>
+      <v t="s">Employees</v>
+      <v t="s">Headquarters</v>
+      <v t="s">Industry</v>
+      <v t="s">Instrument type</v>
+      <v t="s">Year incorporated</v>
+      <v t="s">_Flags</v>
+      <v t="s">UniqueName</v>
+      <v t="s">_DisplayString</v>
+      <v t="s">LearnMoreOnLink</v>
+      <v t="s">Image</v>
+      <v t="s">ExchangeID</v>
+      <v t="s">%ProviderInfo</v>
+    </a>
   </spbArrays>
-  <spbData count="15">
+  <spbData count="14">
     <spb s="0">
       <v>0</v>
       <v>Name</v>
@@ -3865,19 +3869,13 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="4">
-      <v>at close</v>
+      <v>Real-Time Nasdaq Last Sale</v>
       <v>from previous close</v>
       <v>from previous close</v>
-      <v>Source: Nasdaq</v>
+      <v>Source: Nasdaq Last Sale</v>
       <v>GMT</v>
-      <v>Delayed 15 minutes</v>
-      <v>from close</v>
-      <v>from close</v>
     </spb>
     <spb s="5">
       <v>1</v>
@@ -3926,19 +3924,11 @@
       <v>8</v>
       <v>9</v>
       <v>4</v>
-      <v>1</v>
-      <v>1</v>
-      <v>5</v>
     </spb>
     <spb s="10">
       <v>Powered by Refinitiv</v>
     </spb>
-    <spb s="0">
-      <v>3</v>
-      <v>Name</v>
-      <v>LearnMoreOnLink</v>
-    </spb>
-    <spb s="11">
+    <spb s="3">
       <v>11</v>
       <v>2</v>
       <v>2</v>
@@ -3960,7 +3950,7 @@
       <v>9</v>
       <v>4</v>
     </spb>
-    <spb s="12">
+    <spb s="4">
       <v>Delayed 20 minutes</v>
       <v>from previous close</v>
       <v>from previous close</v>
@@ -3972,7 +3962,7 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="13">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="11">
   <s>
     <k n="^Order" t="spba"/>
     <k n="TitleProperty" t="s"/>
@@ -4010,9 +4000,6 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="Price" t="s"/>
@@ -4020,9 +4007,6 @@
     <k n="Change (%)" t="s"/>
     <k n="ExchangeID" t="s"/>
     <k n="Last trade time" t="s"/>
-    <k n="Price (Extended hours)" t="s"/>
-    <k n="Change (Extended hours)" t="s"/>
-    <k n="Change % (Extended hours)" t="s"/>
   </s>
   <s>
     <k n="^Order" t="spba"/>
@@ -4066,41 +4050,9 @@
     <k n="Year incorporated" t="i"/>
     <k n="`%EntityServiceId" t="i"/>
     <k n="Shares outstanding" t="i"/>
-    <k n="Price (Extended hours)" t="i"/>
-    <k n="Change (Extended hours)" t="i"/>
-    <k n="Change % (Extended hours)" t="i"/>
   </s>
   <s>
     <k n="name" t="s"/>
-  </s>
-  <s>
-    <k n="Low" t="i"/>
-    <k n="P/E" t="i"/>
-    <k n="Beta" t="i"/>
-    <k n="High" t="i"/>
-    <k n="Name" t="i"/>
-    <k n="Open" t="i"/>
-    <k n="Price" t="i"/>
-    <k n="Change" t="i"/>
-    <k n="Volume" t="i"/>
-    <k n="Employees" t="i"/>
-    <k n="Change (%)" t="i"/>
-    <k n="Market cap" t="i"/>
-    <k n="52 week low" t="i"/>
-    <k n="52 week high" t="i"/>
-    <k n="Previous close" t="i"/>
-    <k n="Volume average" t="i"/>
-    <k n="Last trade time" t="i"/>
-    <k n="Year incorporated" t="i"/>
-    <k n="`%EntityServiceId" t="i"/>
-    <k n="Shares outstanding" t="i"/>
-  </s>
-  <s>
-    <k n="Price" t="s"/>
-    <k n="Change" t="s"/>
-    <k n="Change (%)" t="s"/>
-    <k n="ExchangeID" t="s"/>
-    <k n="Last trade time" t="s"/>
   </s>
 </spbStructures>
 </file>
@@ -4504,29 +4456,29 @@
       </c>
       <c r="M2" s="20">
         <f ca="1">AVERAGE(M5:M17)</f>
-        <v>59.164673809953719</v>
+        <v>53.942377174027911</v>
       </c>
       <c r="N2" s="20">
         <f ca="1">AVERAGE(N5:N17)</f>
-        <v>39.254719714013234</v>
+        <v>35.702808889974321</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="L3" s="25" t="s">
+      <c r="L3" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="25" t="s">
+      <c r="M3" s="30"/>
+      <c r="N3" s="30"/>
+      <c r="O3" s="30"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
-      <c r="T3" s="26"/>
-      <c r="U3" s="26"/>
-      <c r="V3" s="27"/>
+      <c r="R3" s="30"/>
+      <c r="S3" s="30"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="30"/>
+      <c r="V3" s="31"/>
       <c r="Z3" s="13">
         <f>AVERAGE(Z5:Z33)</f>
         <v>1052549.8109809407</v>
@@ -4635,11 +4587,11 @@
       </c>
       <c r="D5" s="4" cm="1">
         <f t="array" aca="1" ref="D5" ca="1">_FV(B5,"Price")</f>
-        <v>210.96</v>
+        <v>225.16</v>
       </c>
       <c r="E5" s="6">
         <f ca="1">+D5*H5</f>
-        <v>5126328</v>
+        <v>5471388</v>
       </c>
       <c r="F5" s="6">
         <f>+[1]Main!$K$5-[1]Main!$K$6</f>
@@ -4647,7 +4599,7 @@
       </c>
       <c r="G5" s="6">
         <f t="shared" ref="G5:G16" ca="1" si="0">+E5-F5</f>
-        <v>5078003</v>
+        <v>5423063</v>
       </c>
       <c r="H5" s="6">
         <f>+[1]Main!$K$3</f>
@@ -4664,19 +4616,19 @@
       </c>
       <c r="L5" s="19">
         <f ca="1">($G5/$H5)/R5</f>
-        <v>71.078679208308841</v>
+        <v>75.908611181097953</v>
       </c>
       <c r="M5" s="20">
         <f ca="1">($G$5/$H$5)/S5</f>
-        <v>42.647207524985298</v>
+        <v>45.545166708658769</v>
       </c>
       <c r="N5" s="20">
         <f ca="1">($G$5/$H$5)/T5</f>
-        <v>25.238081747877779</v>
+        <v>26.953057593288406</v>
       </c>
       <c r="O5" s="20">
         <f ca="1">($G$5/$H$5)/U5</f>
-        <v>18.775500168232522</v>
+        <v>20.051331255384362</v>
       </c>
       <c r="P5" s="20"/>
       <c r="Q5" s="21">
@@ -4714,11 +4666,11 @@
       </c>
       <c r="D6" s="4" cm="1">
         <f t="array" aca="1" ref="D6" ca="1">_FV(B6,"Price")</f>
-        <v>434.11</v>
+        <v>426.35</v>
       </c>
       <c r="E6" s="6">
         <f ca="1">+D6*H6/5</f>
-        <v>2251381.2820000001</v>
+        <v>2211136.37</v>
       </c>
       <c r="F6" s="6">
         <f>([2]Main!$J$7-[2]Main!$J$8)/FX!C5</f>
@@ -4726,7 +4678,7 @@
       </c>
       <c r="G6" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>2339066.4336098782</v>
+        <v>2298821.5216098782</v>
       </c>
       <c r="H6" s="6">
         <f>+[2]Main!$J$4</f>
@@ -4740,15 +4692,15 @@
       </c>
       <c r="L6" s="19">
         <f ca="1">($G6/$H6)/R6*5</f>
-        <v>42.428729895672504</v>
+        <v>41.698720488334793</v>
       </c>
       <c r="M6" s="20">
         <f ca="1">($G6/$H6)/S6*5</f>
-        <v>28.874353315684942</v>
+        <v>28.377554340012733</v>
       </c>
       <c r="N6" s="20">
         <f ca="1">($G6/$H6)/T6*5</f>
-        <v>23.04636682631573</v>
+        <v>22.649841532498662</v>
       </c>
       <c r="Q6" s="17">
         <v>7.04</v>
@@ -4824,11 +4776,11 @@
       </c>
       <c r="D8" s="4" cm="1">
         <f t="array" aca="1" ref="D8" ca="1">_FV(B8,"Price")</f>
-        <v>399.97</v>
+        <v>392.99</v>
       </c>
       <c r="E8" s="6">
         <f ca="1">+D8*H8</f>
-        <v>1955053.36</v>
+        <v>1920935.12</v>
       </c>
       <c r="F8" s="6">
         <f>+[3]Main!$J$5-[3]Main!$J$6</f>
@@ -4836,7 +4788,7 @@
       </c>
       <c r="G8" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>2006936.36</v>
+        <v>1972818.12</v>
       </c>
       <c r="H8" s="6">
         <f>+[3]Main!$J$3</f>
@@ -4850,15 +4802,15 @@
       </c>
       <c r="L8" s="19">
         <f t="shared" ref="L8:N10" ca="1" si="1">($G8/$H8)/R8</f>
-        <v>86.076386101075002</v>
+        <v>84.613073732102251</v>
       </c>
       <c r="M8" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>36.270703330576652</v>
+        <v>35.654095556725061</v>
       </c>
       <c r="N8" s="20">
         <f t="shared" ca="1" si="1"/>
-        <v>22.822921717739174</v>
+        <v>22.434928388111601</v>
       </c>
       <c r="O8" s="20"/>
       <c r="Q8" s="17">
@@ -4928,21 +4880,20 @@
       <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="4" cm="1">
-        <f t="array" aca="1" ref="D10" ca="1">_FV(B10,"Price")</f>
-        <v>557.89</v>
+      <c r="D10" s="4">
+        <v>484</v>
       </c>
       <c r="E10" s="6">
-        <f t="shared" ref="E10:E16" ca="1" si="2">+D10*H10</f>
-        <v>915497.49</v>
+        <f t="shared" ref="E10:E16" si="2">+D10*H10</f>
+        <v>794244</v>
       </c>
       <c r="F10" s="6">
         <f>+[5]Main!$M$5-[5]Main!$M$6</f>
         <v>4023</v>
       </c>
       <c r="G10" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>911474.49</v>
+        <f t="shared" si="0"/>
+        <v>790221</v>
       </c>
       <c r="H10" s="6">
         <f>+[5]Main!$M$3</f>
@@ -4958,16 +4909,16 @@
         <v>1969</v>
       </c>
       <c r="L10" s="19">
-        <f t="shared" ca="1" si="1"/>
-        <v>209.5994136111207</v>
+        <f t="shared" si="1"/>
+        <v>181.71639474319616</v>
       </c>
       <c r="M10" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>81.085904535689025</v>
+        <f t="shared" si="1"/>
+        <v>70.299043221820412</v>
       </c>
       <c r="N10" s="20">
-        <f t="shared" ca="1" si="1"/>
-        <v>49.504317831503549</v>
+        <f t="shared" si="1"/>
+        <v>42.918756334177345</v>
       </c>
       <c r="O10" s="20"/>
       <c r="Q10" s="21">
@@ -5000,25 +4951,24 @@
         <f t="array" aca="1" ref="C11" ca="1">_FV(B11,"Ticker symbol",TRUE)</f>
         <v>INTC</v>
       </c>
-      <c r="D11" s="4" cm="1">
-        <f t="array" aca="1" ref="D11" ca="1">_FV(B11,"Price")</f>
-        <v>109.84</v>
+      <c r="D11" s="4">
+        <v>91</v>
       </c>
       <c r="E11" s="6">
-        <f t="shared" ca="1" si="2"/>
-        <v>552055.84</v>
+        <f t="shared" si="2"/>
+        <v>464464</v>
       </c>
       <c r="F11" s="6">
         <f>+[6]Main!$L$5-[6]Main!$L$6</f>
-        <v>-6951</v>
+        <v>-12400</v>
       </c>
       <c r="G11" s="6">
-        <f t="shared" ca="1" si="0"/>
-        <v>559006.84</v>
+        <f t="shared" si="0"/>
+        <v>476864</v>
       </c>
       <c r="H11" s="6">
         <f>+[6]Main!$L$3</f>
-        <v>5026</v>
+        <v>5104</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>254</v>
@@ -5027,16 +4977,16 @@
         <v>46198</v>
       </c>
       <c r="L11" s="19">
-        <f t="shared" ref="L11:N11" ca="1" si="3">($G11/$H11)/R11</f>
-        <v>-1853.7168059424328</v>
+        <f t="shared" ref="L11:N11" si="3">($G11/$H11)/R11</f>
+        <v>-1557.1577847439917</v>
       </c>
       <c r="M11" s="20">
-        <f t="shared" ca="1" si="3"/>
-        <v>106.94520034283265</v>
+        <f t="shared" si="3"/>
+        <v>89.836026042922597</v>
       </c>
       <c r="N11" s="20">
-        <f t="shared" ca="1" si="3"/>
-        <v>75.661910446629904</v>
+        <f t="shared" si="3"/>
+        <v>63.557460601795576</v>
       </c>
       <c r="Q11" s="17">
         <v>-4.38</v>
@@ -5069,22 +5019,22 @@
       </c>
       <c r="D12" s="4" cm="1">
         <f t="array" aca="1" ref="D12" ca="1">_FV(B12,"Price")</f>
-        <v>323.39</v>
+        <v>279.44</v>
       </c>
       <c r="E12" s="6">
         <f ca="1">+D12*H12</f>
-        <v>337779.89517847996</v>
+        <v>291874.25062208</v>
       </c>
       <c r="F12" s="6">
-        <f>+[25]Main!$L$5-[25]Main!$L$6</f>
+        <f>+[7]Main!$L$5-[7]Main!$L$6</f>
         <v>3664</v>
       </c>
       <c r="G12" s="6">
         <f ca="1">+E12-F12</f>
-        <v>334115.89517847996</v>
+        <v>288210.25062208</v>
       </c>
       <c r="H12" s="6">
-        <f>+[25]Main!$L$3</f>
+        <f>+[7]Main!$L$3</f>
         <v>1044.497032</v>
       </c>
       <c r="I12" s="3" t="s">
@@ -5106,22 +5056,22 @@
       </c>
       <c r="D13" s="4" cm="1">
         <f t="array" aca="1" ref="D13" ca="1">_FV(B13,"Price")</f>
-        <v>311.45999999999998</v>
+        <v>279.58</v>
       </c>
       <c r="E13" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>282672.28541951999</v>
+        <v>253738.89924095999</v>
       </c>
       <c r="F13" s="6">
-        <f>+[7]Main!$K$5-[7]Main!$K$6</f>
+        <f>+[8]Main!$K$5-[8]Main!$K$6</f>
         <v>1153</v>
       </c>
       <c r="G13" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>281519.28541951999</v>
+        <v>252585.89924095999</v>
       </c>
       <c r="H13" s="6">
-        <f>+[7]Main!$K$3</f>
+        <f>+[8]Main!$K$3</f>
         <v>907.57171200000005</v>
       </c>
       <c r="I13" s="3" t="s">
@@ -5146,22 +5096,22 @@
       </c>
       <c r="D14" s="4" cm="1">
         <f t="array" aca="1" ref="D14" ca="1">_FV(B14,"Price")</f>
-        <v>189.16</v>
+        <v>165.79</v>
       </c>
       <c r="E14" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>210724.24</v>
+        <v>184690.06</v>
       </c>
       <c r="F14" s="6">
-        <f>+[8]Main!$L$5-[8]Main!$L$6</f>
+        <f>+[9]Main!$L$5-[9]Main!$L$6</f>
         <v>-1522</v>
       </c>
       <c r="G14" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>212246.24</v>
+        <v>186212.06</v>
       </c>
       <c r="H14" s="6">
-        <f>+[8]Main!$L$3</f>
+        <f>+[9]Main!$L$3</f>
         <v>1114</v>
       </c>
       <c r="I14" s="3" t="s">
@@ -5189,22 +5139,22 @@
       </c>
       <c r="D15" s="4" cm="1">
         <f t="array" aca="1" ref="D15" ca="1">_FV(B15,"Price")</f>
-        <v>235.81</v>
+        <v>222.02</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>206286.58799999999</v>
+        <v>194223.09599999999</v>
       </c>
       <c r="F15" s="6">
-        <f>+[9]Main!$H$5-[9]Main!$H$6</f>
+        <f>+[10]Main!$H$5-[10]Main!$H$6</f>
         <v>-1117.7000000000003</v>
       </c>
       <c r="G15" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>207404.288</v>
+        <v>195340.796</v>
       </c>
       <c r="H15" s="6">
-        <f>[9]Main!$H$3</f>
+        <f>[10]Main!$H$3</f>
         <v>874.8</v>
       </c>
       <c r="I15" s="3" t="s">
@@ -5226,22 +5176,22 @@
       </c>
       <c r="D16" s="4" cm="1">
         <f t="array" aca="1" ref="D16" ca="1">_FV(B16,"Price")</f>
-        <v>395.65</v>
+        <v>389.39</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" ca="1" si="2"/>
-        <v>192715.98737599998</v>
+        <v>189666.82250559999</v>
       </c>
       <c r="F16" s="6">
-        <f>+[10]Main!$J$5-[10]Main!$J$6</f>
+        <f>+[11]Main!$J$5-[11]Main!$J$6</f>
         <v>-4695.3429999999998</v>
       </c>
       <c r="G16" s="6">
         <f t="shared" ca="1" si="0"/>
-        <v>197411.33037599997</v>
+        <v>194362.16550559999</v>
       </c>
       <c r="H16" s="6">
-        <f>+[10]Main!$J$3</f>
+        <f>+[11]Main!$J$3</f>
         <v>487.08704</v>
       </c>
       <c r="I16" s="3" t="s">
@@ -5266,22 +5216,22 @@
       </c>
       <c r="D17" s="4" cm="1">
         <f t="array" aca="1" ref="D17" ca="1">_FV(B17,"Price")</f>
-        <v>3925</v>
+        <v>4050</v>
       </c>
       <c r="E17" s="6">
         <f ca="1">+D17*H17/FX!C5</f>
-        <v>196679.43107221008</v>
+        <v>202943.10722100656</v>
       </c>
       <c r="F17" s="6">
-        <f>([24]Main!$K$5-[24]Main!$K$6)/FX!C5</f>
+        <f>([12]Main!$K$5-[12]Main!$K$6)/FX!C5</f>
         <v>9981.0878399499852</v>
       </c>
       <c r="G17" s="6">
         <f ca="1">+E17-F17</f>
-        <v>186698.34323226009</v>
+        <v>192962.01938105657</v>
       </c>
       <c r="H17" s="6">
-        <f>+[24]Main!$K$3</f>
+        <f>+[12]Main!$K$3</f>
         <v>1603</v>
       </c>
       <c r="I17" s="3" t="s">
@@ -5416,7 +5366,7 @@
         <v>13216</v>
       </c>
       <c r="F24" s="6">
-        <f>+[11]Main!$M$5-[11]Main!$M$6</f>
+        <f>+[13]Main!$M$5-[13]Main!$M$6</f>
         <v>-504</v>
       </c>
       <c r="G24" s="6">
@@ -5424,7 +5374,7 @@
         <v>13720</v>
       </c>
       <c r="H24" s="6">
-        <f>+[11]Main!$M$3</f>
+        <f>+[13]Main!$M$3</f>
         <v>640</v>
       </c>
       <c r="I24" s="3" t="s">
@@ -5489,11 +5439,14 @@
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="B31" t="s">
+      <c r="B31" s="1" t="s">
         <v>95</v>
       </c>
       <c r="C31" t="s">
         <v>276</v>
+      </c>
+      <c r="D31" s="4">
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
@@ -5882,7 +5835,7 @@
         <v>15167.281808</v>
       </c>
       <c r="F60" s="6">
-        <f>+[12]Main!$J$5-[12]Main!$J$6</f>
+        <f>+[14]Main!$J$5-[14]Main!$J$6</f>
         <v>446.97199999999998</v>
       </c>
       <c r="G60" s="6">
@@ -5890,7 +5843,7 @@
         <v>14720.309808</v>
       </c>
       <c r="H60" s="6">
-        <f>+[12]Main!$J$3</f>
+        <f>+[14]Main!$J$3</f>
         <v>135.42215899999999</v>
       </c>
       <c r="I60" s="3" t="s">
@@ -5915,7 +5868,7 @@
         <v>10543.625651</v>
       </c>
       <c r="F61" s="6">
-        <f>+[13]Main!$K$5-[13]Main!$K$6</f>
+        <f>+[15]Main!$K$5-[15]Main!$K$6</f>
         <v>1203</v>
       </c>
       <c r="G61" s="6">
@@ -5923,7 +5876,7 @@
         <v>9340.6256510000003</v>
       </c>
       <c r="H61" s="6">
-        <f>+[13]Main!$K$3</f>
+        <f>+[15]Main!$K$3</f>
         <v>811.04812700000002</v>
       </c>
       <c r="I61" s="3" t="s">
@@ -5951,7 +5904,7 @@
         <v>2743.6190918399998</v>
       </c>
       <c r="F62" s="6">
-        <f>+[14]Main!$J$5-[14]Main!$J$6</f>
+        <f>+[16]Main!$J$5-[16]Main!$J$6</f>
         <v>295.214</v>
       </c>
       <c r="G62" s="6">
@@ -5959,7 +5912,7 @@
         <v>2448.4050918399998</v>
       </c>
       <c r="H62" s="6">
-        <f>+[14]Main!$J$3</f>
+        <f>+[16]Main!$J$3</f>
         <v>63.864503999999997</v>
       </c>
       <c r="I62" s="3" t="s">
@@ -6013,6 +5966,7 @@
     <hyperlink ref="B12" r:id="rId15" display="ARM.xlsx" xr:uid="{EDFF8EAA-F0C0-4AD9-A9CE-06C5F0CECDD4}"/>
     <hyperlink ref="B16" r:id="rId16" display="ADI.xlsx" xr:uid="{E9120624-73BC-4C1B-A57B-3C4288B30E7A}"/>
     <hyperlink ref="B17" r:id="rId17" display="2454 TT MediaTek.xlsx" xr:uid="{0CFD06DE-D7B0-479F-91F4-5C68224B7360}"/>
+    <hyperlink ref="B31" r:id="rId18" xr:uid="{4F99BC6E-8FE4-433A-BBB2-9A9D616089A2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6023,11 +5977,11 @@
   <dimension ref="A1:AC10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="0.1796875" customWidth="1"/>
     <col min="3" max="3" width="13.54296875" customWidth="1"/>
     <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.36328125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.1796875" style="3" customWidth="1"/>
     <col min="6" max="6" width="9.81640625" style="3" customWidth="1"/>
     <col min="7" max="7" width="8.7265625" style="3"/>
     <col min="8" max="8" width="9.54296875" style="3" customWidth="1"/>
@@ -6039,27 +5993,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>115</v>
+      <c r="A1" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="13" x14ac:dyDescent="0.3">
-      <c r="M2" s="33" t="s">
+      <c r="M2" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="33" t="s">
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="32" t="s">
         <v>239</v>
       </c>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
-      <c r="X2" s="35"/>
+      <c r="T2" s="33"/>
+      <c r="U2" s="33"/>
+      <c r="V2" s="33"/>
+      <c r="W2" s="33"/>
+      <c r="X2" s="34"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -6150,7 +6104,7 @@
       <c r="D4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="14">
         <v>285000</v>
       </c>
       <c r="F4" s="6">
@@ -6175,11 +6129,6 @@
       <c r="K4" s="10">
         <v>46207</v>
       </c>
-      <c r="N4" s="29"/>
-      <c r="O4" s="29"/>
-      <c r="P4" s="29"/>
-      <c r="Q4" s="29"/>
-      <c r="S4" s="29"/>
       <c r="AB4" s="13"/>
       <c r="AC4" s="13"/>
     </row>
@@ -6197,22 +6146,22 @@
         <v>10</v>
       </c>
       <c r="E5" s="4">
-        <v>980</v>
+        <v>830</v>
       </c>
       <c r="F5" s="6">
         <f>+E5*I5</f>
-        <v>1122100</v>
+        <v>950350</v>
       </c>
       <c r="G5" s="6">
-        <f>+[15]Main!$J$5-[15]Main!$J$6</f>
+        <f>+[17]Main!$J$5-[17]Main!$J$6</f>
         <v>25303</v>
       </c>
       <c r="H5" s="6">
         <f>+F5-G5</f>
-        <v>1096797</v>
+        <v>925047</v>
       </c>
       <c r="I5" s="6">
-        <f>+[15]Main!$J$3</f>
+        <f>+[17]Main!$J$3</f>
         <v>1145</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -6225,30 +6174,30 @@
         <v>1978</v>
       </c>
       <c r="M5" s="19">
-        <f>($H5/$I5)/S5</f>
-        <v>1368.4304429195261</v>
-      </c>
-      <c r="N5" s="31">
-        <f>($H5/$I5)/T5</f>
-        <v>126.20570619811174</v>
-      </c>
-      <c r="O5" s="31">
-        <f>($H5/$I5)/U5</f>
-        <v>13.096818567728576</v>
-      </c>
-      <c r="P5" s="31">
-        <f>($H5/$I5)/V5</f>
-        <v>6.2784381598195464</v>
-      </c>
-      <c r="Q5" s="31">
-        <f>($H5/$I5)/W5</f>
-        <v>10.775042857634061</v>
-      </c>
-      <c r="R5" s="32">
-        <f>($H5/$I5)/X5</f>
-        <v>15.314169624998691</v>
-      </c>
-      <c r="S5" s="30">
+        <f t="shared" ref="M5:R5" si="0">($H5/$I5)/S5</f>
+        <v>1154.1447286338116</v>
+      </c>
+      <c r="N5" s="20">
+        <f t="shared" si="0"/>
+        <v>106.44286034830937</v>
+      </c>
+      <c r="O5" s="20">
+        <f t="shared" si="0"/>
+        <v>11.045957205956633</v>
+      </c>
+      <c r="P5" s="20">
+        <f t="shared" si="0"/>
+        <v>5.2952828868300985</v>
+      </c>
+      <c r="Q5" s="20">
+        <f t="shared" si="0"/>
+        <v>9.0877537687701686</v>
+      </c>
+      <c r="R5" s="25">
+        <f t="shared" si="0"/>
+        <v>12.916088090226509</v>
+      </c>
+      <c r="S5" s="2">
         <v>0.7</v>
       </c>
       <c r="T5" s="2">
@@ -6260,7 +6209,7 @@
       <c r="V5" s="2">
         <v>152.57</v>
       </c>
-      <c r="W5" s="28">
+      <c r="W5" s="2">
         <v>88.9</v>
       </c>
       <c r="X5" s="18">
@@ -6278,18 +6227,39 @@
         <v>36</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" t="s">
-        <v>268</v>
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="Q6" s="29"/>
-      <c r="S6" s="29"/>
+        <v>44</v>
+      </c>
+      <c r="E6" s="14">
+        <v>1816000</v>
+      </c>
+      <c r="F6" s="6">
+        <f>+E6*I6/KRW</f>
+        <v>890643.70587222313</v>
+      </c>
+      <c r="G6" s="6">
+        <f>([18]Main!$L$5-[18]Main!$L$6)/KRW</f>
+        <v>47783.709316342349</v>
+      </c>
+      <c r="H6" s="6">
+        <f>+F6-G6</f>
+        <v>842859.99655588076</v>
+      </c>
+      <c r="I6" s="6">
+        <f>+[18]Main!$L$3</f>
+        <v>712</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K6" s="10">
+        <v>46230</v>
+      </c>
       <c r="AB6" s="13"/>
       <c r="AC6" s="13"/>
     </row>
@@ -6298,20 +6268,39 @@
         <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>268</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="6">
-        <v>1007000</v>
-      </c>
-      <c r="F7" s="6"/>
-      <c r="Q7" s="29"/>
-      <c r="S7" s="29"/>
+        <v>269</v>
+      </c>
+      <c r="E7" s="28">
+        <v>54550</v>
+      </c>
+      <c r="F7" s="6">
+        <f>+E7*I7/JPY</f>
+        <v>187342.33792559939</v>
+      </c>
+      <c r="G7" s="6">
+        <f>([19]Main!$J$5-[19]Main!$J$6)/JPY</f>
+        <v>-2171.4004820499808</v>
+      </c>
+      <c r="H7" s="6">
+        <f>+F7-G7</f>
+        <v>189513.73840764936</v>
+      </c>
+      <c r="I7" s="6">
+        <f>+[19]Main!$J$3</f>
+        <v>541.45541700000001</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K7" s="10">
+        <v>46230</v>
+      </c>
       <c r="AB7" s="13"/>
       <c r="AC7" s="13"/>
     </row>
@@ -6330,32 +6319,30 @@
       </c>
       <c r="E8" s="4" cm="1">
         <f t="array" aca="1" ref="E8" ca="1">_FV(B8,"Price")</f>
-        <v>1915.92</v>
+        <v>1641.11</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">+E8*I8</f>
-        <v>283728.12914735998</v>
+        <v>243031.58275137996</v>
       </c>
       <c r="G8" s="6">
-        <f>+[16]Main!$L$5-[16]Main!$L$6</f>
+        <f>+[20]Main!$L$5-[20]Main!$L$6</f>
         <v>3735</v>
       </c>
       <c r="H8" s="6">
         <f ca="1">+F8-G8</f>
-        <v>279993.12914735998</v>
+        <v>239296.58275137996</v>
       </c>
       <c r="I8" s="6">
-        <f>+[16]Main!$L$3</f>
+        <f>+[20]Main!$L$3</f>
         <v>148.08975799999999</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>254</v>
       </c>
       <c r="K8" s="10">
-        <v>46146</v>
-      </c>
-      <c r="Q8" s="29"/>
-      <c r="S8" s="29"/>
+        <v>46230</v>
+      </c>
       <c r="AC8">
         <v>625000</v>
       </c>
@@ -6375,11 +6362,9 @@
       </c>
       <c r="E9" s="4" cm="1">
         <f t="array" aca="1" ref="E9" ca="1">_FV(B9,"Price")</f>
-        <v>910.34</v>
+        <v>973.44</v>
       </c>
       <c r="F9" s="6"/>
-      <c r="Q9" s="29"/>
-      <c r="S9" s="29"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
@@ -6396,11 +6381,9 @@
       </c>
       <c r="E10" s="4" cm="1">
         <f t="array" aca="1" ref="E10" ca="1">_FV(B10,"Price")</f>
-        <v>582.58500000000004</v>
+        <v>508.8</v>
       </c>
       <c r="F10" s="6"/>
-      <c r="Q10" s="29"/>
-      <c r="S10" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6409,19 +6392,21 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B5" r:id="rId1" display="MU.xlsx" xr:uid="{C50FA289-6EE1-4DAA-B344-2AFF21D7BBD1}"/>
-    <hyperlink ref="B7" r:id="rId2" display="NVDA.xlsx" xr:uid="{BB28EC67-A86C-4D67-BB7A-EC0D785C32BB}"/>
-    <hyperlink ref="B6" r:id="rId3" display="NVDA.xlsx" xr:uid="{F58E2C92-B174-41FA-9008-D56DC0490143}"/>
+    <hyperlink ref="B6" r:id="rId2" display="NVDA.xlsx" xr:uid="{BB28EC67-A86C-4D67-BB7A-EC0D785C32BB}"/>
+    <hyperlink ref="B7" r:id="rId3" display="NVDA.xlsx" xr:uid="{F58E2C92-B174-41FA-9008-D56DC0490143}"/>
     <hyperlink ref="B8" r:id="rId4" display="NVDA.xlsx" xr:uid="{189BA126-A6AA-4682-BBEF-32377A1B9453}"/>
     <hyperlink ref="B9" r:id="rId5" display="NVDA.xlsx" xr:uid="{57AC8EC0-51DD-418F-B632-90A83298F5CA}"/>
     <hyperlink ref="B10" r:id="rId6" display="NVDA.xlsx" xr:uid="{08079C4F-8AB3-4A9B-9015-3E26D655952F}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{B27CF321-7BF4-4270-AEE8-B748F0C4C26B}"/>
     <hyperlink ref="C4" r:id="rId8" xr:uid="{1029B44D-CEA0-4D67-8448-8B6C9BD51C81}"/>
-    <hyperlink ref="C7" r:id="rId9" xr:uid="{CFBBFB6B-8B2B-4FFB-8BF8-C48FB7738363}"/>
+    <hyperlink ref="C6" r:id="rId9" xr:uid="{CFBBFB6B-8B2B-4FFB-8BF8-C48FB7738363}"/>
     <hyperlink ref="C5" r:id="rId10" xr:uid="{7B5B4C89-03CC-4E5D-A0CC-890BDE26B1A6}"/>
     <hyperlink ref="C8" r:id="rId11" xr:uid="{C3511D7D-1F0E-40D4-818C-166E2D5CD881}"/>
+    <hyperlink ref="C7" r:id="rId12" xr:uid="{C0505EF0-56E9-43B0-B007-1F1B2EA5EB23}"/>
+    <hyperlink ref="A1" location="Semiconductors!A1" display="Semis" xr:uid="{DA0360A2-4C16-4960-A6E7-02CAD873B77C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId12"/>
+  <legacyDrawing r:id="rId13"/>
 </worksheet>
 </file>
 
@@ -6485,7 +6470,7 @@
         <v>530438</v>
       </c>
       <c r="F3" s="6">
-        <f>+[17]Main!$L$5-[17]Main!$L$6</f>
+        <f>+[21]Main!$L$5-[21]Main!$L$6</f>
         <v>1413.0000000000009</v>
       </c>
       <c r="G3" s="6">
@@ -6493,7 +6478,7 @@
         <v>529025</v>
       </c>
       <c r="H3" s="6">
-        <f>+[17]Main!$L$3</f>
+        <f>+[21]Main!$L$3</f>
         <v>393.5</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -6525,7 +6510,7 @@
         <v>267520</v>
       </c>
       <c r="F4" s="6">
-        <f>+[18]Main!$K$5-[18]Main!$K$6</f>
+        <f>+[22]Main!$K$5-[22]Main!$K$6</f>
         <v>6926</v>
       </c>
       <c r="G4" s="6">
@@ -6533,7 +6518,7 @@
         <v>260594</v>
       </c>
       <c r="H4" s="6">
-        <f>+[18]Main!$K$3</f>
+        <f>+[22]Main!$K$3</f>
         <v>799</v>
       </c>
       <c r="I4" s="3" t="s">
@@ -6657,15 +6642,95 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DF4C6BF-D4BF-4479-9128-495AD030DB4E}">
-  <dimension ref="A4:V9"/>
+  <dimension ref="A3:X10"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.90625" customWidth="1"/>
     <col min="2" max="2" width="29.81640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.7265625" style="26"/>
+    <col min="6" max="8" width="8.7265625" style="13"/>
+    <col min="10" max="10" width="8.90625" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M3" s="17">
+        <v>2025</v>
+      </c>
+      <c r="N3">
+        <v>2026</v>
+      </c>
+      <c r="O3">
+        <f>+N3+1</f>
+        <v>2027</v>
+      </c>
+      <c r="P3">
+        <f>+O3+1</f>
+        <v>2028</v>
+      </c>
+      <c r="Q3">
+        <f>+P3+1</f>
+        <v>2029</v>
+      </c>
+      <c r="R3" s="18">
+        <v>2030</v>
+      </c>
+      <c r="S3">
+        <v>2025</v>
+      </c>
+      <c r="T3">
+        <v>2026</v>
+      </c>
+      <c r="U3">
+        <v>2027</v>
+      </c>
+      <c r="V3">
+        <f>+U3+1</f>
+        <v>2028</v>
+      </c>
+      <c r="W3">
+        <f>+V3+1</f>
+        <v>2029</v>
+      </c>
+      <c r="X3" s="18">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -6673,43 +6738,65 @@
         <v>266</v>
       </c>
       <c r="C4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
       <c r="L4" s="17"/>
       <c r="P4" s="18"/>
       <c r="Q4" s="17"/>
       <c r="V4" s="18"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>36</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>283</v>
       </c>
       <c r="C5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" s="27" t="s">
         <v>284</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="E5" s="4">
+        <v>819</v>
+      </c>
+      <c r="F5" s="6">
+        <f>+E5*I5</f>
+        <v>78787.8</v>
+      </c>
+      <c r="G5" s="6">
+        <f>+[23]Main!$I$5-[23]Main!$I$6</f>
+        <v>-109.49999999999955</v>
+      </c>
+      <c r="H5" s="6">
+        <f>+F5-G5</f>
+        <v>78897.3</v>
+      </c>
+      <c r="I5" s="6">
+        <f>+[23]Main!$I$3</f>
+        <v>96.2</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="K5" s="10">
+        <v>46217</v>
+      </c>
       <c r="L5" s="17"/>
       <c r="P5" s="18"/>
       <c r="Q5" s="17"/>
       <c r="V5" s="18"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>36</v>
       </c>
@@ -6717,21 +6804,22 @@
         <v>287</v>
       </c>
       <c r="C6" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="4"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
       <c r="L6" s="17"/>
       <c r="P6" s="18"/>
       <c r="Q6" s="17"/>
       <c r="V6" s="18"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -6742,7 +6830,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>36</v>
       </c>
@@ -6753,7 +6841,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -6764,7 +6852,47 @@
         <v>343</v>
       </c>
     </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="E10" s="2">
+        <v>118</v>
+      </c>
+      <c r="F10" s="13">
+        <f>+E10*I10</f>
+        <v>9979.1699659999995</v>
+      </c>
+      <c r="G10" s="13">
+        <f>+[24]Main!$J$5-[24]Main!$J$6</f>
+        <v>442.47900000000004</v>
+      </c>
+      <c r="H10" s="13">
+        <f>+F10-G10</f>
+        <v>9536.6909660000001</v>
+      </c>
+      <c r="I10" s="13">
+        <f>+[24]Main!$J$3</f>
+        <v>84.569237000000001</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="K10" s="5">
+        <v>46240</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{452462D9-D5E5-4B84-A36E-3B9E33E85711}"/>
+    <hyperlink ref="B10" r:id="rId2" xr:uid="{6252A5C0-F9AD-44A9-B030-C369CEBBED47}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -6776,6 +6904,7 @@
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.26953125" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -6820,9 +6949,11 @@
         <v>124</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" s="3"/>
+        <v>296</v>
+      </c>
+      <c r="D3" s="3">
+        <v>56.14</v>
+      </c>
       <c r="E3" s="6">
         <v>20000</v>
       </c>
@@ -6859,29 +6990,29 @@
         <v>109</v>
       </c>
       <c r="D5" s="2">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E5" s="13">
         <f>+D5*H5</f>
-        <v>17711.180015999998</v>
+        <v>13727</v>
       </c>
       <c r="F5" s="13">
-        <f>+[19]Main!$J$5-[19]Main!$J$6</f>
-        <v>3336.799</v>
+        <f>+[25]Main!$J$5-[25]Main!$J$6</f>
+        <v>3091.8959999999997</v>
       </c>
       <c r="G5" s="13">
         <f>+E5-F5</f>
-        <v>14374.381015999999</v>
+        <v>10635.103999999999</v>
       </c>
       <c r="H5" s="13">
-        <f>+[19]Main!$J$3</f>
-        <v>368.98291699999999</v>
+        <f>+[25]Main!$J$3</f>
+        <v>371</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>178</v>
+        <v>254</v>
       </c>
       <c r="J5" s="5">
-        <v>45664</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -6899,7 +7030,7 @@
         <v>4239.0257214499998</v>
       </c>
       <c r="F6" s="13">
-        <f>+[20]Main!$L$5-[20]Main!$L$6</f>
+        <f>+[26]Main!$L$5-[26]Main!$L$6</f>
         <v>217</v>
       </c>
       <c r="G6" s="13">
@@ -6907,7 +7038,7 @@
         <v>4022.0257214499998</v>
       </c>
       <c r="H6" s="13">
-        <f>+[20]Main!$L$3</f>
+        <f>+[26]Main!$L$3</f>
         <v>283.54687100000001</v>
       </c>
       <c r="I6" s="3" t="s">
@@ -6946,7 +7077,7 @@
         <v>5460.8176507499993</v>
       </c>
       <c r="F8" s="13">
-        <f>+[21]Main!$L$5-[21]Main!$L$6</f>
+        <f>+[27]Main!$L$5-[27]Main!$L$6</f>
         <v>804.03300000000002</v>
       </c>
       <c r="G8" s="13">
@@ -6954,7 +7085,7 @@
         <v>4656.7846507499989</v>
       </c>
       <c r="H8" s="13">
-        <f>+[21]Main!$L$3</f>
+        <f>+[27]Main!$L$3</f>
         <v>346.71858099999997</v>
       </c>
       <c r="I8" s="3" t="s">
@@ -7451,7 +7582,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F11ECA54-B59D-4EDC-8BE7-0C63EA165B15}">
-  <dimension ref="A1:P62"/>
+  <dimension ref="A1:P63"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.1796875" customWidth="1"/>
@@ -7529,22 +7660,22 @@
         <v>11</v>
       </c>
       <c r="D3" s="4">
-        <v>205.51</v>
+        <v>334.36</v>
       </c>
       <c r="E3" s="6">
         <f>+D3*H3</f>
-        <v>3071963.48</v>
+        <v>4998013.28</v>
       </c>
       <c r="F3" s="6">
-        <f>+[22]Main!$O$5-[22]Main!$O$6</f>
+        <f>+[28]Main!$O$5-[28]Main!$O$6</f>
         <v>31288</v>
       </c>
       <c r="G3" s="6">
         <f>+E3-F3</f>
-        <v>3040675.48</v>
+        <v>4966725.28</v>
       </c>
       <c r="H3" s="6">
-        <f>+[22]Main!$O$3</f>
+        <f>+[28]Main!$O$3</f>
         <v>14948</v>
       </c>
       <c r="I3" s="3" t="s">
@@ -7554,19 +7685,19 @@
         <v>45750</v>
       </c>
       <c r="K3" s="2">
-        <f>[22]Model!$CE$39</f>
+        <f>[28]Model!$CE$39</f>
         <v>0.46906012207980208</v>
       </c>
       <c r="L3" s="7">
         <f>+K3/D3-1</f>
-        <v>-0.99771758005897615</v>
+        <v>-0.99859714044120174</v>
       </c>
       <c r="M3" s="8">
-        <f>+[22]Model!$CE$36</f>
+        <f>+[28]Model!$CE$36</f>
         <v>4.1953407917453944E-2</v>
       </c>
       <c r="N3" s="8">
-        <f>+[22]Model!$CE$37</f>
+        <f>+[28]Model!$CE$37</f>
         <v>3.632000000000013E-2</v>
       </c>
       <c r="O3" s="8">
@@ -7635,33 +7766,34 @@
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>36</v>
-      </c>
       <c r="B6" t="s">
+        <v>363</v>
+      </c>
+      <c r="C6" t="s">
+        <v>364</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" t="s">
-        <v>58</v>
-      </c>
-      <c r="C8" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -7669,10 +7801,10 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
@@ -7680,10 +7812,10 @@
         <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
@@ -7691,10 +7823,10 @@
         <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>214</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>213</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
@@ -7702,10 +7834,10 @@
         <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>214</v>
       </c>
       <c r="C12" t="s">
-        <v>73</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
@@ -7713,10 +7845,10 @@
         <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>279</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>280</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
@@ -7724,10 +7856,10 @@
         <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="C14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
@@ -7735,10 +7867,10 @@
         <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>281</v>
       </c>
       <c r="C15" t="s">
-        <v>64</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -7746,10 +7878,10 @@
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>184</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
@@ -7757,10 +7889,10 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
@@ -7768,10 +7900,10 @@
         <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>190</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -7779,10 +7911,10 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="C19" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
@@ -7790,10 +7922,10 @@
         <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
@@ -7801,10 +7933,10 @@
         <v>36</v>
       </c>
       <c r="B21" t="s">
-        <v>277</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
-        <v>278</v>
+        <v>192</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
@@ -7812,10 +7944,10 @@
         <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>201</v>
+        <v>277</v>
       </c>
       <c r="C22" t="s">
-        <v>202</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7823,10 +7955,10 @@
         <v>36</v>
       </c>
       <c r="B23" t="s">
-        <v>274</v>
+        <v>201</v>
       </c>
       <c r="C23" t="s">
-        <v>275</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -7834,10 +7966,10 @@
         <v>36</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>274</v>
       </c>
       <c r="C24" t="s">
-        <v>212</v>
+        <v>275</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -7845,21 +7977,21 @@
         <v>36</v>
       </c>
       <c r="B25" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C25" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>324</v>
+      <c r="B26" t="s">
+        <v>215</v>
       </c>
       <c r="C26" t="s">
-        <v>325</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -7867,10 +7999,10 @@
         <v>36</v>
       </c>
       <c r="B27" s="22" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
       <c r="C27" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -7878,21 +8010,21 @@
         <v>36</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
-      <c r="B29" t="s">
-        <v>219</v>
+      <c r="B29" s="22" t="s">
+        <v>349</v>
       </c>
       <c r="C29" t="s">
-        <v>220</v>
+        <v>348</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
@@ -7900,10 +8032,10 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>84</v>
+        <v>219</v>
       </c>
       <c r="C30" t="s">
-        <v>85</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -7911,10 +8043,10 @@
         <v>36</v>
       </c>
       <c r="B31" t="s">
-        <v>320</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>321</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -7922,10 +8054,10 @@
         <v>36</v>
       </c>
       <c r="B32" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="C32" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -7933,32 +8065,32 @@
         <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C33" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="22" t="s">
-        <v>322</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>323</v>
+      <c r="B34" t="s">
+        <v>334</v>
+      </c>
+      <c r="C34" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
-      <c r="B35" t="s">
-        <v>221</v>
-      </c>
-      <c r="C35" t="s">
-        <v>222</v>
+      <c r="B35" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C35" s="22" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -7966,40 +8098,40 @@
         <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C36" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C37" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="22" t="s">
         <v>356</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C38" s="22" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
         <v>232</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>233</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" t="s">
-        <v>318</v>
-      </c>
-      <c r="C39" s="22" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -8007,10 +8139,10 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
-      </c>
-      <c r="C40" t="s">
-        <v>119</v>
+        <v>318</v>
+      </c>
+      <c r="C40" s="22" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
@@ -8018,10 +8150,10 @@
         <v>36</v>
       </c>
       <c r="B41" t="s">
-        <v>312</v>
+        <v>118</v>
       </c>
       <c r="C41" t="s">
-        <v>313</v>
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
@@ -8029,10 +8161,10 @@
         <v>36</v>
       </c>
       <c r="B42" t="s">
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="C42" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
@@ -8040,21 +8172,21 @@
         <v>36</v>
       </c>
       <c r="B43" t="s">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="C43" t="s">
-        <v>300</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="22" t="s">
-        <v>350</v>
+      <c r="B44" t="s">
+        <v>299</v>
       </c>
       <c r="C44" t="s">
-        <v>351</v>
+        <v>300</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -8062,21 +8194,21 @@
         <v>36</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C45" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>36</v>
       </c>
-      <c r="B46" t="s">
-        <v>88</v>
+      <c r="B46" s="22" t="s">
+        <v>352</v>
       </c>
       <c r="C46" t="s">
-        <v>89</v>
+        <v>353</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
@@ -8084,10 +8216,10 @@
         <v>36</v>
       </c>
       <c r="B47" t="s">
-        <v>301</v>
+        <v>88</v>
       </c>
       <c r="C47" t="s">
-        <v>302</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
@@ -8095,10 +8227,10 @@
         <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>124</v>
+        <v>301</v>
       </c>
       <c r="C48" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
@@ -8106,46 +8238,21 @@
         <v>36</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>124</v>
       </c>
       <c r="C49" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>107</v>
+      <c r="B50" t="s">
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
-      </c>
-      <c r="D50" s="4">
-        <v>39</v>
-      </c>
-      <c r="E50" s="6">
-        <f>+D50*H50</f>
-        <v>14390.333762999999</v>
-      </c>
-      <c r="F50" s="6">
-        <f>+[19]Main!$J$5-[19]Main!$J$6</f>
-        <v>3336.799</v>
-      </c>
-      <c r="G50" s="6">
-        <f>+E50-F50</f>
-        <v>11053.534763</v>
-      </c>
-      <c r="H50" s="6">
-        <f>+[19]Main!$J$3</f>
-        <v>368.98291699999999</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J50" s="5">
-        <v>45534</v>
+        <v>303</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
@@ -8153,32 +8260,32 @@
         <v>36</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D51" s="3">
-        <v>8.51</v>
+        <v>109</v>
+      </c>
+      <c r="D51" s="4">
+        <v>39</v>
       </c>
       <c r="E51" s="6">
         <f>+D51*H51</f>
-        <v>2412.9838722099998</v>
+        <v>14469</v>
       </c>
       <c r="F51" s="6">
-        <f>+[20]Main!$L$5-[20]Main!$L$6</f>
-        <v>217</v>
+        <f>+[25]Main!$J$5-[25]Main!$J$6</f>
+        <v>3091.8959999999997</v>
       </c>
       <c r="G51" s="6">
         <f>+E51-F51</f>
-        <v>2195.9838722099998</v>
+        <v>11377.103999999999</v>
       </c>
       <c r="H51" s="6">
-        <f>+[20]Main!$L$3</f>
-        <v>283.54687100000001</v>
+        <f>+[25]Main!$J$3</f>
+        <v>371</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="J51" s="5">
         <v>45534</v>
@@ -8189,10 +8296,35 @@
         <v>36</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>110</v>
+        <v>112</v>
+      </c>
+      <c r="D52" s="3">
+        <v>8.51</v>
+      </c>
+      <c r="E52" s="6">
+        <f>+D52*H52</f>
+        <v>2412.9838722099998</v>
+      </c>
+      <c r="F52" s="6">
+        <f>+[26]Main!$L$5-[26]Main!$L$6</f>
+        <v>217</v>
+      </c>
+      <c r="G52" s="6">
+        <f>+E52-F52</f>
+        <v>2195.9838722099998</v>
+      </c>
+      <c r="H52" s="6">
+        <f>+[26]Main!$L$3</f>
+        <v>283.54687100000001</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="J52" s="5">
+        <v>45534</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -8200,10 +8332,10 @@
         <v>36</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C53" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -8211,13 +8343,10 @@
         <v>36</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" s="3">
-        <v>101.64</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -8225,74 +8354,88 @@
         <v>36</v>
       </c>
       <c r="B55" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="3">
+        <v>101.64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>237</v>
       </c>
-      <c r="D55" s="4">
+      <c r="D56" s="4">
         <v>247</v>
       </c>
-      <c r="E55" s="6">
-        <f>+D55*H55</f>
+      <c r="E56" s="6">
+        <f>+D56*H56</f>
         <v>28641.902146</v>
       </c>
-      <c r="F55" s="6">
-        <f>+[23]Main!$I$5-[23]Main!$I$6</f>
+      <c r="F56" s="6">
+        <f>+[29]Main!$I$5-[29]Main!$I$6</f>
         <v>-373.40000000000003</v>
       </c>
-      <c r="G55" s="6">
-        <f>+E55-F55</f>
+      <c r="G56" s="6">
+        <f>+E56-F56</f>
         <v>29015.302146000002</v>
       </c>
-      <c r="H55" s="6">
-        <f>+[23]Main!$I$3</f>
+      <c r="H56" s="6">
+        <f>+[29]Main!$I$3</f>
         <v>115.959118</v>
       </c>
-      <c r="I55" s="3" t="s">
+      <c r="I56" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="J55" s="5">
+      <c r="J56" s="5">
         <v>45915</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="B59" s="9" t="s">
+    <row r="60" spans="1:10" ht="13" x14ac:dyDescent="0.3">
+      <c r="B60" s="9" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>55</v>
-      </c>
-      <c r="E60" s="3">
-        <v>200</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E61" s="3">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
+        <v>54</v>
+      </c>
+      <c r="E62" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B63" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{CD056E5E-713C-45E7-82FC-EFD06739D880}"/>
-    <hyperlink ref="B50" r:id="rId2" xr:uid="{E138C484-1EF3-497D-8DD8-4398C67AAB14}"/>
-    <hyperlink ref="B54" r:id="rId3" xr:uid="{17EE0F28-0CA3-4454-8659-59421816F562}"/>
+    <hyperlink ref="B51" r:id="rId2" xr:uid="{E138C484-1EF3-497D-8DD8-4398C67AAB14}"/>
+    <hyperlink ref="B55" r:id="rId3" xr:uid="{17EE0F28-0CA3-4454-8659-59421816F562}"/>
     <hyperlink ref="A1" location="Semiconductors!A1" display="Semis" xr:uid="{3EBFEA52-93DD-4F50-8A15-3931D4DD8A3B}"/>
-    <hyperlink ref="B51" r:id="rId4" xr:uid="{B849A3EA-637F-401B-9004-B19AC4384C38}"/>
-    <hyperlink ref="B52" r:id="rId5" xr:uid="{B3FD8109-CF06-4F67-80CA-74CB8FA3899F}"/>
-    <hyperlink ref="B53" r:id="rId6" xr:uid="{41CB0E3A-9A33-4B05-90FA-F5D94D41DCCA}"/>
+    <hyperlink ref="B52" r:id="rId4" xr:uid="{B849A3EA-637F-401B-9004-B19AC4384C38}"/>
+    <hyperlink ref="B53" r:id="rId5" xr:uid="{B3FD8109-CF06-4F67-80CA-74CB8FA3899F}"/>
+    <hyperlink ref="B54" r:id="rId6" xr:uid="{41CB0E3A-9A33-4B05-90FA-F5D94D41DCCA}"/>
     <hyperlink ref="B4" r:id="rId7" xr:uid="{080EF83F-F30F-4A70-B656-61CF4AB15DF7}"/>
-    <hyperlink ref="B55" r:id="rId8" xr:uid="{0A91E701-42A1-47EB-A9B9-A7A56A386588}"/>
+    <hyperlink ref="B56" r:id="rId8" xr:uid="{0A91E701-42A1-47EB-A9B9-A7A56A386588}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
